--- a/03_Tools/Rebalancing_Tool_v3.4.xlsx
+++ b/03_Tools/Rebalancing_Tool_v3.4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tobia\OneDrive\Desktop\Claude Stuff\03_Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33EFF7C1-3382-40ED-B5B9-0F08C71B852C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DC77EC-8547-4709-9038-E815317B0BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/03_Tools/Rebalancing_Tool_v3.4.xlsx
+++ b/03_Tools/Rebalancing_Tool_v3.4.xlsx
@@ -1381,7 +1381,7 @@
         <v/>
       </c>
       <c r="J10" s="17">
-        <f>I10-F10</f>
+        <f>IF(P10=0,0,I10-F10)</f>
         <v/>
       </c>
       <c r="K10" s="18">
@@ -1450,7 +1450,7 @@
         <v/>
       </c>
       <c r="J11" s="23">
-        <f>I11-F11</f>
+        <f>IF(P11=0,0,I11-F11)</f>
         <v/>
       </c>
       <c r="K11" s="24">
@@ -1519,7 +1519,7 @@
         <v/>
       </c>
       <c r="J12" s="17">
-        <f>I12-F12</f>
+        <f>IF(P12=0,0,I12-F12)</f>
         <v/>
       </c>
       <c r="K12" s="18">
@@ -1588,7 +1588,7 @@
         <v/>
       </c>
       <c r="J13" s="23">
-        <f>I13-F13</f>
+        <f>IF(P13=0,0,I13-F13)</f>
         <v/>
       </c>
       <c r="K13" s="24">
@@ -1657,7 +1657,7 @@
         <v/>
       </c>
       <c r="J14" s="17">
-        <f>I14-F14</f>
+        <f>IF(P14=0,0,I14-F14)</f>
         <v/>
       </c>
       <c r="K14" s="18">
@@ -1726,7 +1726,7 @@
         <v/>
       </c>
       <c r="J15" s="23">
-        <f>I15-F15</f>
+        <f>IF(P15=0,0,I15-F15)</f>
         <v/>
       </c>
       <c r="K15" s="24">
@@ -1795,7 +1795,7 @@
         <v/>
       </c>
       <c r="J16" s="17">
-        <f>I16-F16</f>
+        <f>IF(P16=0,0,I16-F16)</f>
         <v/>
       </c>
       <c r="K16" s="18">
@@ -1864,7 +1864,7 @@
         <v/>
       </c>
       <c r="J17" s="23">
-        <f>I17-F17</f>
+        <f>IF(P17=0,0,I17-F17)</f>
         <v/>
       </c>
       <c r="K17" s="24">
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="J18" s="17">
-        <f>I18-F18</f>
+        <f>IF(P18=0,0,I18-F18)</f>
         <v/>
       </c>
       <c r="K18" s="18">
@@ -2002,7 +2002,7 @@
         <v/>
       </c>
       <c r="J19" s="23">
-        <f>I19-F19</f>
+        <f>IF(P19=0,0,I19-F19)</f>
         <v/>
       </c>
       <c r="K19" s="24">
@@ -2071,7 +2071,7 @@
         <v/>
       </c>
       <c r="J20" s="17">
-        <f>I20-F20</f>
+        <f>IF(P20=0,0,I20-F20)</f>
         <v/>
       </c>
       <c r="K20" s="18">

--- a/03_Tools/Rebalancing_Tool_v3.4.xlsx
+++ b/03_Tools/Rebalancing_Tool_v3.4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tobia\OneDrive\Desktop\Claude Stuff\03_Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6202B1A-E672-4754-8C99-DF3C7E3D451E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8340C460-79F7-476E-B969-07D07C16950D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio &amp; Rebalancing" sheetId="1" r:id="rId1"/>
@@ -149,10 +149,10 @@
     <t>Aktie</t>
   </si>
   <si>
-    <t>DEFCON 3 (66)</t>
-  </si>
-  <si>
-    <t>🟡 DEFCON 3 (66) | China Rev 14.7% Risk-Map</t>
+    <t>DEFCON 3 (68)</t>
+  </si>
+  <si>
+    <t>🟡 DEFCON 3 (68) | China Rev 14.7% Risk-Map</t>
   </si>
   <si>
     <t>Broadcom</t>
@@ -663,7 +663,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -829,13 +829,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -844,6 +842,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1323,44 +1330,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="69"/>
-      <c r="P1" s="69"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
     </row>
     <row r="2" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="70">
+      <c r="A2" s="68">
         <v>46129</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
     </row>
     <row r="3" spans="1:16" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -2929,8 +2936,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.85546875" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3150,11 +3157,11 @@
       <c r="A25" s="60" t="s">
         <v>125</v>
       </c>
-      <c r="B25" s="61">
+      <c r="B25" s="70">
         <f>B4*B6</f>
         <v>285</v>
       </c>
-      <c r="C25" s="62" t="s">
+      <c r="C25" s="61" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3162,68 +3169,68 @@
       <c r="A26" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="B26" s="63">
+      <c r="B26" s="62">
         <f>COUNTIFS('Portfolio &amp; Rebalancing'!C5:C20,"Aktie",'Portfolio &amp; Rebalancing'!N5:N20,"DEFCON 4*",'Portfolio &amp; Rebalancing'!O5:O20,"&lt;&gt;🔴*")+COUNTIFS('Portfolio &amp; Rebalancing'!C5:C20,"Aktie",'Portfolio &amp; Rebalancing'!N5:N20,"DEFCON 3*",'Portfolio &amp; Rebalancing'!O5:O20,"&lt;&gt;🔴*")</f>
         <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="64" t="s">
+      <c r="A27" s="63" t="s">
         <v>127</v>
       </c>
-      <c r="B27" s="65">
+      <c r="B27" s="71">
         <v>0.5</v>
       </c>
-      <c r="C27" s="64" t="s">
+      <c r="C27" s="69" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="66" t="s">
+      <c r="A28" s="64" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="64" t="s">
+      <c r="A29" s="63" t="s">
         <v>129</v>
       </c>
-      <c r="B29" s="67" t="s">
+      <c r="B29" s="65" t="s">
         <v>130</v>
       </c>
-      <c r="C29" s="64" t="s">
+      <c r="C29" s="63" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="64" t="s">
+      <c r="A30" s="63" t="s">
         <v>132</v>
       </c>
-      <c r="B30" s="67" t="s">
+      <c r="B30" s="65" t="s">
         <v>133</v>
       </c>
-      <c r="C30" s="64" t="s">
+      <c r="C30" s="63" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="64" t="s">
+      <c r="A31" s="63" t="s">
         <v>135</v>
       </c>
-      <c r="B31" s="67" t="s">
+      <c r="B31" s="65" t="s">
         <v>136</v>
       </c>
-      <c r="C31" s="64" t="s">
+      <c r="C31" s="63" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="64" t="s">
+      <c r="A32" s="63" t="s">
         <v>138</v>
       </c>
-      <c r="B32" s="67" t="s">
+      <c r="B32" s="65" t="s">
         <v>136</v>
       </c>
-      <c r="C32" s="64" t="s">
+      <c r="C32" s="63" t="s">
         <v>139</v>
       </c>
     </row>

--- a/03_Tools/Rebalancing_Tool_v3.4.xlsx
+++ b/03_Tools/Rebalancing_Tool_v3.4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tobia\OneDrive\Desktop\Claude Stuff\03_Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8340C460-79F7-476E-B969-07D07C16950D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE8D108-ECB4-417F-B3F5-91C9530772C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio &amp; Rebalancing" sheetId="1" r:id="rId1"/>
@@ -836,21 +836,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1330,44 +1330,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
     </row>
     <row r="2" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="68">
+      <c r="A2" s="71">
         <v>46129</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
     </row>
     <row r="3" spans="1:16" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -1437,26 +1437,26 @@
         <v>0</v>
       </c>
       <c r="F5" s="5">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="G5" s="6">
         <f t="shared" ref="G5:G20" si="0">IF(F$25=0,0,F5/F$25)</f>
-        <v>4.4812648657344099E-2</v>
+        <v>4.304963260382038E-2</v>
       </c>
       <c r="H5" s="6">
         <v>0.05</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I20" si="1">H5*F$25</f>
-        <v>565.68850000000009</v>
+        <v>593.50100000000009</v>
       </c>
       <c r="J5" s="5">
         <f>I5-F5</f>
-        <v>58.68850000000009</v>
+        <v>82.50100000000009</v>
       </c>
       <c r="K5" s="6">
         <f t="shared" ref="K5:K20" si="2">G5-H5</f>
-        <v>-5.1873513426559034E-3</v>
+        <v>-6.9503673961796228E-3</v>
       </c>
       <c r="L5" s="3" t="str">
         <f>IF(C5="Aktie",IF(K5&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K5&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K5&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K5&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -1490,26 +1490,26 @@
         <v>0.7</v>
       </c>
       <c r="F6" s="11">
-        <v>2792.3</v>
+        <v>2960.39</v>
       </c>
       <c r="G6" s="12">
         <f t="shared" si="0"/>
-        <v>0.24680544151065473</v>
+        <v>0.24940059073194482</v>
       </c>
       <c r="H6" s="12">
         <v>0.3</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="1"/>
-        <v>3394.1309999999999</v>
+        <v>3561.0059999999999</v>
       </c>
       <c r="J6" s="11">
         <f>I6-F6</f>
-        <v>601.83099999999968</v>
+        <v>600.61599999999999</v>
       </c>
       <c r="K6" s="12">
         <f t="shared" si="2"/>
-        <v>-5.3194558489345262E-2</v>
+        <v>-5.0599409268055173E-2</v>
       </c>
       <c r="L6" s="9" t="str">
         <f>IF(C6="Aktie",IF(K6&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K6&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K6&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K6&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -1543,26 +1543,26 @@
         <v>0</v>
       </c>
       <c r="F7" s="11">
-        <v>913.01</v>
+        <v>1002.95</v>
       </c>
       <c r="G7" s="12">
         <f t="shared" si="0"/>
-        <v>8.0699006608760823E-2</v>
+        <v>8.4494381643838851E-2</v>
       </c>
       <c r="H7" s="12">
         <v>0.1</v>
       </c>
       <c r="I7" s="11">
         <f t="shared" si="1"/>
-        <v>1131.3770000000002</v>
+        <v>1187.0020000000002</v>
       </c>
       <c r="J7" s="11">
         <f>I7-F7</f>
-        <v>218.36700000000019</v>
+        <v>184.05200000000013</v>
       </c>
       <c r="K7" s="12">
         <f t="shared" si="2"/>
-        <v>-1.9300993391239182E-2</v>
+        <v>-1.5505618356161155E-2</v>
       </c>
       <c r="L7" s="9" t="str">
         <f>IF(C7="Aktie",IF(K7&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K7&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K7&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K7&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -1596,26 +1596,26 @@
         <v>0</v>
       </c>
       <c r="F8" s="11">
-        <v>917.46</v>
+        <v>955.68</v>
       </c>
       <c r="G8" s="12">
         <f t="shared" si="0"/>
-        <v>8.1092332617686239E-2</v>
+        <v>8.0512080013344534E-2</v>
       </c>
       <c r="H8" s="12">
         <v>0.15</v>
       </c>
       <c r="I8" s="11">
         <f t="shared" si="1"/>
-        <v>1697.0654999999999</v>
+        <v>1780.5029999999999</v>
       </c>
       <c r="J8" s="11">
         <f>I8-F8</f>
-        <v>779.60549999999989</v>
+        <v>824.82299999999998</v>
       </c>
       <c r="K8" s="12">
         <f t="shared" si="2"/>
-        <v>-6.8907667382313756E-2</v>
+        <v>-6.9487919986655461E-2</v>
       </c>
       <c r="L8" s="9" t="str">
         <f>IF(C8="Aktie",IF(K8&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K8&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K8&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K8&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -1653,26 +1653,26 @@
       </c>
       <c r="G9" s="12">
         <f t="shared" si="0"/>
-        <v>8.8476255041422966E-2</v>
+        <v>8.4330102223922107E-2</v>
       </c>
       <c r="H9" s="12">
         <v>0.1</v>
       </c>
       <c r="I9" s="11">
         <f t="shared" si="1"/>
-        <v>1131.3770000000002</v>
+        <v>1187.0020000000002</v>
       </c>
       <c r="J9" s="11">
         <f>I9-F9</f>
-        <v>130.37700000000018</v>
+        <v>186.00200000000018</v>
       </c>
       <c r="K9" s="12">
         <f t="shared" si="2"/>
-        <v>-1.152374495857704E-2</v>
+        <v>-1.5669897776077898E-2</v>
       </c>
       <c r="L9" s="9" t="str">
         <f>IF(C9="Aktie",IF(K9&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K9&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K9&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K9&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
-        <v>⚖️ Halten</v>
+        <v>📈 Aufstocken</v>
       </c>
       <c r="M9" s="13" t="str">
         <f>IF(C9="Aktie",IF(G9&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
@@ -1702,26 +1702,26 @@
         <v>0</v>
       </c>
       <c r="F10" s="17">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="G10" s="18">
         <f t="shared" si="0"/>
-        <v>3.2173183651426532E-2</v>
+        <v>3.2687392270611168E-2</v>
       </c>
       <c r="H10" s="18">
         <v>2.7300000000000001E-2</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="1"/>
-        <v>308.86592100000001</v>
+        <v>324.05154600000003</v>
       </c>
       <c r="J10" s="17">
         <f t="shared" ref="J10:J20" si="3">IF(P10=0,0,I10-F10)</f>
-        <v>-55.134078999999986</v>
+        <v>-63.94845399999997</v>
       </c>
       <c r="K10" s="18">
         <f t="shared" si="2"/>
-        <v>4.8731836514265305E-3</v>
+        <v>5.3873922706111667E-3</v>
       </c>
       <c r="L10" s="15" t="str">
         <f>IF(C10="Aktie",IF(K10&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K10&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K10&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K10&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -1759,26 +1759,26 @@
         <v>1</v>
       </c>
       <c r="F11" s="23">
-        <v>356</v>
+        <v>453</v>
       </c>
       <c r="G11" s="24">
         <f t="shared" si="0"/>
-        <v>3.1466080714032542E-2</v>
+        <v>3.8163372934502213E-2</v>
       </c>
       <c r="H11" s="24">
         <v>2.7300000000000001E-2</v>
       </c>
       <c r="I11" s="23">
         <f t="shared" si="1"/>
-        <v>308.86592100000001</v>
+        <v>324.05154600000003</v>
       </c>
       <c r="J11" s="23">
         <f t="shared" si="3"/>
-        <v>-47.134078999999986</v>
+        <v>-128.94845399999997</v>
       </c>
       <c r="K11" s="24">
         <f t="shared" si="2"/>
-        <v>4.1660807140325405E-3</v>
+        <v>1.0863372934502211E-2</v>
       </c>
       <c r="L11" s="21" t="str">
         <f>IF(C11="Aktie",IF(K11&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K11&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K11&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K11&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -1816,18 +1816,18 @@
         <v>1</v>
       </c>
       <c r="F12" s="17">
-        <v>301</v>
+        <v>333</v>
       </c>
       <c r="G12" s="18">
         <f t="shared" si="0"/>
-        <v>2.6604748019448864E-2</v>
+        <v>2.8053870170395668E-2</v>
       </c>
       <c r="H12" s="18">
         <v>2.7300000000000001E-2</v>
       </c>
       <c r="I12" s="17">
         <f t="shared" si="1"/>
-        <v>308.86592100000001</v>
+        <v>324.05154600000003</v>
       </c>
       <c r="J12" s="17">
         <f t="shared" si="3"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="K12" s="18">
         <f t="shared" si="2"/>
-        <v>-6.9525198055113771E-4</v>
+        <v>7.5387017039566656E-4</v>
       </c>
       <c r="L12" s="15" t="str">
         <f>IF(C12="Aktie",IF(K12&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K12&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K12&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K12&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -1873,26 +1873,26 @@
         <v>1</v>
       </c>
       <c r="F13" s="23">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="G13" s="24">
         <f t="shared" si="0"/>
-        <v>3.0935753510987051E-2</v>
+        <v>2.9149066303173876E-2</v>
       </c>
       <c r="H13" s="24">
         <v>2.7300000000000001E-2</v>
       </c>
       <c r="I13" s="23">
         <f t="shared" si="1"/>
-        <v>308.86592100000001</v>
+        <v>324.05154600000003</v>
       </c>
       <c r="J13" s="23">
         <f t="shared" si="3"/>
-        <v>-41.134078999999986</v>
+        <v>-21.94845399999997</v>
       </c>
       <c r="K13" s="24">
         <f t="shared" si="2"/>
-        <v>3.6357535109870498E-3</v>
+        <v>1.8490663031738748E-3</v>
       </c>
       <c r="L13" s="21" t="str">
         <f>IF(C13="Aktie",IF(K13&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K13&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K13&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K13&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -1930,26 +1930,26 @@
         <v>0</v>
       </c>
       <c r="F14" s="17">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="G14" s="18">
         <f t="shared" si="0"/>
-        <v>3.3322225924691772E-2</v>
+        <v>3.3361359121551602E-2</v>
       </c>
       <c r="H14" s="18">
         <v>2.7300000000000001E-2</v>
       </c>
       <c r="I14" s="17">
         <f t="shared" si="1"/>
-        <v>308.86592100000001</v>
+        <v>324.05154600000003</v>
       </c>
       <c r="J14" s="17">
         <f t="shared" si="3"/>
-        <v>-68.134078999999986</v>
+        <v>-71.94845399999997</v>
       </c>
       <c r="K14" s="18">
         <f t="shared" si="2"/>
-        <v>6.0222259246917702E-3</v>
+        <v>6.0613591215516009E-3</v>
       </c>
       <c r="L14" s="15" t="str">
         <f>IF(C14="Aktie",IF(K14&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K14&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K14&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K14&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -1987,26 +1987,26 @@
         <v>1</v>
       </c>
       <c r="F15" s="23">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="G15" s="24">
         <f t="shared" si="0"/>
-        <v>2.8549281097282338E-2</v>
+        <v>2.5442248623001477E-2</v>
       </c>
       <c r="H15" s="24">
         <v>2.7300000000000001E-2</v>
       </c>
       <c r="I15" s="23">
         <f t="shared" si="1"/>
-        <v>308.86592100000001</v>
+        <v>324.05154600000003</v>
       </c>
       <c r="J15" s="23">
         <f t="shared" si="3"/>
-        <v>-14.134078999999986</v>
+        <v>22.05154600000003</v>
       </c>
       <c r="K15" s="24">
         <f t="shared" si="2"/>
-        <v>1.2492810972823364E-3</v>
+        <v>-1.8577513769985239E-3</v>
       </c>
       <c r="L15" s="21" t="str">
         <f>IF(C15="Aktie",IF(K15&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K15&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K15&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K15&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2044,26 +2044,26 @@
         <v>0</v>
       </c>
       <c r="F16" s="17">
-        <v>336</v>
+        <v>390</v>
       </c>
       <c r="G16" s="18">
         <f t="shared" si="0"/>
-        <v>2.969832337054757E-2</v>
+        <v>3.2855883983346275E-2</v>
       </c>
       <c r="H16" s="18">
         <v>2.7300000000000001E-2</v>
       </c>
       <c r="I16" s="17">
         <f t="shared" si="1"/>
-        <v>308.86592100000001</v>
+        <v>324.05154600000003</v>
       </c>
       <c r="J16" s="17">
         <f t="shared" si="3"/>
-        <v>-27.134078999999986</v>
+        <v>-65.94845399999997</v>
       </c>
       <c r="K16" s="18">
         <f t="shared" si="2"/>
-        <v>2.3983233705475691E-3</v>
+        <v>5.5558839833462735E-3</v>
       </c>
       <c r="L16" s="15" t="str">
         <f>IF(C16="Aktie",IF(K16&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K16&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K16&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K16&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2101,26 +2101,26 @@
         <v>1</v>
       </c>
       <c r="F17" s="23">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="G17" s="24">
         <f t="shared" si="0"/>
-        <v>3.5620310471222237E-2</v>
+        <v>3.3024375696081389E-2</v>
       </c>
       <c r="H17" s="24">
         <v>2.7300000000000001E-2</v>
       </c>
       <c r="I17" s="23">
         <f t="shared" si="1"/>
-        <v>308.86592100000001</v>
+        <v>324.05154600000003</v>
       </c>
       <c r="J17" s="23">
         <f t="shared" si="3"/>
-        <v>-94.134078999999986</v>
+        <v>-67.94845399999997</v>
       </c>
       <c r="K17" s="24">
         <f t="shared" si="2"/>
-        <v>8.3203104712222357E-3</v>
+        <v>5.7243756960813873E-3</v>
       </c>
       <c r="L17" s="21" t="str">
         <f>IF(C17="Aktie",IF(K17&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K17&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K17&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K17&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2158,26 +2158,26 @@
         <v>1</v>
       </c>
       <c r="F18" s="17">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="G18" s="18">
         <f t="shared" si="0"/>
-        <v>3.676935274448747E-2</v>
+        <v>3.5972980668945796E-2</v>
       </c>
       <c r="H18" s="18">
         <v>2.7300000000000001E-2</v>
       </c>
       <c r="I18" s="17">
         <f t="shared" si="1"/>
-        <v>308.86592100000001</v>
+        <v>324.05154600000003</v>
       </c>
       <c r="J18" s="17">
         <f t="shared" si="3"/>
-        <v>-107.13407899999999</v>
+        <v>-102.94845399999997</v>
       </c>
       <c r="K18" s="18">
         <f t="shared" si="2"/>
-        <v>9.4693527444874685E-3</v>
+        <v>8.6729806689457949E-3</v>
       </c>
       <c r="L18" s="15" t="str">
         <f>IF(C18="Aktie",IF(K18&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K18&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K18&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K18&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2215,26 +2215,26 @@
         <v>1</v>
       </c>
       <c r="F19" s="23">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="G19" s="24">
         <f t="shared" si="0"/>
-        <v>2.280406973095617E-2</v>
+        <v>2.274638121923973E-2</v>
       </c>
       <c r="H19" s="24">
         <v>2.7300000000000001E-2</v>
       </c>
       <c r="I19" s="23">
         <f t="shared" si="1"/>
-        <v>308.86592100000001</v>
+        <v>324.05154600000003</v>
       </c>
       <c r="J19" s="23">
         <f t="shared" si="3"/>
-        <v>50.865921000000014</v>
+        <v>54.05154600000003</v>
       </c>
       <c r="K19" s="24">
         <f t="shared" si="2"/>
-        <v>-4.495930269043831E-3</v>
+        <v>-4.5536187807602713E-3</v>
       </c>
       <c r="L19" s="21" t="str">
         <f>IF(C19="Aktie",IF(K19&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K19&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K19&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K19&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2272,18 +2272,18 @@
         <v>1</v>
       </c>
       <c r="F20" s="17">
-        <v>249</v>
+        <v>292</v>
       </c>
       <c r="G20" s="18">
         <f t="shared" si="0"/>
-        <v>2.2008578926387933E-2</v>
+        <v>2.4599790059325929E-2</v>
       </c>
       <c r="H20" s="18">
         <v>2.7E-2</v>
       </c>
       <c r="I20" s="17">
         <f t="shared" si="1"/>
-        <v>305.47179</v>
+        <v>320.49054000000001</v>
       </c>
       <c r="J20" s="17">
         <f t="shared" si="3"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="K20" s="18">
         <f t="shared" si="2"/>
-        <v>-4.9914210736120672E-3</v>
+        <v>-2.4002099406740703E-3</v>
       </c>
       <c r="L20" s="15" t="str">
         <f>IF(C20="Aktie",IF(K20&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K20&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K20&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K20&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2322,11 +2322,11 @@
       <c r="E21" s="27"/>
       <c r="F21" s="28">
         <f>SUM(F5:F20)</f>
-        <v>9863.77</v>
+        <v>10420.02</v>
       </c>
       <c r="G21" s="29">
         <f>SUM(G5:G20)</f>
-        <v>0.87183759259733951</v>
+        <v>0.87784350826704582</v>
       </c>
       <c r="H21" s="29">
         <f>SUM(H5:H20)</f>
@@ -2334,15 +2334,15 @@
       </c>
       <c r="I21" s="28">
         <f>SUM(I5:I20)</f>
-        <v>11313.770000000004</v>
+        <v>11870.020000000006</v>
       </c>
       <c r="J21" s="28">
         <f>ROUND(SUM(J5:J20),2)</f>
-        <v>1385.66</v>
+        <v>1430.46</v>
       </c>
       <c r="K21" s="29">
         <f>SUMPRODUCT((C5:C20="Aktie")*ABS(K5:K20))/COUNTIF(C5:C20,"Aktie")</f>
-        <v>4.5742831643531398E-3</v>
+        <v>4.8799892042764408E-3</v>
       </c>
       <c r="L21" s="26" t="s">
         <v>72</v>
@@ -2367,7 +2367,7 @@
     <row r="22" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K22" s="32">
         <f>SUMPRODUCT((C5:C20&lt;&gt;"Aktie")*ABS(K5:K20))/COUNTIF(C5:C20,"&lt;&gt;Aktie")</f>
-        <v>3.1622863112826229E-2</v>
+        <v>3.1642642556625869E-2</v>
       </c>
       <c r="L22" s="33" t="s">
         <v>73</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="F25" s="41">
         <f>F21 + F24</f>
-        <v>11313.77</v>
+        <v>11870.02</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="F26" s="42">
         <f>F24 - MIN(F23, SUMIFS(J5:J20, D5:D20, "Scalable", J5:J20, "&gt;0"))</f>
-        <v>1210.0685789999998</v>
+        <v>1105.3939079999996</v>
       </c>
     </row>
   </sheetData>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C4" s="47">
         <f>'Portfolio &amp; Rebalancing'!F5</f>
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="D4" s="48">
         <f>'Portfolio &amp; Rebalancing'!E5</f>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="C5" s="47">
         <f>'Portfolio &amp; Rebalancing'!F6</f>
-        <v>2792.3</v>
+        <v>2960.39</v>
       </c>
       <c r="D5" s="48">
         <f>'Portfolio &amp; Rebalancing'!E6</f>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="E5" s="47">
         <f t="shared" si="0"/>
-        <v>1954.61</v>
+        <v>2072.2729999999997</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="C6" s="47">
         <f>'Portfolio &amp; Rebalancing'!F7</f>
-        <v>913.01</v>
+        <v>1002.95</v>
       </c>
       <c r="D6" s="48">
         <f>'Portfolio &amp; Rebalancing'!E7</f>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="C7" s="47">
         <f>'Portfolio &amp; Rebalancing'!F8</f>
-        <v>917.46</v>
+        <v>955.68</v>
       </c>
       <c r="D7" s="48">
         <f>'Portfolio &amp; Rebalancing'!E8</f>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="C9" s="47">
         <f>'Portfolio &amp; Rebalancing'!F10</f>
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="D9" s="48">
         <f>'Portfolio &amp; Rebalancing'!E10</f>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="C10" s="47">
         <f>'Portfolio &amp; Rebalancing'!F11</f>
-        <v>356</v>
+        <v>453</v>
       </c>
       <c r="D10" s="48">
         <f>'Portfolio &amp; Rebalancing'!E11</f>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="E10" s="47">
         <f t="shared" si="0"/>
-        <v>356</v>
+        <v>453</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="C11" s="47">
         <f>'Portfolio &amp; Rebalancing'!F12</f>
-        <v>301</v>
+        <v>333</v>
       </c>
       <c r="D11" s="48">
         <f>'Portfolio &amp; Rebalancing'!E12</f>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="E11" s="47">
         <f t="shared" si="0"/>
-        <v>301</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="C12" s="47">
         <f>'Portfolio &amp; Rebalancing'!F13</f>
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D12" s="48">
         <f>'Portfolio &amp; Rebalancing'!E13</f>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="E12" s="47">
         <f t="shared" si="0"/>
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="C13" s="47">
         <f>'Portfolio &amp; Rebalancing'!F14</f>
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="D13" s="48">
         <f>'Portfolio &amp; Rebalancing'!E14</f>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C14" s="47">
         <f>'Portfolio &amp; Rebalancing'!F15</f>
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="D14" s="48">
         <f>'Portfolio &amp; Rebalancing'!E15</f>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="E14" s="47">
         <f t="shared" si="0"/>
-        <v>323</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C15" s="47">
         <f>'Portfolio &amp; Rebalancing'!F16</f>
-        <v>336</v>
+        <v>390</v>
       </c>
       <c r="D15" s="48">
         <f>'Portfolio &amp; Rebalancing'!E16</f>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="C16" s="47">
         <f>'Portfolio &amp; Rebalancing'!F17</f>
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="D16" s="48">
         <f>'Portfolio &amp; Rebalancing'!E17</f>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="E16" s="47">
         <f t="shared" si="0"/>
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="C17" s="47">
         <f>'Portfolio &amp; Rebalancing'!F18</f>
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="D17" s="48">
         <f>'Portfolio &amp; Rebalancing'!E18</f>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="E17" s="47">
         <f t="shared" si="0"/>
-        <v>416</v>
+        <v>427</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C18" s="47">
         <f>'Portfolio &amp; Rebalancing'!F19</f>
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="D18" s="48">
         <f>'Portfolio &amp; Rebalancing'!E19</f>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="E18" s="47">
         <f t="shared" si="0"/>
-        <v>258</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="C19" s="47">
         <f>'Portfolio &amp; Rebalancing'!F20</f>
-        <v>249</v>
+        <v>292</v>
       </c>
       <c r="D19" s="48">
         <f>'Portfolio &amp; Rebalancing'!E20</f>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="E19" s="47">
         <f t="shared" si="0"/>
-        <v>249</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2873,11 +2873,11 @@
       </c>
       <c r="C20" s="50">
         <f>'Portfolio &amp; Rebalancing'!F21</f>
-        <v>9863.77</v>
+        <v>10420.02</v>
       </c>
       <c r="E20" s="50">
         <f>SUM(E4:E19)</f>
-        <v>5281.28</v>
+        <v>5557.9429999999993</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B22" s="51">
         <f>IF('Portfolio &amp; Rebalancing'!F25=0,0,E20/'Portfolio &amp; Rebalancing'!F25)</f>
-        <v>0.46680107515001629</v>
+        <v>0.46823366767705521</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="B23" s="51">
         <f>SUMPRODUCT('Portfolio &amp; Rebalancing'!$E$5:$E$20,'Portfolio &amp; Rebalancing'!$I$5:$I$20)/SUM('Portfolio &amp; Rebalancing'!$I$5:$I$20)</f>
-        <v>0.49509999999999971</v>
+        <v>0.4950999999999996</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -3157,7 +3157,7 @@
       <c r="A25" s="60" t="s">
         <v>125</v>
       </c>
-      <c r="B25" s="70">
+      <c r="B25" s="67">
         <f>B4*B6</f>
         <v>285</v>
       </c>
@@ -3178,10 +3178,10 @@
       <c r="A27" s="63" t="s">
         <v>127</v>
       </c>
-      <c r="B27" s="71">
+      <c r="B27" s="68">
         <v>0.5</v>
       </c>
-      <c r="C27" s="69" t="s">
+      <c r="C27" s="66" t="s">
         <v>98</v>
       </c>
     </row>

--- a/03_Tools/Rebalancing_Tool_v3.4.xlsx
+++ b/03_Tools/Rebalancing_Tool_v3.4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tobia\OneDrive\Desktop\Claude Stuff\03_Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157CC840-8191-4CF5-BC19-1978E47EAC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB7FC57-15D8-4DED-B222-8C170299C3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -856,7 +856,7 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="18">
     <dxf>
       <fill>
         <patternFill>
@@ -886,8 +886,20 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF843C0C"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE4D6"/>
+          <bgColor rgb="FFFCE4D6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -896,7 +908,8 @@
         <color rgb="FF9C5700"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
@@ -906,7 +919,8 @@
         <color rgb="FF9C5700"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
@@ -916,7 +930,19 @@
         <color rgb="FF276221"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF276221"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
@@ -926,18 +952,20 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF7E3700"/>
+        <color rgb="FF843C0C"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCC88"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE4D6"/>
+          <bgColor rgb="FFFCE4D6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -946,7 +974,8 @@
         <color rgb="FF9C5700"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
@@ -956,7 +985,8 @@
         <color rgb="FF276221"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
@@ -2426,49 +2456,55 @@
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <conditionalFormatting sqref="L5:L20">
-    <cfRule type="expression" dxfId="15" priority="2">
+    <cfRule type="expression" dxfId="17" priority="2">
       <formula>NOT(ISERROR(SEARCH("Reduzieren",L5)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="3">
+    <cfRule type="expression" dxfId="16" priority="3">
       <formula>NOT(ISERROR(SEARCH("Aufstocken",L5)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="4">
+    <cfRule type="expression" dxfId="15" priority="4">
       <formula>NOT(ISERROR(SEARCH("Halten",L5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M20">
-    <cfRule type="expression" dxfId="12" priority="5">
+    <cfRule type="expression" dxfId="14" priority="5">
       <formula>NOT(ISERROR(SEARCH("ÜBER CAP",M5)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="6">
+    <cfRule type="expression" dxfId="13" priority="6">
       <formula>NOT(ISERROR(SEARCH("OK",M5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5:N20">
-    <cfRule type="expression" dxfId="10" priority="7">
+    <cfRule type="expression" dxfId="12" priority="16" stopIfTrue="1">
       <formula>LEFT(N5,8)="DEFCON 4"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="8">
+    <cfRule type="expression" dxfId="11" priority="16" stopIfTrue="1">
       <formula>LEFT(N5,8)="DEFCON 3"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="9">
+    <cfRule type="expression" dxfId="10" priority="17" stopIfTrue="1">
       <formula>LEFT(N5,8)="DEFCON 2"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="10">
+    <cfRule type="expression" dxfId="9" priority="18" stopIfTrue="1">
       <formula>LEFT(N5,8)="DEFCON 1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O5:O20">
-    <cfRule type="expression" dxfId="6" priority="11">
+    <cfRule type="expression" dxfId="8" priority="19" stopIfTrue="1">
       <formula>O5="✅ Clean"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="12">
+    <cfRule type="expression" dxfId="7" priority="20" stopIfTrue="1">
+      <formula>LEFT(O5,1)="🟢"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="21" stopIfTrue="1">
       <formula>LEFT(O5,1)="🟡"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="13">
+    <cfRule type="expression" dxfId="5" priority="22" stopIfTrue="1">
       <formula>LEFT(O5,2)="🚩"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="14">
+    <cfRule type="expression" dxfId="4" priority="23" stopIfTrue="1">
+      <formula>LEFT(O5,1)="🟠"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="24" stopIfTrue="1">
       <formula>LEFT(O5,2)="🔴"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/03_Tools/Rebalancing_Tool_v3.4.xlsx
+++ b/03_Tools/Rebalancing_Tool_v3.4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tobia\OneDrive\Desktop\Claude Stuff\03_Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB7FC57-15D8-4DED-B222-8C170299C3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CB7F22-2BA9-4B90-B318-C26D0D2EB6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2492,20 +2492,20 @@
     <cfRule type="expression" dxfId="8" priority="19" stopIfTrue="1">
       <formula>O5="✅ Clean"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="19" stopIfTrue="1">
       <formula>LEFT(O5,1)="🟢"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="19" stopIfTrue="1">
       <formula>LEFT(O5,1)="🟡"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="22" stopIfTrue="1">
-      <formula>LEFT(O5,2)="🚩"</formula>
+    <cfRule type="expression" dxfId="5" priority="20" stopIfTrue="1">
+      <formula>LEFT(O5,1)="🚩"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="21" stopIfTrue="1">
       <formula>LEFT(O5,1)="🟠"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="24" stopIfTrue="1">
-      <formula>LEFT(O5,2)="🔴"</formula>
+    <cfRule type="expression" dxfId="3" priority="22" stopIfTrue="1">
+      <formula>LEFT(O5,1)="🔴"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5:P20">

--- a/03_Tools/Rebalancing_Tool_v3.4.xlsx
+++ b/03_Tools/Rebalancing_Tool_v3.4.xlsx
@@ -1987,12 +1987,12 @@
       </c>
       <c r="N18" s="15" t="inlineStr">
         <is>
-          <t>DEFCON 2 (63)</t>
+          <t>DEFCON 2 (64)</t>
         </is>
       </c>
       <c r="O18" s="15" t="inlineStr">
         <is>
-          <t>🟠 DEFCON 2 (63) | Forward 18.04. nach Advisor-Review | Q2 FY26 28.04.</t>
+          <t>🟠 DEFCON 2 (64) | Q2 Beat-Cascade D3 (mittags) → Codex-Review-Revert D2 (spätabends, HIGH-1+2 28.04.) | Q3 ~Ende Juli ROIC-Verify</t>
         </is>
       </c>
       <c r="P18" s="17">

--- a/03_Tools/Rebalancing_Tool_v3.4.xlsx
+++ b/03_Tools/Rebalancing_Tool_v3.4.xlsx
@@ -978,7 +978,7 @@
     </row>
     <row r="2" ht="13.5" customHeight="1" s="70">
       <c r="A2" s="71" t="n">
-        <v>46140</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="3" ht="3.75" customHeight="1" s="70"/>
@@ -2125,12 +2125,12 @@
       </c>
       <c r="N20" s="15" t="inlineStr">
         <is>
-          <t>DEFCON 2 (63)</t>
+          <t>DEFCON 2 (61)</t>
         </is>
       </c>
       <c r="O20" s="15" t="inlineStr">
         <is>
-          <t>🔴 FLAG: Score 63 (DEFCON 2 seit 18.04.) | Tariff-Check: CN 14.7% Risk-Map</t>
+          <t>🔴 FLAG: Score 61 (DEFCON 2, Q1 FY26 Tag-+1 Vollanalyse 30.04.) | CommScope-NL 1,6x | China-Tax-ETR 27% strukturell</t>
         </is>
       </c>
       <c r="P20" s="17">

--- a/03_Tools/Rebalancing_Tool_v3.4.xlsx
+++ b/03_Tools/Rebalancing_Tool_v3.4.xlsx
@@ -1573,12 +1573,12 @@
       </c>
       <c r="N12" s="15" t="inlineStr">
         <is>
-          <t>DEFCON 2 (59)</t>
+          <t>DEFCON 2 (50)</t>
         </is>
       </c>
       <c r="O12" s="15" t="inlineStr">
         <is>
-          <t>🔴 FLAG: CapEx/OCF &gt;60% | Score 59 | DEFCON 2 | Re-Check 29.04.</t>
+          <t>🔴 FLAG: CapEx/OCF aktiv | Score 50 | DEFCON 2 | Bull-Case Trigger B FAIL (CY26 $190B) | Re-Check Q4 FY26 ~Juli</t>
         </is>
       </c>
       <c r="P12" s="17">

--- a/03_Tools/Rebalancing_Tool_v3.4.xlsx
+++ b/03_Tools/Rebalancing_Tool_v3.4.xlsx
@@ -1504,12 +1504,12 @@
       </c>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t>DEFCON 4 (84) | Insider-Check Q3</t>
+          <t>DEFCON 2 (53) | Vollanalyse 30.04.</t>
         </is>
       </c>
       <c r="O11" s="21" t="inlineStr">
         <is>
-          <t>🔴 FLAG: Insider-Selling 90d $106M+ | Aktiviert 27.04.2026 | Re-Eval Q3 FY26</t>
+          <t>🔴 FLAG: Insider-Selling 90d $106M+ | Aktiviert 27.04.2026 | Vollanalyse 30.04. Score 84→53 (D4→D2) | Re-Eval Q3 FY26</t>
         </is>
       </c>
       <c r="P11" s="23">

--- a/03_Tools/Rebalancing_Tool_v3.4.xlsx
+++ b/03_Tools/Rebalancing_Tool_v3.4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tobia\OneDrive\Desktop\Claude Stuff\03_Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3F8EE2-41B4-48A0-9DDE-896F929C3E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59FF7EA-2373-4173-8164-449484EA10F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1475,26 +1475,26 @@
         <v>0</v>
       </c>
       <c r="F5" s="5">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="G5" s="6">
         <f t="shared" ref="G5:G20" si="0">IF(F$25=0,0,F5/F$25)</f>
-        <v>4.2834489407838426E-2</v>
+        <v>4.221839532376867E-2</v>
       </c>
       <c r="H5" s="6">
         <v>0.05</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I20" si="1">H5*F$25</f>
-        <v>693.36649999999997</v>
+        <v>689.27300000000002</v>
       </c>
       <c r="J5" s="5">
         <f>I5-F5</f>
-        <v>99.366499999999974</v>
+        <v>107.27300000000002</v>
       </c>
       <c r="K5" s="6">
         <f t="shared" ref="K5:K20" si="2">G5-H5</f>
-        <v>-7.1655105921615767E-3</v>
+        <v>-7.7816046762313323E-3</v>
       </c>
       <c r="L5" s="3" t="str">
         <f>IF(C5="Aktie",IF(K5&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K5&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K5&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K5&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -1528,26 +1528,26 @@
         <v>0.7</v>
       </c>
       <c r="F6" s="11">
-        <v>3632.72</v>
+        <v>3675.72</v>
       </c>
       <c r="G6" s="12">
         <f t="shared" si="0"/>
-        <v>0.26196246862229428</v>
+        <v>0.26663745714687792</v>
       </c>
       <c r="H6" s="12">
         <v>0.3</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="1"/>
-        <v>4160.1989999999996</v>
+        <v>4135.6379999999999</v>
       </c>
       <c r="J6" s="11">
         <f>I6-F6</f>
-        <v>527.47899999999981</v>
+        <v>459.91800000000012</v>
       </c>
       <c r="K6" s="12">
         <f t="shared" si="2"/>
-        <v>-3.8037531377705713E-2</v>
+        <v>-3.3362542853122068E-2</v>
       </c>
       <c r="L6" s="9" t="str">
         <f>IF(C6="Aktie",IF(K6&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K6&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K6&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K6&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -1581,26 +1581,26 @@
         <v>0</v>
       </c>
       <c r="F7" s="11">
-        <v>1246.4100000000001</v>
+        <v>1228.3</v>
       </c>
       <c r="G7" s="12">
         <f t="shared" si="0"/>
-        <v>8.9881036940780978E-2</v>
+        <v>8.9101125388634114E-2</v>
       </c>
       <c r="H7" s="12">
         <v>0.1</v>
       </c>
       <c r="I7" s="11">
         <f t="shared" si="1"/>
-        <v>1386.7329999999999</v>
+        <v>1378.546</v>
       </c>
       <c r="J7" s="11">
         <f>I7-F7</f>
-        <v>140.32299999999987</v>
+        <v>150.24600000000009</v>
       </c>
       <c r="K7" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0118963059219027E-2</v>
+        <v>-1.0898874611365891E-2</v>
       </c>
       <c r="L7" s="9" t="str">
         <f>IF(C7="Aktie",IF(K7&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K7&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K7&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K7&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -1634,26 +1634,26 @@
         <v>0</v>
       </c>
       <c r="F8" s="11">
-        <v>1800.2</v>
+        <v>1769.44</v>
       </c>
       <c r="G8" s="12">
         <f t="shared" si="0"/>
-        <v>0.12981590544106186</v>
+        <v>0.12835552821596088</v>
       </c>
       <c r="H8" s="12">
         <v>0.15</v>
       </c>
       <c r="I8" s="11">
         <f t="shared" si="1"/>
-        <v>2080.0994999999998</v>
+        <v>2067.819</v>
       </c>
       <c r="J8" s="11">
         <f>I8-F8</f>
-        <v>279.89949999999976</v>
+        <v>298.37899999999991</v>
       </c>
       <c r="K8" s="12">
         <f t="shared" si="2"/>
-        <v>-2.0184094558938132E-2</v>
+        <v>-2.164447178403911E-2</v>
       </c>
       <c r="L8" s="9" t="str">
         <f>IF(C8="Aktie",IF(K8&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K8&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K8&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K8&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -1687,26 +1687,26 @@
         <v>0.67</v>
       </c>
       <c r="F9" s="11">
-        <v>1194</v>
+        <v>1187</v>
       </c>
       <c r="G9" s="12">
         <f t="shared" si="0"/>
-        <v>8.6101650425857046E-2</v>
+        <v>8.6105215205005858E-2</v>
       </c>
       <c r="H9" s="12">
         <v>0.1</v>
       </c>
       <c r="I9" s="11">
         <f t="shared" si="1"/>
-        <v>1386.7329999999999</v>
+        <v>1378.546</v>
       </c>
       <c r="J9" s="11">
         <f>I9-F9</f>
-        <v>192.73299999999995</v>
+        <v>191.54600000000005</v>
       </c>
       <c r="K9" s="12">
         <f t="shared" si="2"/>
-        <v>-1.389834957414296E-2</v>
+        <v>-1.3894784794994147E-2</v>
       </c>
       <c r="L9" s="9" t="str">
         <f>IF(C9="Aktie",IF(K9&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K9&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K9&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K9&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -1740,26 +1740,26 @@
         <v>0</v>
       </c>
       <c r="F10" s="17">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="G10" s="18">
         <f t="shared" si="0"/>
-        <v>3.1657139478183619E-2</v>
+        <v>3.2135307780806734E-2</v>
       </c>
       <c r="H10" s="18">
         <v>2.7300000000000001E-2</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="1"/>
-        <v>378.57810899999998</v>
+        <v>376.34305799999998</v>
       </c>
       <c r="J10" s="17">
         <f t="shared" ref="J10:J20" si="3">IF(P10=0,0,I10-F10)</f>
-        <v>-60.421891000000016</v>
+        <v>-66.656942000000015</v>
       </c>
       <c r="K10" s="18">
         <f t="shared" si="2"/>
-        <v>4.3571394781836172E-3</v>
+        <v>4.8353077808067323E-3</v>
       </c>
       <c r="L10" s="15" t="str">
         <f>IF(C10="Aktie",IF(K10&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K10&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K10&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K10&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -1797,18 +1797,18 @@
         <v>1</v>
       </c>
       <c r="F11" s="23">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="G11" s="24">
         <f t="shared" si="0"/>
-        <v>3.6488639125195697E-2</v>
+        <v>3.7430742245815524E-2</v>
       </c>
       <c r="H11" s="24">
         <v>2.7300000000000001E-2</v>
       </c>
       <c r="I11" s="23">
         <f t="shared" si="1"/>
-        <v>378.57810899999998</v>
+        <v>376.34305799999998</v>
       </c>
       <c r="J11" s="23">
         <f t="shared" si="3"/>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="K11" s="24">
         <f t="shared" si="2"/>
-        <v>9.188639125195696E-3</v>
+        <v>1.0130742245815522E-2</v>
       </c>
       <c r="L11" s="21" t="str">
         <f>IF(C11="Aktie",IF(K11&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K11&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K11&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K11&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -1854,18 +1854,18 @@
         <v>1</v>
       </c>
       <c r="F12" s="17">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="G12" s="18">
         <f t="shared" si="0"/>
-        <v>2.7114087571291665E-2</v>
+        <v>2.8073056684361639E-2</v>
       </c>
       <c r="H12" s="18">
         <v>2.7300000000000001E-2</v>
       </c>
       <c r="I12" s="17">
         <f t="shared" si="1"/>
-        <v>378.57810899999998</v>
+        <v>376.34305799999998</v>
       </c>
       <c r="J12" s="17">
         <f t="shared" si="3"/>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="K12" s="18">
         <f t="shared" si="2"/>
-        <v>-1.8591242870833607E-4</v>
+        <v>7.7305668436163794E-4</v>
       </c>
       <c r="L12" s="15" t="str">
         <f>IF(C12="Aktie",IF(K12&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K12&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K12&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K12&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -1911,26 +1911,26 @@
         <v>1</v>
       </c>
       <c r="F13" s="23">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="G13" s="24">
         <f t="shared" si="0"/>
-        <v>2.7690983051531913E-2</v>
+        <v>2.9306240052925332E-2</v>
       </c>
       <c r="H13" s="24">
         <v>2.7300000000000001E-2</v>
       </c>
       <c r="I13" s="23">
         <f t="shared" si="1"/>
-        <v>378.57810899999998</v>
+        <v>376.34305799999998</v>
       </c>
       <c r="J13" s="23">
         <f t="shared" si="3"/>
-        <v>-5.4218910000000164</v>
+        <v>-27.656942000000015</v>
       </c>
       <c r="K13" s="24">
         <f t="shared" si="2"/>
-        <v>3.9098305153191168E-4</v>
+        <v>2.0062400529253302E-3</v>
       </c>
       <c r="L13" s="21" t="str">
         <f>IF(C13="Aktie",IF(K13&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K13&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K13&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K13&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -1968,26 +1968,26 @@
         <v>0</v>
       </c>
       <c r="F14" s="17">
-        <v>420</v>
+        <v>394</v>
       </c>
       <c r="G14" s="18">
         <f t="shared" si="0"/>
-        <v>3.028701271261303E-2</v>
+        <v>2.8580838071417279E-2</v>
       </c>
       <c r="H14" s="18">
         <v>2.7300000000000001E-2</v>
       </c>
       <c r="I14" s="17">
         <f t="shared" si="1"/>
-        <v>378.57810899999998</v>
+        <v>376.34305799999998</v>
       </c>
       <c r="J14" s="17">
         <f t="shared" si="3"/>
-        <v>-41.421891000000016</v>
+        <v>-17.656942000000015</v>
       </c>
       <c r="K14" s="18">
         <f t="shared" si="2"/>
-        <v>2.9870127126130283E-3</v>
+        <v>1.2808380714172778E-3</v>
       </c>
       <c r="L14" s="15" t="str">
         <f>IF(C14="Aktie",IF(K14&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K14&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K14&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K14&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2025,26 +2025,26 @@
         <v>1</v>
       </c>
       <c r="F15" s="23">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="G15" s="24">
         <f t="shared" si="0"/>
-        <v>2.466228178027061E-2</v>
+        <v>2.3357943804559297E-2</v>
       </c>
       <c r="H15" s="24">
         <v>2.7300000000000001E-2</v>
       </c>
       <c r="I15" s="23">
         <f t="shared" si="1"/>
-        <v>378.57810899999998</v>
+        <v>376.34305799999998</v>
       </c>
       <c r="J15" s="23">
         <f t="shared" si="3"/>
-        <v>36.578108999999984</v>
+        <v>54.343057999999985</v>
       </c>
       <c r="K15" s="24">
         <f t="shared" si="2"/>
-        <v>-2.6377182197293916E-3</v>
+        <v>-3.9420561954407046E-3</v>
       </c>
       <c r="L15" s="21" t="str">
         <f>IF(C15="Aktie",IF(K15&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K15&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K15&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K15&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2082,26 +2082,26 @@
         <v>0</v>
       </c>
       <c r="F16" s="17">
-        <v>434</v>
+        <v>407</v>
       </c>
       <c r="G16" s="18">
         <f t="shared" si="0"/>
-        <v>3.1296579803033464E-2</v>
+        <v>2.9523860647377748E-2</v>
       </c>
       <c r="H16" s="18">
         <v>2.7300000000000001E-2</v>
       </c>
       <c r="I16" s="17">
         <f t="shared" si="1"/>
-        <v>378.57810899999998</v>
+        <v>376.34305799999998</v>
       </c>
       <c r="J16" s="17">
         <f t="shared" si="3"/>
-        <v>-55.421891000000016</v>
+        <v>-30.656942000000015</v>
       </c>
       <c r="K16" s="18">
         <f t="shared" si="2"/>
-        <v>3.9965798030334627E-3</v>
+        <v>2.2238606473777463E-3</v>
       </c>
       <c r="L16" s="15" t="str">
         <f>IF(C16="Aktie",IF(K16&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K16&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K16&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K16&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2139,26 +2139,26 @@
         <v>1</v>
       </c>
       <c r="F17" s="23">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="G17" s="24">
         <f t="shared" si="0"/>
-        <v>3.0575460452733155E-2</v>
+        <v>3.1917687186354321E-2</v>
       </c>
       <c r="H17" s="24">
         <v>2.7300000000000001E-2</v>
       </c>
       <c r="I17" s="23">
         <f t="shared" si="1"/>
-        <v>378.57810899999998</v>
+        <v>376.34305799999998</v>
       </c>
       <c r="J17" s="23">
         <f t="shared" si="3"/>
-        <v>-45.421891000000016</v>
+        <v>-63.656942000000015</v>
       </c>
       <c r="K17" s="24">
         <f t="shared" si="2"/>
-        <v>3.2754604527331539E-3</v>
+        <v>4.6176871863543197E-3</v>
       </c>
       <c r="L17" s="21" t="str">
         <f>IF(C17="Aktie",IF(K17&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K17&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K17&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K17&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2196,26 +2196,26 @@
         <v>1</v>
       </c>
       <c r="F18" s="17">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="G18" s="18">
         <f t="shared" si="0"/>
-        <v>3.4036833334174642E-2</v>
+        <v>3.4674214716084922E-2</v>
       </c>
       <c r="H18" s="18">
         <v>2.7300000000000001E-2</v>
       </c>
       <c r="I18" s="17">
         <f t="shared" si="1"/>
-        <v>378.57810899999998</v>
+        <v>376.34305799999998</v>
       </c>
       <c r="J18" s="17">
         <f t="shared" si="3"/>
-        <v>-93.421891000000016</v>
+        <v>-101.65694200000002</v>
       </c>
       <c r="K18" s="18">
         <f t="shared" si="2"/>
-        <v>6.7368333341746404E-3</v>
+        <v>7.374214716084921E-3</v>
       </c>
       <c r="L18" s="15" t="str">
         <f>IF(C18="Aktie",IF(K18&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K18&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K18&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K18&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2253,26 +2253,26 @@
         <v>1</v>
       </c>
       <c r="F19" s="23">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="G19" s="24">
         <f t="shared" si="0"/>
-        <v>2.3436378884760082E-2</v>
+        <v>2.2124760435995608E-2</v>
       </c>
       <c r="H19" s="24">
         <v>2.7300000000000001E-2</v>
       </c>
       <c r="I19" s="23">
         <f t="shared" si="1"/>
-        <v>378.57810899999998</v>
+        <v>376.34305799999998</v>
       </c>
       <c r="J19" s="23">
         <f t="shared" si="3"/>
-        <v>53.578108999999984</v>
+        <v>71.343057999999985</v>
       </c>
       <c r="K19" s="24">
         <f t="shared" si="2"/>
-        <v>-3.8636211152399194E-3</v>
+        <v>-5.1752395640043934E-3</v>
       </c>
       <c r="L19" s="21" t="str">
         <f>IF(C19="Aktie",IF(K19&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K19&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K19&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K19&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2310,18 +2310,18 @@
         <v>1</v>
       </c>
       <c r="F20" s="17">
-        <v>328</v>
+        <v>297</v>
       </c>
       <c r="G20" s="18">
         <f t="shared" si="0"/>
-        <v>2.3652714689850175E-2</v>
+        <v>2.1544438850789167E-2</v>
       </c>
       <c r="H20" s="18">
         <v>2.7E-2</v>
       </c>
       <c r="I20" s="17">
         <f t="shared" si="1"/>
-        <v>374.41790999999995</v>
+        <v>372.20741999999996</v>
       </c>
       <c r="J20" s="17">
         <f t="shared" si="3"/>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="K20" s="18">
         <f t="shared" si="2"/>
-        <v>-3.3472853101498244E-3</v>
+        <v>-5.4555611492108323E-3</v>
       </c>
       <c r="L20" s="15" t="str">
         <f>IF(C20="Aktie",IF(K20&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K20&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K20&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K20&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2360,11 +2360,11 @@
       <c r="E21" s="27"/>
       <c r="F21" s="28">
         <f>SUM(F5:F20)</f>
-        <v>12917.329999999998</v>
+        <v>12835.46</v>
       </c>
       <c r="G21" s="29">
         <f>SUM(G5:G20)</f>
-        <v>0.93149366172147074</v>
+        <v>0.93108681175673524</v>
       </c>
       <c r="H21" s="29">
         <f>SUM(H5:H20)</f>
@@ -2372,15 +2372,15 @@
       </c>
       <c r="I21" s="28">
         <f>SUM(I5:I20)</f>
-        <v>13867.33</v>
+        <v>13785.460000000005</v>
       </c>
       <c r="J21" s="28">
         <f>ROUND(SUM(J5:J20),2)</f>
-        <v>1028.43</v>
+        <v>1025.1099999999999</v>
       </c>
       <c r="K21" s="29">
         <f>SUMPRODUCT((C5:C20="Aktie")*ABS(K5:K20))/COUNTIF(C5:C20,"Aktie")</f>
-        <v>3.7242895482993625E-3</v>
+        <v>4.3468003903454015E-3</v>
       </c>
       <c r="L21" s="26" t="s">
         <v>74</v>
@@ -2405,7 +2405,7 @@
     <row r="22" spans="1:16" ht="16.5" customHeight="1">
       <c r="K22" s="32">
         <f>SUMPRODUCT((C5:C20&lt;&gt;"Aktie")*ABS(K5:K20))/COUNTIF(C5:C20,"&lt;&gt;Aktie")</f>
-        <v>1.7880889832433484E-2</v>
+        <v>1.7516455743950509E-2</v>
       </c>
       <c r="L22" s="33" t="s">
         <v>75</v>
@@ -2429,7 +2429,7 @@
         <v>79</v>
       </c>
       <c r="F23" s="38">
-        <v>1291.77</v>
+        <v>1297.78</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="16.5" customHeight="1">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="F25" s="41">
         <f>F21 + F24</f>
-        <v>13867.329999999998</v>
+        <v>13785.46</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="16.5" customHeight="1">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="F26" s="42">
         <f>F24 - MIN(F23, SUMIFS(J5:J20, D5:D20, "Scalable", J5:J20, "&gt;0"))</f>
-        <v>567.74428200000011</v>
+        <v>525.49488399999996</v>
       </c>
     </row>
   </sheetData>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="C4" s="47">
         <f>'Portfolio &amp; Rebalancing'!F5</f>
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="D4" s="48">
         <f>'Portfolio &amp; Rebalancing'!E5</f>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="C5" s="47">
         <f>'Portfolio &amp; Rebalancing'!F6</f>
-        <v>3632.72</v>
+        <v>3675.72</v>
       </c>
       <c r="D5" s="48">
         <f>'Portfolio &amp; Rebalancing'!E6</f>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="E5" s="47">
         <f t="shared" si="0"/>
-        <v>2542.9039999999995</v>
+        <v>2573.0039999999999</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="C6" s="47">
         <f>'Portfolio &amp; Rebalancing'!F7</f>
-        <v>1246.4100000000001</v>
+        <v>1228.3</v>
       </c>
       <c r="D6" s="48">
         <f>'Portfolio &amp; Rebalancing'!E7</f>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="C7" s="47">
         <f>'Portfolio &amp; Rebalancing'!F8</f>
-        <v>1800.2</v>
+        <v>1769.44</v>
       </c>
       <c r="D7" s="48">
         <f>'Portfolio &amp; Rebalancing'!E8</f>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="C8" s="47">
         <f>'Portfolio &amp; Rebalancing'!F9</f>
-        <v>1194</v>
+        <v>1187</v>
       </c>
       <c r="D8" s="48">
         <f>'Portfolio &amp; Rebalancing'!E9</f>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="E8" s="47">
         <f t="shared" si="0"/>
-        <v>799.98</v>
+        <v>795.29000000000008</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="C9" s="47">
         <f>'Portfolio &amp; Rebalancing'!F10</f>
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="D9" s="48">
         <f>'Portfolio &amp; Rebalancing'!E10</f>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="C10" s="47">
         <f>'Portfolio &amp; Rebalancing'!F11</f>
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="D10" s="48">
         <f>'Portfolio &amp; Rebalancing'!E11</f>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="E10" s="47">
         <f t="shared" si="0"/>
-        <v>506</v>
+        <v>516</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="C11" s="47">
         <f>'Portfolio &amp; Rebalancing'!F12</f>
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="D11" s="48">
         <f>'Portfolio &amp; Rebalancing'!E12</f>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="E11" s="47">
         <f t="shared" si="0"/>
-        <v>376</v>
+        <v>387</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C12" s="47">
         <f>'Portfolio &amp; Rebalancing'!F13</f>
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="D12" s="48">
         <f>'Portfolio &amp; Rebalancing'!E13</f>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="E12" s="47">
         <f t="shared" si="0"/>
-        <v>384</v>
+        <v>404</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C13" s="47">
         <f>'Portfolio &amp; Rebalancing'!F14</f>
-        <v>420</v>
+        <v>394</v>
       </c>
       <c r="D13" s="48">
         <f>'Portfolio &amp; Rebalancing'!E14</f>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="C14" s="47">
         <f>'Portfolio &amp; Rebalancing'!F15</f>
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="D14" s="48">
         <f>'Portfolio &amp; Rebalancing'!E15</f>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="E14" s="47">
         <f t="shared" si="0"/>
-        <v>342</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="C15" s="47">
         <f>'Portfolio &amp; Rebalancing'!F16</f>
-        <v>434</v>
+        <v>407</v>
       </c>
       <c r="D15" s="48">
         <f>'Portfolio &amp; Rebalancing'!E16</f>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C16" s="47">
         <f>'Portfolio &amp; Rebalancing'!F17</f>
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="D16" s="48">
         <f>'Portfolio &amp; Rebalancing'!E17</f>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="E16" s="47">
         <f t="shared" si="0"/>
-        <v>424</v>
+        <v>440</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="C17" s="47">
         <f>'Portfolio &amp; Rebalancing'!F18</f>
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D17" s="48">
         <f>'Portfolio &amp; Rebalancing'!E18</f>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="E17" s="47">
         <f t="shared" si="0"/>
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="C18" s="47">
         <f>'Portfolio &amp; Rebalancing'!F19</f>
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="D18" s="48">
         <f>'Portfolio &amp; Rebalancing'!E19</f>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="E18" s="47">
         <f t="shared" si="0"/>
-        <v>325</v>
+        <v>305</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C19" s="47">
         <f>'Portfolio &amp; Rebalancing'!F20</f>
-        <v>328</v>
+        <v>297</v>
       </c>
       <c r="D19" s="48">
         <f>'Portfolio &amp; Rebalancing'!E20</f>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="E19" s="47">
         <f t="shared" si="0"/>
-        <v>328</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2917,11 +2917,11 @@
       </c>
       <c r="C20" s="50">
         <f>'Portfolio &amp; Rebalancing'!F21</f>
-        <v>12917.329999999998</v>
+        <v>12835.46</v>
       </c>
       <c r="E20" s="50">
         <f>SUM(E4:E19)</f>
-        <v>6499.884</v>
+        <v>6517.2939999999999</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="B22" s="51">
         <f>IF('Portfolio &amp; Rebalancing'!F25=0,0,E20/'Portfolio &amp; Rebalancing'!F25)</f>
-        <v>0.46871921271073819</v>
+        <v>0.47276579816705427</v>
       </c>
     </row>
     <row r="23" spans="1:5">

--- a/03_Tools/Rebalancing_Tool_v3.4.xlsx
+++ b/03_Tools/Rebalancing_Tool_v3.4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tobia\OneDrive\Desktop\Claude Stuff\03_Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_ADF9235F583F999A114096030E7988BB87031414" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E117FD-7A60-4C74-829B-C782E3508459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1777,7 +1777,7 @@
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="101">
         <f ca="1">TODAY()</f>
-        <v>46179</v>
+        <v>46182</v>
       </c>
       <c r="B2" s="100"/>
       <c r="C2" s="100"/>
@@ -1869,11 +1869,11 @@
         <v>0</v>
       </c>
       <c r="F5" s="5">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="G5" s="6">
         <f t="shared" ref="G5:G23" si="0">IF(F$28=0,0,F5/F$28)</f>
-        <v>5.0827343424183699E-2</v>
+        <v>4.8214243907007237E-2</v>
       </c>
       <c r="H5" s="6">
         <f>'Parameter &amp; Regeln'!$B$56/'Parameter &amp; Regeln'!$B$4</f>
@@ -1881,15 +1881,15 @@
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I23" si="1">H5*F$28</f>
-        <v>645.2494277400582</v>
+        <v>676.11654704170712</v>
       </c>
       <c r="J5" s="5">
         <f t="shared" ref="J5:J23" si="2">I5-F5</f>
-        <v>-17.750572259941805</v>
+        <v>17.116547041707122</v>
       </c>
       <c r="K5" s="6">
         <f t="shared" ref="K5:K23" si="3">G5-H5</f>
-        <v>1.360806081797665E-3</v>
+        <v>-1.2522934353787971E-3</v>
       </c>
       <c r="L5" s="3" t="str">
         <f>IF(C5="Aktie",IF(K5&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K5&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K5&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K5&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="G6" s="11">
         <f t="shared" si="0"/>
-        <v>0.30134098324460906</v>
+        <v>0.28758369817151685</v>
       </c>
       <c r="H6" s="11">
         <f>'Parameter &amp; Regeln'!$B$57/'Parameter &amp; Regeln'!$B$4</f>
@@ -1943,15 +1943,15 @@
       </c>
       <c r="I6" s="10">
         <f t="shared" si="1"/>
-        <v>3251.551037827352</v>
+        <v>3407.0971096023277</v>
       </c>
       <c r="J6" s="10">
         <f t="shared" si="2"/>
-        <v>-679.18896217264773</v>
+        <v>-523.64289039767209</v>
       </c>
       <c r="K6" s="11">
         <f t="shared" si="3"/>
-        <v>5.2068432323173569E-2</v>
+        <v>3.8311147250081362E-2</v>
       </c>
       <c r="L6" s="8" t="str">
         <f>IF(C6="Aktie",IF(K6&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K6&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K6&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K6&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="G7" s="11">
         <f t="shared" si="0"/>
-        <v>9.9080354733459275E-2</v>
+        <v>9.4556984992859319E-2</v>
       </c>
       <c r="H7" s="11">
         <f>'Parameter &amp; Regeln'!$B$58/'Parameter &amp; Regeln'!$B$4</f>
@@ -2005,15 +2005,15 @@
       </c>
       <c r="I7" s="10">
         <f t="shared" si="1"/>
-        <v>1556.1897963142578</v>
+        <v>1630.6340252182347</v>
       </c>
       <c r="J7" s="10">
         <f t="shared" si="2"/>
-        <v>263.76979631425775</v>
+        <v>338.21402521823461</v>
       </c>
       <c r="K7" s="11">
         <f t="shared" si="3"/>
-        <v>-2.0221294151118799E-2</v>
+        <v>-2.4744663891718754E-2</v>
       </c>
       <c r="L7" s="8" t="str">
         <f>IF(C7="Aktie",IF(K7&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K7&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K7&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K7&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="R7" s="94" t="str">
         <f>IF(AND(C7="Aktie",OR(LEFT(O7,1)="🔴",LEFT(N7,8)="DEFCON 1")),IF(J7&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J7&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J7&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
-        <v/>
+        <v>🛒 Nachkaufen</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2055,11 +2055,11 @@
         <v>0.67</v>
       </c>
       <c r="F8" s="10">
-        <v>1323</v>
+        <v>1335</v>
       </c>
       <c r="G8" s="11">
         <f t="shared" si="0"/>
-        <v>0.10142469886907245</v>
+        <v>9.7672254348793106E-2</v>
       </c>
       <c r="H8" s="11">
         <f>'Parameter &amp; Regeln'!$B$59/'Parameter &amp; Regeln'!$B$4</f>
@@ -2067,15 +2067,15 @@
       </c>
       <c r="I8" s="10">
         <f t="shared" si="1"/>
-        <v>1303.1508050436471</v>
+        <v>1365.4902812803105</v>
       </c>
       <c r="J8" s="10">
         <f t="shared" si="2"/>
-        <v>-19.849194956352903</v>
+        <v>30.490281280310455</v>
       </c>
       <c r="K8" s="11">
         <f t="shared" si="3"/>
-        <v>1.5216920795477068E-3</v>
+        <v>-2.2307524407316343E-3</v>
       </c>
       <c r="L8" s="8" t="str">
         <f>IF(C8="Aktie",IF(K8&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K8&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K8&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K8&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2129,11 +2129,11 @@
       </c>
       <c r="I9" s="10">
         <f t="shared" si="1"/>
-        <v>1037.4598642095054</v>
+        <v>1087.0893501454898</v>
       </c>
       <c r="J9" s="10">
         <f t="shared" si="2"/>
-        <v>1037.4598642095054</v>
+        <v>1087.0893501454898</v>
       </c>
       <c r="K9" s="11">
         <f t="shared" si="3"/>
@@ -2179,11 +2179,11 @@
         <v>0.68</v>
       </c>
       <c r="F10" s="16">
-        <v>91</v>
+        <v>196</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" si="0"/>
-        <v>6.9763020386134486E-3</v>
+        <v>1.4339896518624306E-2</v>
       </c>
       <c r="H10" s="17">
         <f>'Parameter &amp; Regeln'!$B$61/'Parameter &amp; Regeln'!$B$4</f>
@@ -2191,15 +2191,15 @@
       </c>
       <c r="I10" s="16">
         <f t="shared" si="1"/>
-        <v>645.2494277400582</v>
+        <v>676.11654704170712</v>
       </c>
       <c r="J10" s="16">
         <f t="shared" si="2"/>
-        <v>554.2494277400582</v>
+        <v>480.11654704170712</v>
       </c>
       <c r="K10" s="17">
         <f t="shared" si="3"/>
-        <v>-4.2490235303772585E-2</v>
+        <v>-3.5126640823761726E-2</v>
       </c>
       <c r="L10" s="14" t="str">
         <f>IF(C10="Aktie",IF(K10&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K10&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K10&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K10&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2241,11 +2241,11 @@
         <v>1</v>
       </c>
       <c r="F11" s="66">
-        <v>185</v>
+        <v>381</v>
       </c>
       <c r="G11" s="67">
         <f t="shared" si="0"/>
-        <v>1.4182592056521845E-2</v>
+        <v>2.7875002926509494E-2</v>
       </c>
       <c r="H11" s="67">
         <f>'Parameter &amp; Regeln'!$B$35/'Parameter &amp; Regeln'!$B$4</f>
@@ -2253,15 +2253,15 @@
       </c>
       <c r="I11" s="66">
         <f t="shared" si="1"/>
-        <v>506.07798254122213</v>
+        <v>530.28748787584868</v>
       </c>
       <c r="J11" s="66">
         <f t="shared" si="2"/>
-        <v>321.07798254122213</v>
+        <v>149.28748787584868</v>
       </c>
       <c r="K11" s="67">
         <f t="shared" si="3"/>
-        <v>-2.4614692133584852E-2</v>
+        <v>-1.0922281263597202E-2</v>
       </c>
       <c r="L11" s="64" t="str">
         <f>IF(C11="Aktie",IF(K11&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K11&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K11&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K11&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="R11" s="95" t="str">
         <f>IF(AND(C11="Aktie",OR(LEFT(O11,1)="🔴",LEFT(N11,8)="DEFCON 1")),IF(J11&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J11&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J11&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
-        <v>🚩 FLAG (gesperrt)</v>
+        <v/>
       </c>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2307,11 +2307,11 @@
         <v>1</v>
       </c>
       <c r="F12" s="68">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="G12" s="82">
         <f t="shared" si="0"/>
-        <v>2.5375340382209358E-2</v>
+        <v>2.5094818907592537E-2</v>
       </c>
       <c r="H12" s="82">
         <f>'Parameter &amp; Regeln'!$B$37/'Parameter &amp; Regeln'!$B$4</f>
@@ -2319,15 +2319,15 @@
       </c>
       <c r="I12" s="68">
         <f t="shared" si="1"/>
-        <v>227.73509214354996</v>
+        <v>238.62936954413192</v>
       </c>
       <c r="J12" s="68">
         <f t="shared" si="2"/>
-        <v>-103.26490785645004</v>
+        <v>-104.37063045586808</v>
       </c>
       <c r="K12" s="82">
         <f t="shared" si="3"/>
-        <v>7.916562496661346E-3</v>
+        <v>7.6360410220445256E-3</v>
       </c>
       <c r="L12" s="80" t="str">
         <f>IF(C12="Aktie",IF(K12&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K12&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K12&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K12&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2373,11 +2373,11 @@
         <v>0</v>
       </c>
       <c r="F13" s="66">
-        <v>486</v>
+        <v>519</v>
       </c>
       <c r="G13" s="67">
         <f t="shared" si="0"/>
-        <v>3.7258052645781713E-2</v>
+        <v>3.7971460679418444E-2</v>
       </c>
       <c r="H13" s="67">
         <f>'Parameter &amp; Regeln'!$B$36/'Parameter &amp; Regeln'!$B$4</f>
@@ -2385,15 +2385,15 @@
       </c>
       <c r="I13" s="66">
         <f t="shared" si="1"/>
-        <v>404.86238603297767</v>
+        <v>424.22999030067894</v>
       </c>
       <c r="J13" s="66">
         <f t="shared" si="2"/>
-        <v>-81.137613967022332</v>
+        <v>-94.770009699321065</v>
       </c>
       <c r="K13" s="67">
         <f t="shared" si="3"/>
-        <v>6.2202252936963583E-3</v>
+        <v>6.9336333273330893E-3</v>
       </c>
       <c r="L13" s="64" t="str">
         <f>IF(C13="Aktie",IF(K13&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K13&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K13&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K13&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2439,11 +2439,11 @@
         <v>1</v>
       </c>
       <c r="F14" s="68">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G14" s="82">
         <f t="shared" si="0"/>
-        <v>3.4421534234477344E-2</v>
+        <v>3.2776906328284131E-2</v>
       </c>
       <c r="H14" s="82">
         <f>'Parameter &amp; Regeln'!$B$37/'Parameter &amp; Regeln'!$B$4</f>
@@ -2451,15 +2451,15 @@
       </c>
       <c r="I14" s="68">
         <f t="shared" si="1"/>
-        <v>227.73509214354996</v>
+        <v>238.62936954413192</v>
       </c>
       <c r="J14" s="68">
         <f t="shared" si="2"/>
-        <v>-221.26490785645004</v>
+        <v>-209.37063045586808</v>
       </c>
       <c r="K14" s="82">
         <f t="shared" si="3"/>
-        <v>1.6962756348929332E-2</v>
+        <v>1.5318128442736119E-2</v>
       </c>
       <c r="L14" s="80" t="str">
         <f>IF(C14="Aktie",IF(K14&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K14&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K14&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K14&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2505,11 +2505,11 @@
         <v>1</v>
       </c>
       <c r="F15" s="66">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="G15" s="67">
         <f t="shared" si="0"/>
-        <v>3.6261438068836936E-2</v>
+        <v>3.5557090347201087E-2</v>
       </c>
       <c r="H15" s="67">
         <f>'Parameter &amp; Regeln'!$B$35/'Parameter &amp; Regeln'!$B$4</f>
@@ -2517,15 +2517,15 @@
       </c>
       <c r="I15" s="66">
         <f t="shared" si="1"/>
-        <v>506.07798254122213</v>
+        <v>530.28748787584868</v>
       </c>
       <c r="J15" s="66">
         <f t="shared" si="2"/>
-        <v>33.077982541222127</v>
+        <v>44.287487875848683</v>
       </c>
       <c r="K15" s="67">
         <f t="shared" si="3"/>
-        <v>-2.5358461212697594E-3</v>
+        <v>-3.2401938429056087E-3</v>
       </c>
       <c r="L15" s="64" t="str">
         <f>IF(C15="Aktie",IF(K15&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K15&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K15&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K15&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2571,11 +2571,11 @@
         <v>0</v>
       </c>
       <c r="F16" s="68">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="G16" s="82">
         <f t="shared" si="0"/>
-        <v>3.0895051885288131E-2</v>
+        <v>2.9996722309367171E-2</v>
       </c>
       <c r="H16" s="82">
         <f>'Parameter &amp; Regeln'!$B$37/'Parameter &amp; Regeln'!$B$4</f>
@@ -2583,15 +2583,15 @@
       </c>
       <c r="I16" s="68">
         <f t="shared" si="1"/>
-        <v>227.73509214354996</v>
+        <v>238.62936954413192</v>
       </c>
       <c r="J16" s="68">
         <f t="shared" si="2"/>
-        <v>-175.26490785645004</v>
+        <v>-171.37063045586808</v>
       </c>
       <c r="K16" s="82">
         <f t="shared" si="3"/>
-        <v>1.3436273999740119E-2</v>
+        <v>1.2537944423819159E-2</v>
       </c>
       <c r="L16" s="80" t="str">
         <f>IF(C16="Aktie",IF(K16&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K16&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K16&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K16&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2649,11 +2649,11 @@
       </c>
       <c r="I17" s="66">
         <f t="shared" si="1"/>
-        <v>404.86238603297767</v>
+        <v>424.22999030067894</v>
       </c>
       <c r="J17" s="66">
         <f t="shared" si="2"/>
-        <v>404.86238603297767</v>
+        <v>424.22999030067894</v>
       </c>
       <c r="K17" s="67">
         <f t="shared" si="3"/>
@@ -2703,11 +2703,11 @@
         <v>1</v>
       </c>
       <c r="F18" s="68">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="G18" s="82">
         <f t="shared" si="0"/>
-        <v>3.2964943698942671E-2</v>
+        <v>3.1094163369465969E-2</v>
       </c>
       <c r="H18" s="82">
         <f>'Parameter &amp; Regeln'!$B$35/'Parameter &amp; Regeln'!$B$4</f>
@@ -2715,15 +2715,15 @@
       </c>
       <c r="I18" s="68">
         <f t="shared" si="1"/>
-        <v>506.07798254122213</v>
+        <v>530.28748787584868</v>
       </c>
       <c r="J18" s="68">
         <f t="shared" si="2"/>
-        <v>76.077982541222127</v>
+        <v>105.28748787584868</v>
       </c>
       <c r="K18" s="82">
         <f t="shared" si="3"/>
-        <v>-5.8323404911640245E-3</v>
+        <v>-7.7031208206407263E-3</v>
       </c>
       <c r="L18" s="80" t="str">
         <f>IF(C18="Aktie",IF(K18&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K18&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K18&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K18&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2769,11 +2769,11 @@
         <v>0</v>
       </c>
       <c r="F19" s="66">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="G19" s="67">
         <f t="shared" si="0"/>
-        <v>3.1508353163407991E-2</v>
+        <v>3.058202420808653E-2</v>
       </c>
       <c r="H19" s="67">
         <f>'Parameter &amp; Regeln'!$B$37/'Parameter &amp; Regeln'!$B$4</f>
@@ -2781,15 +2781,15 @@
       </c>
       <c r="I19" s="66">
         <f t="shared" si="1"/>
-        <v>227.73509214354996</v>
+        <v>238.62936954413192</v>
       </c>
       <c r="J19" s="66">
         <f t="shared" si="2"/>
-        <v>-183.26490785645004</v>
+        <v>-179.37063045586808</v>
       </c>
       <c r="K19" s="67">
         <f t="shared" si="3"/>
-        <v>1.404957527785998E-2</v>
+        <v>1.3123246322538518E-2</v>
       </c>
       <c r="L19" s="64" t="str">
         <f>IF(C19="Aktie",IF(K19&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K19&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K19&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K19&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2835,11 +2835,11 @@
         <v>1</v>
       </c>
       <c r="F20" s="68">
-        <v>194</v>
+        <v>451</v>
       </c>
       <c r="G20" s="82">
         <f t="shared" si="0"/>
-        <v>1.4872555994406693E-2</v>
+        <v>3.299639454030389E-2</v>
       </c>
       <c r="H20" s="82">
         <f>'Parameter &amp; Regeln'!$B$35/'Parameter &amp; Regeln'!$B$4</f>
@@ -2847,15 +2847,15 @@
       </c>
       <c r="I20" s="68">
         <f t="shared" si="1"/>
-        <v>506.07798254122213</v>
+        <v>530.28748787584868</v>
       </c>
       <c r="J20" s="68">
         <f t="shared" si="2"/>
-        <v>312.07798254122213</v>
+        <v>79.287487875848683</v>
       </c>
       <c r="K20" s="82">
         <f t="shared" si="3"/>
-        <v>-2.3924728195700004E-2</v>
+        <v>-5.8008896498028054E-3</v>
       </c>
       <c r="L20" s="80" t="str">
         <f>IF(C20="Aktie",IF(K20&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K20&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K20&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K20&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="R20" s="96" t="str">
         <f>IF(AND(C20="Aktie",OR(LEFT(O20,1)="🔴",LEFT(N20,8)="DEFCON 1")),IF(J20&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J20&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J20&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
-        <v>🛒 Nachkaufen</v>
+        <v/>
       </c>
     </row>
     <row r="21" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2901,11 +2901,11 @@
         <v>1</v>
       </c>
       <c r="F21" s="66">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="G21" s="67">
         <f t="shared" si="0"/>
-        <v>3.0665063905993179E-2</v>
+        <v>2.8972443986608292E-2</v>
       </c>
       <c r="H21" s="67">
         <f>'Parameter &amp; Regeln'!$B$37/'Parameter &amp; Regeln'!$B$4</f>
@@ -2913,15 +2913,15 @@
       </c>
       <c r="I21" s="66">
         <f t="shared" si="1"/>
-        <v>227.73509214354996</v>
+        <v>238.62936954413192</v>
       </c>
       <c r="J21" s="66">
         <f t="shared" si="2"/>
-        <v>-172.26490785645004</v>
+        <v>-157.37063045586808</v>
       </c>
       <c r="K21" s="67">
         <f t="shared" si="3"/>
-        <v>1.3206286020445168E-2</v>
+        <v>1.151366610106028E-2</v>
       </c>
       <c r="L21" s="64" t="str">
         <f>IF(C21="Aktie",IF(K21&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K21&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K21&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K21&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2967,11 +2967,11 @@
         <v>1</v>
       </c>
       <c r="F22" s="68">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="G22" s="82">
         <f t="shared" si="0"/>
-        <v>3.6798076687191816E-2</v>
+        <v>3.4752300236461968E-2</v>
       </c>
       <c r="H22" s="82">
         <f>'Parameter &amp; Regeln'!$B$36/'Parameter &amp; Regeln'!$B$4</f>
@@ -2979,15 +2979,15 @@
       </c>
       <c r="I22" s="68">
         <f t="shared" si="1"/>
-        <v>404.86238603297767</v>
+        <v>424.22999030067894</v>
       </c>
       <c r="J22" s="68">
         <f t="shared" si="2"/>
-        <v>-75.137613967022332</v>
+        <v>-50.770009699321065</v>
       </c>
       <c r="K22" s="82">
         <f t="shared" si="3"/>
-        <v>5.7602493351064619E-3</v>
+        <v>3.7144728843766135E-3</v>
       </c>
       <c r="L22" s="80" t="str">
         <f>IF(C22="Aktie",IF(K22&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K22&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K22&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K22&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -3033,11 +3033,11 @@
         <v>1</v>
       </c>
       <c r="F23" s="66">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G23" s="67">
         <f t="shared" si="0"/>
-        <v>3.6108112749306968E-2</v>
+        <v>3.4532812024442208E-2</v>
       </c>
       <c r="H23" s="67">
         <f>'Parameter &amp; Regeln'!$B$37/'Parameter &amp; Regeln'!$B$4</f>
@@ -3045,15 +3045,15 @@
       </c>
       <c r="I23" s="66">
         <f t="shared" si="1"/>
-        <v>227.73509214354996</v>
+        <v>238.62936954413192</v>
       </c>
       <c r="J23" s="66">
         <f t="shared" si="2"/>
-        <v>-243.26490785645004</v>
+        <v>-233.37063045586808</v>
       </c>
       <c r="K23" s="67">
         <f t="shared" si="3"/>
-        <v>1.8649334863758957E-2</v>
+        <v>1.7074034138894197E-2</v>
       </c>
       <c r="L23" s="64" t="str">
         <f>IF(C23="Aktie",IF(K23&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K23&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K23&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K23&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -3092,11 +3092,11 @@
       <c r="E24" s="19"/>
       <c r="F24" s="20">
         <f>SUM(F5:F23)</f>
-        <v>12013.16</v>
+        <v>12637.16</v>
       </c>
       <c r="G24" s="21">
         <f>SUM(G5:G23)</f>
-        <v>0.92096079778230266</v>
+        <v>0.92456921780254253</v>
       </c>
       <c r="H24" s="21">
         <f>SUM(H5:H23)</f>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="I24" s="20">
         <f>SUM(I5:I23)</f>
-        <v>13044.160000000002</v>
+        <v>13668.160000000003</v>
       </c>
       <c r="J24" s="20">
         <f>ROUND(SUM(J5:J23),2)</f>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="K24" s="21">
         <f t="array" ref="K24">SUMPRODUCT((C5:C23="Aktie")*ABS(K5:K23))/COUNTIF(C5:C23,"Aktie")</f>
-        <v>1.4165130610000132E-2</v>
+        <v>1.1273498430141091E-2</v>
       </c>
       <c r="L24" s="18" t="s">
         <v>83</v>
@@ -3137,7 +3137,7 @@
     <row r="25" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K25" s="24">
         <f t="array" ref="K25">SUMPRODUCT((C5:C23&lt;&gt;"Aktie")*ABS(K5:K23))/COUNTIF(C5:C23,"&lt;&gt;Aktie")</f>
-        <v>3.2866148754854836E-2</v>
+        <v>3.0199988405231831E-2</v>
       </c>
       <c r="L25" s="25" t="s">
         <v>84</v>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="F28" s="33">
         <f>F24 + F27</f>
-        <v>13044.16</v>
+        <v>13668.16</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="C4" s="39">
         <f>'Portfolio &amp; Rebalancing'!F5</f>
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="D4" s="40">
         <f>'Portfolio &amp; Rebalancing'!E5</f>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="C7" s="39">
         <f>'Portfolio &amp; Rebalancing'!F8</f>
-        <v>1323</v>
+        <v>1335</v>
       </c>
       <c r="D7" s="40">
         <f>'Portfolio &amp; Rebalancing'!E8</f>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="E7" s="39">
         <f t="shared" si="0"/>
-        <v>886.41000000000008</v>
+        <v>894.45</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C9" s="39">
         <f>'Portfolio &amp; Rebalancing'!F10</f>
-        <v>91</v>
+        <v>196</v>
       </c>
       <c r="D9" s="40">
         <f>'Portfolio &amp; Rebalancing'!E10</f>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E9" s="39">
         <f t="shared" si="0"/>
-        <v>61.88</v>
+        <v>133.28</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="C10" s="39">
         <f>'Portfolio &amp; Rebalancing'!F11</f>
-        <v>185</v>
+        <v>381</v>
       </c>
       <c r="D10" s="40">
         <f>'Portfolio &amp; Rebalancing'!E11</f>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="E10" s="39">
         <f t="shared" si="0"/>
-        <v>185</v>
+        <v>381</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="C11" s="39">
         <f>'Portfolio &amp; Rebalancing'!F12</f>
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="D11" s="40">
         <f>'Portfolio &amp; Rebalancing'!E12</f>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="E11" s="39">
         <f t="shared" si="0"/>
-        <v>331</v>
+        <v>343</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="C12" s="39">
         <f>'Portfolio &amp; Rebalancing'!F13</f>
-        <v>486</v>
+        <v>519</v>
       </c>
       <c r="D12" s="40">
         <f>'Portfolio &amp; Rebalancing'!E13</f>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="C13" s="39">
         <f>'Portfolio &amp; Rebalancing'!F14</f>
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D13" s="40">
         <f>'Portfolio &amp; Rebalancing'!E14</f>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="E13" s="39">
         <f t="shared" si="0"/>
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="C14" s="39">
         <f>'Portfolio &amp; Rebalancing'!F15</f>
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="D14" s="40">
         <f>'Portfolio &amp; Rebalancing'!E15</f>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="E14" s="39">
         <f t="shared" si="0"/>
-        <v>473</v>
+        <v>486</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="C15" s="39">
         <f>'Portfolio &amp; Rebalancing'!F16</f>
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="D15" s="40">
         <f>'Portfolio &amp; Rebalancing'!E16</f>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="C17" s="39">
         <f>'Portfolio &amp; Rebalancing'!F18</f>
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="D17" s="40">
         <f>'Portfolio &amp; Rebalancing'!E18</f>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="E17" s="39">
         <f t="shared" si="0"/>
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="C18" s="39">
         <f>'Portfolio &amp; Rebalancing'!F19</f>
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="D18" s="40">
         <f>'Portfolio &amp; Rebalancing'!E19</f>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="C19" s="39">
         <f>'Portfolio &amp; Rebalancing'!F20</f>
-        <v>194</v>
+        <v>451</v>
       </c>
       <c r="D19" s="40">
         <f>'Portfolio &amp; Rebalancing'!E20</f>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="E19" s="39">
         <f t="shared" si="0"/>
-        <v>194</v>
+        <v>451</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="C20" s="39">
         <f>'Portfolio &amp; Rebalancing'!F21</f>
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="D20" s="40">
         <f>'Portfolio &amp; Rebalancing'!E21</f>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="E20" s="39">
         <f t="shared" si="0"/>
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C21" s="39">
         <f>'Portfolio &amp; Rebalancing'!F22</f>
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="D21" s="40">
         <f>'Portfolio &amp; Rebalancing'!E22</f>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="E21" s="39">
         <f t="shared" si="0"/>
-        <v>480</v>
+        <v>475</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="C22" s="39">
         <f>'Portfolio &amp; Rebalancing'!F23</f>
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D22" s="40">
         <f>'Portfolio &amp; Rebalancing'!E23</f>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="E22" s="39">
         <f t="shared" si="0"/>
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -3757,11 +3757,11 @@
       </c>
       <c r="C23" s="42">
         <f>'Portfolio &amp; Rebalancing'!F24</f>
-        <v>12013.16</v>
+        <v>12637.16</v>
       </c>
       <c r="E23" s="42">
         <f>SUM(E4:E22)</f>
-        <v>7112.808</v>
+        <v>7656.2479999999996</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="B25" s="43">
         <f>IF('Portfolio &amp; Rebalancing'!F24=0,0,E23/'Portfolio &amp; Rebalancing'!F24)</f>
-        <v>0.59208468046708773</v>
+        <v>0.60585194774775342</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="B26" s="43">
         <f>SUMPRODUCT('Portfolio &amp; Rebalancing'!$E$5:$E$23,'Portfolio &amp; Rebalancing'!$I$5:$I$23)/SUM('Portfolio &amp; Rebalancing'!$I$5:$I$23)</f>
-        <v>0.58043646944713867</v>
+        <v>0.58043646944713845</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">

--- a/03_Tools/Rebalancing_Tool_v3.4.xlsx
+++ b/03_Tools/Rebalancing_Tool_v3.4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tobia\OneDrive\Desktop\Claude Stuff\03_Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E117FD-7A60-4C74-829B-C782E3508459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338D1794-8EE1-4A6D-AA4A-93F9098B45F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,10 @@
     <sheet name="US-Exposure" sheetId="2" r:id="rId2"/>
     <sheet name="Parameter &amp; Regeln" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Portfolio &amp; Rebalancing'!$A$1:$R$31</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Portfolio &amp; Rebalancing'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +44,117 @@
     <author>Tobias Kowalski</author>
   </authors>
   <commentList>
-    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{36C7BF1C-B04A-4C21-BCA9-9EFB07A1A6F0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t>Tobias Kowalski:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t xml:space="preserve">
+💱 FX: EUR-nativ (EUWAX Gold, Handel &amp; Abrechnung in EUR) — kein Währungsrisiko auf Depotwert-Ebene.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F6" authorId="0" shapeId="0" xr:uid="{42BB1CBA-38A6-4AB7-9689-28B380F32BCF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t>Tobias Kowalski:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t xml:space="preserve">
+💱 FX: EUR-gehandelt (Xetra). Underlying USD-dominiert — interne FX-Exposure über US-Faktor (Sp. E = 0,70) approximiert. Stichtag Depotwert: [eintragen].</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{DC4A30E8-E6AF-48C7-A09F-C8923148297D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t>Tobias Kowalski:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t xml:space="preserve">
+💱 FX: EUR-gehandelt (Xetra). Underlying EM-Währungen gemischt — interne FX-Exposure über US-Faktor (Sp. E = 0,00) approximiert. Stichtag Depotwert: [eintragen].</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{3F5005B3-60F9-47BB-9F32-92DFED99122B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t>Tobias Kowalski:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t xml:space="preserve">
+💱 FX: EUR-gehandelt (Xetra). Underlying ex-US (EUR/JPY/GBP u.a.) — US-Faktor (Sp. E = 0,00). Stichtag Depotwert: [eintragen].</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F9" authorId="0" shapeId="0" xr:uid="{A98030F3-0CF2-4F10-B074-1C4D2E07FC8E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t>Tobias Kowalski:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t xml:space="preserve">
+💱 FX: EUR-gehandelt (Xetra). Underlying global gemischt — US-Faktor (Sp. E = 0,67). Stichtag Depotwert: [eintragen].</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -55,7 +169,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{523029CC-059C-4B81-8079-08C5E4A37663}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t>Tobias Kowalski:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t xml:space="preserve">
+💱 FX: EUR-gehandelt (Xetra). Underlying US-dominiert — US-Faktor (Sp. E = 0,62). Stichtag Depotwert: [eintragen].</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -70,7 +206,139 @@
         </r>
       </text>
     </comment>
-    <comment ref="E16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{C82CE413-15AA-4FD2-B8A5-E5D4B6816BEF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t>Tobias Kowalski:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t xml:space="preserve">
+💱 FX: EUR-gehandelt (Xetra). Underlying US-dominiert — US-Faktor (Sp. E = 0,68). Stichtag Depotwert: [eintragen].</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{77C0FB83-E145-410D-9EAD-E51F8491AFF1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t>Tobias Kowalski:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t xml:space="preserve">
+💱 FX: Basiswährung USD (Amazon, NASDAQ). EUR-Depotwert währungsabhängig. USD/EUR-Kurs: [eintragen] · Stichtag: [eintragen] · Quelle: [eintragen].</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{54F59535-64B3-44C9-9DDB-6CDBBD0898E1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t>Tobias Kowalski:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t xml:space="preserve">
+💱 FX: Basiswährung USD (Amphenol, NYSE). EUR-Depotwert währungsabhängig. USD/EUR-Kurs: [eintragen] · Stichtag: [eintragen] · Quelle: [eintragen].</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{AA363B49-E40E-4AF7-B8EC-1F41F6353A93}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t>Tobias Kowalski:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t xml:space="preserve">
+💱 FX: EUR-nativ (ASML, Euronext Amsterdam) — kein Währungsrisiko auf Depotwert-Ebene.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F15" authorId="0" shapeId="0" xr:uid="{2469F3D6-E9FA-47A9-A12F-8E3BD6B5A926}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t>Tobias Kowalski:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t xml:space="preserve">
+💱 FX: Basiswährung USD (Berkshire B, NYSE). EUR-Depotwert währungsabhängig. USD/EUR-Kurs: [eintragen] · Stichtag: [eintragen] · Quelle: [eintragen].</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F16" authorId="0" shapeId="0" xr:uid="{0DA34E13-2DEC-4455-908A-A6F13F25309C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t>Tobias Kowalski:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t xml:space="preserve">
+💱 FX: Basiswährung USD (Broadcom, NASDAQ). EUR-Depotwert währungsabhängig. USD/EUR-Kurs: [eintragen] · Stichtag: [eintragen] · Quelle: [eintragen].</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -85,12 +353,188 @@
         </r>
       </text>
     </comment>
+    <comment ref="F17" authorId="0" shapeId="0" xr:uid="{4743FB4F-4E68-4CBD-A5C5-9DBB52A6078B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t>Tobias Kowalski:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t xml:space="preserve">
+💱 FX: EUR-nativ (Hermès, Euronext Paris) — kein Währungsrisiko auf Depotwert-Ebene.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{A16A4438-BDAF-4113-8DE7-0EC0A025321A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t>Tobias Kowalski:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t xml:space="preserve">
+💱 FX: Basiswährung JPY (Keyence, Tokio; KYCCF = US-OTC-ADR). EUR-Depotwert währungsabhängig. JPY/EUR-Kurs: [eintragen] · Stichtag: [eintragen] · Quelle: [eintragen].</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F19" authorId="0" shapeId="0" xr:uid="{D7349C2C-033C-4F4E-BD9D-0502C548D88A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t>Tobias Kowalski:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t xml:space="preserve">
+💱 FX: Basiswährung USD (Microsoft, NASDAQ). EUR-Depotwert währungsabhängig. USD/EUR-Kurs: [eintragen] · Stichtag: [eintragen] · Quelle: [eintragen].</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F20" authorId="0" shapeId="0" xr:uid="{AAE92BA9-82DB-433D-9676-E2015E296E20}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t>Tobias Kowalski:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t xml:space="preserve">
+💱 FX: EUR-nativ (Schneider Electric, Euronext Paris) — kein Währungsrisiko auf Depotwert-Ebene.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F21" authorId="0" shapeId="0" xr:uid="{D6C1C7C9-3185-44AB-A0C0-6DCB3521403F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t>Tobias Kowalski:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t xml:space="preserve">
+💱 FX: Basiswährung USD (ServiceNow, NYSE). EUR-Depotwert währungsabhängig. USD/EUR-Kurs: [eintragen] · Stichtag: [eintragen] · Quelle: [eintragen].</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F22" authorId="0" shapeId="0" xr:uid="{F172CAB6-23B0-458A-A6D7-DBA6FCA87289}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t>Tobias Kowalski:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t xml:space="preserve">
+💱 FX: Basiswährung USD (Thermo Fisher, NYSE). EUR-Depotwert währungsabhängig. USD/EUR-Kurs: [eintragen] · Stichtag: [eintragen] · Quelle: [eintragen].</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F23" authorId="0" shapeId="0" xr:uid="{AB936CE3-A1A3-4F33-B239-651719548759}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t>Tobias Kowalski:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t xml:space="preserve">
+💱 FX: Basiswährung USD (Visa, NYSE). EUR-Depotwert währungsabhängig. USD/EUR-Kurs: [eintragen] · Stichtag: [eintragen] · Quelle: [eintragen].</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F24" authorId="0" shapeId="0" xr:uid="{C6FA12BE-BF20-412C-921F-2D60BCF5A46D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t>Tobias Kowalski:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+          </rPr>
+          <t xml:space="preserve">
+💱 FX: Basiswährung USD (Zeta Global, NYSE). EUR-Depotwert währungsabhängig. USD/EUR-Kurs: [eintragen] · Stichtag: [eintragen] · Quelle: [eintragen].</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="173">
   <si>
     <t>🦅 DYNASTIE-DEPOT – Rebalancing Tool v4.0</t>
   </si>
@@ -614,6 +1058,12 @@
   </si>
   <si>
     <t>Schwelle Fehlbetrag für Nachkauf-Signal (€)</t>
+  </si>
+  <si>
+    <t>EXUS</t>
+  </si>
+  <si>
+    <t>Xtrackers MSCI World ex USA</t>
   </si>
 </sst>
 </file>
@@ -625,7 +1075,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.00&quot; €&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot; Positionen&quot;"/>
   </numFmts>
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -818,6 +1268,17 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Segoe UI"/>
+    </font>
   </fonts>
   <fills count="25">
     <fill>
@@ -966,7 +1427,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1005,19 +1466,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1243,7 +1692,46 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1445,6 +1933,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1730,9 +2222,34 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{DF4B8C1F-5896-4959-8537-45DDC7ECB0E8}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="de-DE" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;149dc743-0a03-441a-aae5-74e65415a01b&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R35"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -1755,45 +2272,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="95" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="100"/>
-      <c r="O1" s="100"/>
-      <c r="P1" s="100"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="96"/>
+      <c r="P1" s="96"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="101">
+      <c r="A2" s="97">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
-      </c>
-      <c r="B2" s="100"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100"/>
-      <c r="N2" s="100"/>
-      <c r="O2" s="100"/>
-      <c r="P2" s="100"/>
+        <v>46185</v>
+      </c>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="96"/>
+      <c r="O2" s="96"/>
+      <c r="P2" s="96"/>
     </row>
     <row r="3" spans="1:18" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -1845,10 +2362,10 @@
       <c r="P4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="Q4" s="61" t="s">
+      <c r="Q4" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="R4" s="90" t="s">
+      <c r="R4" s="86" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1869,48 +2386,48 @@
         <v>0</v>
       </c>
       <c r="F5" s="5">
-        <v>659</v>
+        <v>630</v>
       </c>
       <c r="G5" s="6">
-        <f t="shared" ref="G5:G23" si="0">IF(F$28=0,0,F5/F$28)</f>
-        <v>4.8214243907007237E-2</v>
+        <f t="shared" ref="G5:G24" si="0">IF(F$29=0,0,F5/F$29)</f>
+        <v>3.8975139428921411E-2</v>
       </c>
       <c r="H5" s="6">
-        <f>'Parameter &amp; Regeln'!$B$56/'Parameter &amp; Regeln'!$B$4</f>
+        <f>VLOOKUP($B5,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE)/'Parameter &amp; Regeln'!$B$4</f>
         <v>4.9466537342386034E-2</v>
       </c>
       <c r="I5" s="5">
-        <f t="shared" ref="I5:I23" si="1">H5*F$28</f>
-        <v>676.11654704170712</v>
+        <f t="shared" ref="I5:I24" si="1">H5*F$29</f>
+        <v>799.58452958292924</v>
       </c>
       <c r="J5" s="5">
-        <f t="shared" ref="J5:J23" si="2">I5-F5</f>
-        <v>17.116547041707122</v>
+        <f t="shared" ref="J5:J24" si="2">I5-F5</f>
+        <v>169.58452958292924</v>
       </c>
       <c r="K5" s="6">
-        <f t="shared" ref="K5:K23" si="3">G5-H5</f>
-        <v>-1.2522934353787971E-3</v>
+        <f t="shared" ref="K5:K24" si="3">G5-H5</f>
+        <v>-1.0491397913464623E-2</v>
       </c>
       <c r="L5" s="3" t="str">
         <f>IF(C5="Aktie",IF(K5&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K5&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K5&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K5&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
         <v>⚖️ Halten</v>
       </c>
-      <c r="M5" s="98" t="str">
+      <c r="M5" s="94" t="str">
         <f>IF(C5="Aktie",IF(G5&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
         <v/>
       </c>
-      <c r="N5" s="88"/>
-      <c r="O5" s="88"/>
-      <c r="P5" s="69">
-        <f>IF(C5="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q5/SUMIFS($Q$5:$Q$23,$C$5:$C$23,"Aktie"),IFERROR(VLOOKUP(B5,'Parameter &amp; Regeln'!$A$56:$B$61,2,FALSE),0))</f>
+      <c r="N5" s="84"/>
+      <c r="O5" s="84"/>
+      <c r="P5" s="65">
+        <f>IF(C5="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q5/SUMIFS($Q$5:$Q$24,$C$5:$C$24,"Aktie"),IFERROR(VLOOKUP(B5,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE),0))</f>
         <v>51</v>
       </c>
-      <c r="Q5" s="62">
+      <c r="Q5" s="58">
         <f>IF(OR(C5="ETF",C5="Gold"),H5,IF(C5&lt;&gt;"Aktie",0,IF(OR(LEFT(O5,1)="🔴",LEFT(N5,8)="DEFCON 1"),0,IF(LEFT(N5,8)="DEFCON 2",IFERROR(VLOOKUP(B5,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B5,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
         <v>4.9466537342386034E-2</v>
       </c>
-      <c r="R5" s="93" t="str">
-        <f>IF(AND(C5="Aktie",OR(LEFT(O5,1)="🔴",LEFT(N5,8)="DEFCON 1")),IF(J5&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J5&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J5&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
+      <c r="R5" s="89" t="str">
+        <f>IF(AND(C5="Aktie",OR(LEFT(O5,1)="🔴",LEFT(N5,8)="DEFCON 1")),IF(J5&gt;'Parameter &amp; Regeln'!$B$65,"🚩 FLAG (gesperrt)",""),IF(J5&gt;'Parameter &amp; Regeln'!$B$65,"🛒 Nachkaufen",IF(J5&lt;-'Parameter &amp; Regeln'!$B$65,"⏸️ Über Ziel","")))</f>
         <v/>
       </c>
     </row>
@@ -1931,27 +2448,27 @@
         <v>0.7</v>
       </c>
       <c r="F6" s="10">
-        <v>3930.74</v>
+        <v>3943.46</v>
       </c>
       <c r="G6" s="11">
         <f t="shared" si="0"/>
-        <v>0.28758369817151685</v>
-      </c>
-      <c r="H6" s="11">
-        <f>'Parameter &amp; Regeln'!$B$57/'Parameter &amp; Regeln'!$B$4</f>
-        <v>0.24927255092143549</v>
+        <v>0.24396333862281655</v>
+      </c>
+      <c r="H6" s="6">
+        <f>VLOOKUP($B6,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE)/'Parameter &amp; Regeln'!$B$4</f>
+        <v>0.19980601357904948</v>
       </c>
       <c r="I6" s="10">
         <f t="shared" si="1"/>
-        <v>3407.0971096023277</v>
+        <v>3229.6943743937927</v>
       </c>
       <c r="J6" s="10">
         <f t="shared" si="2"/>
-        <v>-523.64289039767209</v>
+        <v>-713.76562560620732</v>
       </c>
       <c r="K6" s="11">
         <f t="shared" si="3"/>
-        <v>3.8311147250081362E-2</v>
+        <v>4.4157325043767071E-2</v>
       </c>
       <c r="L6" s="8" t="str">
         <f>IF(C6="Aktie",IF(K6&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K6&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K6&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K6&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -1961,18 +2478,18 @@
         <f>IF(C6="Aktie",IF(G6&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
         <v/>
       </c>
-      <c r="N6" s="89"/>
-      <c r="O6" s="89"/>
-      <c r="P6" s="69">
-        <f>IF(C6="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q6/SUMIFS($Q$5:$Q$23,$C$5:$C$23,"Aktie"),IFERROR(VLOOKUP(B6,'Parameter &amp; Regeln'!$A$56:$B$61,2,FALSE),0))</f>
-        <v>257</v>
-      </c>
-      <c r="Q6" s="62">
+      <c r="N6" s="85"/>
+      <c r="O6" s="85"/>
+      <c r="P6" s="65">
+        <f>IF(C6="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q6/SUMIFS($Q$5:$Q$24,$C$5:$C$24,"Aktie"),IFERROR(VLOOKUP(B6,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE),0))</f>
+        <v>206</v>
+      </c>
+      <c r="Q6" s="58">
         <f>IF(OR(C6="ETF",C6="Gold"),H6,IF(C6&lt;&gt;"Aktie",0,IF(OR(LEFT(O6,1)="🔴",LEFT(N6,8)="DEFCON 1"),0,IF(LEFT(N6,8)="DEFCON 2",IFERROR(VLOOKUP(B6,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B6,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
-        <v>0.24927255092143549</v>
-      </c>
-      <c r="R6" s="94" t="str">
-        <f>IF(AND(C6="Aktie",OR(LEFT(O6,1)="🔴",LEFT(N6,8)="DEFCON 1")),IF(J6&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J6&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J6&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
+        <v>0.19980601357904948</v>
+      </c>
+      <c r="R6" s="90" t="str">
+        <f>IF(AND(C6="Aktie",OR(LEFT(O6,1)="🔴",LEFT(N6,8)="DEFCON 1")),IF(J6&gt;'Parameter &amp; Regeln'!$B$65,"🚩 FLAG (gesperrt)",""),IF(J6&gt;'Parameter &amp; Regeln'!$B$65,"🛒 Nachkaufen",IF(J6&lt;-'Parameter &amp; Regeln'!$B$65,"⏸️ Über Ziel","")))</f>
         <v>⏸️ Über Ziel</v>
       </c>
     </row>
@@ -1993,27 +2510,27 @@
         <v>0</v>
       </c>
       <c r="F7" s="10">
-        <v>1292.42</v>
+        <v>1349.52</v>
       </c>
       <c r="G7" s="11">
         <f t="shared" si="0"/>
-        <v>9.4556984992859319E-2</v>
-      </c>
-      <c r="H7" s="11">
-        <f>'Parameter &amp; Regeln'!$B$58/'Parameter &amp; Regeln'!$B$4</f>
+        <v>8.3488460574790507E-2</v>
+      </c>
+      <c r="H7" s="6">
+        <f>VLOOKUP($B7,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE)/'Parameter &amp; Regeln'!$B$4</f>
         <v>0.11930164888457807</v>
       </c>
       <c r="I7" s="10">
         <f t="shared" si="1"/>
-        <v>1630.6340252182347</v>
+        <v>1928.4097478176527</v>
       </c>
       <c r="J7" s="10">
         <f t="shared" si="2"/>
-        <v>338.21402521823461</v>
+        <v>578.88974781765273</v>
       </c>
       <c r="K7" s="11">
         <f t="shared" si="3"/>
-        <v>-2.4744663891718754E-2</v>
+        <v>-3.5813188309787566E-2</v>
       </c>
       <c r="L7" s="8" t="str">
         <f>IF(C7="Aktie",IF(K7&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K7&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K7&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K7&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
@@ -2023,89 +2540,89 @@
         <f>IF(C7="Aktie",IF(G7&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
         <v/>
       </c>
-      <c r="N7" s="89"/>
-      <c r="O7" s="89"/>
-      <c r="P7" s="69">
-        <f>IF(C7="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q7/SUMIFS($Q$5:$Q$23,$C$5:$C$23,"Aktie"),IFERROR(VLOOKUP(B7,'Parameter &amp; Regeln'!$A$56:$B$61,2,FALSE),0))</f>
+      <c r="N7" s="85"/>
+      <c r="O7" s="85"/>
+      <c r="P7" s="65">
+        <f>IF(C7="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q7/SUMIFS($Q$5:$Q$24,$C$5:$C$24,"Aktie"),IFERROR(VLOOKUP(B7,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE),0))</f>
         <v>123</v>
       </c>
-      <c r="Q7" s="62">
+      <c r="Q7" s="58">
         <f>IF(OR(C7="ETF",C7="Gold"),H7,IF(C7&lt;&gt;"Aktie",0,IF(OR(LEFT(O7,1)="🔴",LEFT(N7,8)="DEFCON 1"),0,IF(LEFT(N7,8)="DEFCON 2",IFERROR(VLOOKUP(B7,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B7,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
         <v>0.11930164888457807</v>
       </c>
-      <c r="R7" s="94" t="str">
-        <f>IF(AND(C7="Aktie",OR(LEFT(O7,1)="🔴",LEFT(N7,8)="DEFCON 1")),IF(J7&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J7&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J7&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
+      <c r="R7" s="90" t="str">
+        <f>IF(AND(C7="Aktie",OR(LEFT(O7,1)="🔴",LEFT(N7,8)="DEFCON 1")),IF(J7&gt;'Parameter &amp; Regeln'!$B$65,"🚩 FLAG (gesperrt)",""),IF(J7&gt;'Parameter &amp; Regeln'!$B$65,"🛒 Nachkaufen",IF(J7&lt;-'Parameter &amp; Regeln'!$B$65,"⏸️ Über Ziel","")))</f>
         <v>🛒 Nachkaufen</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>29</v>
+        <v>172</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>30</v>
+        <v>171</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E8" s="9">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="F8" s="10">
-        <v>1335</v>
+        <v>1978.17</v>
       </c>
       <c r="G8" s="11">
-        <f t="shared" si="0"/>
-        <v>9.7672254348793106E-2</v>
-      </c>
-      <c r="H8" s="11">
-        <f>'Parameter &amp; Regeln'!$B$59/'Parameter &amp; Regeln'!$B$4</f>
-        <v>9.990300678952474E-2</v>
+        <f t="shared" ref="G8" si="4">IF(F$29=0,0,F8/F$29)</f>
+        <v>0.12238008184779281</v>
+      </c>
+      <c r="H8" s="6">
+        <f>VLOOKUP($B8,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE)/'Parameter &amp; Regeln'!$B$4</f>
+        <v>7.953443258971872E-2</v>
       </c>
       <c r="I8" s="10">
-        <f t="shared" si="1"/>
-        <v>1365.4902812803105</v>
+        <f t="shared" ref="I8" si="5">H8*F$29</f>
+        <v>1285.6064985451019</v>
       </c>
       <c r="J8" s="10">
-        <f t="shared" si="2"/>
-        <v>30.490281280310455</v>
+        <f t="shared" ref="J8" si="6">I8-F8</f>
+        <v>-692.56350145489819</v>
       </c>
       <c r="K8" s="11">
-        <f t="shared" si="3"/>
-        <v>-2.2307524407316343E-3</v>
+        <f t="shared" ref="K8" si="7">G8-H8</f>
+        <v>4.2845649258074089E-2</v>
       </c>
       <c r="L8" s="8" t="str">
         <f>IF(C8="Aktie",IF(K8&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K8&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K8&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K8&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
-        <v>⚖️ Halten</v>
+        <v>📉 Reduzieren</v>
       </c>
       <c r="M8" s="12" t="str">
         <f>IF(C8="Aktie",IF(G8&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
         <v/>
       </c>
-      <c r="N8" s="89"/>
-      <c r="O8" s="89"/>
-      <c r="P8" s="69">
-        <f>IF(C8="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q8/SUMIFS($Q$5:$Q$23,$C$5:$C$23,"Aktie"),IFERROR(VLOOKUP(B8,'Parameter &amp; Regeln'!$A$56:$B$61,2,FALSE),0))</f>
-        <v>103</v>
-      </c>
-      <c r="Q8" s="62">
+      <c r="N8" s="85"/>
+      <c r="O8" s="85"/>
+      <c r="P8" s="65">
+        <f>IF(C8="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q8/SUMIFS($Q$5:$Q$24,$C$5:$C$24,"Aktie"),IFERROR(VLOOKUP(B8,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE),0))</f>
+        <v>82</v>
+      </c>
+      <c r="Q8" s="58">
         <f>IF(OR(C8="ETF",C8="Gold"),H8,IF(C8&lt;&gt;"Aktie",0,IF(OR(LEFT(O8,1)="🔴",LEFT(N8,8)="DEFCON 1"),0,IF(LEFT(N8,8)="DEFCON 2",IFERROR(VLOOKUP(B8,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B8,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
-        <v>9.990300678952474E-2</v>
-      </c>
-      <c r="R8" s="94" t="str">
-        <f>IF(AND(C8="Aktie",OR(LEFT(O8,1)="🔴",LEFT(N8,8)="DEFCON 1")),IF(J8&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J8&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J8&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
-        <v/>
+        <v>7.953443258971872E-2</v>
+      </c>
+      <c r="R8" s="90" t="str">
+        <f>IF(AND(C8="Aktie",OR(LEFT(O8,1)="🔴",LEFT(N8,8)="DEFCON 1")),IF(J8&gt;'Parameter &amp; Regeln'!$B$65,"🚩 FLAG (gesperrt)",""),IF(J8&gt;'Parameter &amp; Regeln'!$B$65,"🛒 Nachkaufen",IF(J8&lt;-'Parameter &amp; Regeln'!$B$65,"⏸️ Über Ziel","")))</f>
+        <v>⏸️ Über Ziel</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>25</v>
@@ -2114,1117 +2631,1179 @@
         <v>22</v>
       </c>
       <c r="E9" s="9">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="F9" s="10">
-        <v>0</v>
+        <v>1366</v>
       </c>
       <c r="G9" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="11">
-        <f>'Parameter &amp; Regeln'!$B$60/'Parameter &amp; Regeln'!$B$4</f>
+        <v>8.4508000730010552E-2</v>
+      </c>
+      <c r="H9" s="6">
+        <f>VLOOKUP($B9,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE)/'Parameter &amp; Regeln'!$B$4</f>
         <v>7.953443258971872E-2</v>
       </c>
       <c r="I9" s="10">
         <f t="shared" si="1"/>
-        <v>1087.0893501454898</v>
+        <v>1285.6064985451019</v>
       </c>
       <c r="J9" s="10">
         <f t="shared" si="2"/>
-        <v>1087.0893501454898</v>
+        <v>-80.393501454898114</v>
       </c>
       <c r="K9" s="11">
         <f t="shared" si="3"/>
-        <v>-7.953443258971872E-2</v>
+        <v>4.9735681402918314E-3</v>
       </c>
       <c r="L9" s="8" t="str">
         <f>IF(C9="Aktie",IF(K9&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K9&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K9&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K9&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
-        <v>📈 Aufstocken</v>
+        <v>⚖️ Halten</v>
       </c>
       <c r="M9" s="12" t="str">
         <f>IF(C9="Aktie",IF(G9&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
         <v/>
       </c>
-      <c r="N9" s="89"/>
-      <c r="O9" s="89"/>
-      <c r="P9" s="69">
-        <f>IF(C9="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q9/SUMIFS($Q$5:$Q$23,$C$5:$C$23,"Aktie"),IFERROR(VLOOKUP(B9,'Parameter &amp; Regeln'!$A$56:$B$61,2,FALSE),0))</f>
+      <c r="N9" s="85"/>
+      <c r="O9" s="85"/>
+      <c r="P9" s="65">
+        <f>IF(C9="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q9/SUMIFS($Q$5:$Q$24,$C$5:$C$24,"Aktie"),IFERROR(VLOOKUP(B9,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE),0))</f>
         <v>82</v>
       </c>
-      <c r="Q9" s="62">
+      <c r="Q9" s="58">
         <f>IF(OR(C9="ETF",C9="Gold"),H9,IF(C9&lt;&gt;"Aktie",0,IF(OR(LEFT(O9,1)="🔴",LEFT(N9,8)="DEFCON 1"),0,IF(LEFT(N9,8)="DEFCON 2",IFERROR(VLOOKUP(B9,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B9,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
         <v>7.953443258971872E-2</v>
       </c>
-      <c r="R9" s="94" t="str">
-        <f>IF(AND(C9="Aktie",OR(LEFT(O9,1)="🔴",LEFT(N9,8)="DEFCON 1")),IF(J9&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J9&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J9&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
-        <v>🛒 Nachkaufen</v>
+      <c r="R9" s="90" t="str">
+        <f>IF(AND(C9="Aktie",OR(LEFT(O9,1)="🔴",LEFT(N9,8)="DEFCON 1")),IF(J9&gt;'Parameter &amp; Regeln'!$B$65,"🚩 FLAG (gesperrt)",""),IF(J9&gt;'Parameter &amp; Regeln'!$B$65,"🛒 Nachkaufen",IF(J9&lt;-'Parameter &amp; Regeln'!$B$65,"⏸️ Über Ziel","")))</f>
+        <v/>
       </c>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="14" t="s">
+      <c r="A10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="F10" s="16">
-        <v>196</v>
-      </c>
-      <c r="G10" s="17">
+      <c r="E10" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="F10" s="10">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
         <f t="shared" si="0"/>
-        <v>1.4339896518624306E-2</v>
-      </c>
-      <c r="H10" s="17">
-        <f>'Parameter &amp; Regeln'!$B$61/'Parameter &amp; Regeln'!$B$4</f>
-        <v>4.9466537342386034E-2</v>
-      </c>
-      <c r="I10" s="16">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6">
+        <f>VLOOKUP($B10,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE)/'Parameter &amp; Regeln'!$B$4</f>
+        <v>6.9835111542192047E-2</v>
+      </c>
+      <c r="I10" s="10">
         <f t="shared" si="1"/>
-        <v>676.11654704170712</v>
-      </c>
-      <c r="J10" s="16">
+        <v>1128.8252182347235</v>
+      </c>
+      <c r="J10" s="10">
         <f t="shared" si="2"/>
-        <v>480.11654704170712</v>
-      </c>
-      <c r="K10" s="17">
+        <v>1128.8252182347235</v>
+      </c>
+      <c r="K10" s="11">
         <f t="shared" si="3"/>
-        <v>-3.5126640823761726E-2</v>
-      </c>
-      <c r="L10" s="14" t="str">
+        <v>-6.9835111542192047E-2</v>
+      </c>
+      <c r="L10" s="8" t="str">
         <f>IF(C10="Aktie",IF(K10&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K10&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K10&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K10&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
         <v>📈 Aufstocken</v>
       </c>
-      <c r="M10" s="97" t="str">
+      <c r="M10" s="12" t="str">
         <f>IF(C10="Aktie",IF(G10&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
         <v/>
       </c>
-      <c r="N10" s="89"/>
-      <c r="O10" s="89"/>
-      <c r="P10" s="69">
-        <f>IF(C10="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q10/SUMIFS($Q$5:$Q$23,$C$5:$C$23,"Aktie"),IFERROR(VLOOKUP(B10,'Parameter &amp; Regeln'!$A$56:$B$61,2,FALSE),0))</f>
+      <c r="N10" s="85"/>
+      <c r="O10" s="85"/>
+      <c r="P10" s="65">
+        <f>IF(C10="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q10/SUMIFS($Q$5:$Q$24,$C$5:$C$24,"Aktie"),IFERROR(VLOOKUP(B10,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE),0))</f>
+        <v>72</v>
+      </c>
+      <c r="Q10" s="58">
+        <f>IF(OR(C10="ETF",C10="Gold"),H10,IF(C10&lt;&gt;"Aktie",0,IF(OR(LEFT(O10,1)="🔴",LEFT(N10,8)="DEFCON 1"),0,IF(LEFT(N10,8)="DEFCON 2",IFERROR(VLOOKUP(B10,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B10,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
+        <v>6.9835111542192047E-2</v>
+      </c>
+      <c r="R10" s="90" t="str">
+        <f>IF(AND(C10="Aktie",OR(LEFT(O10,1)="🔴",LEFT(N10,8)="DEFCON 1")),IF(J10&gt;'Parameter &amp; Regeln'!$B$65,"🚩 FLAG (gesperrt)",""),IF(J10&gt;'Parameter &amp; Regeln'!$B$65,"🛒 Nachkaufen",IF(J10&lt;-'Parameter &amp; Regeln'!$B$65,"⏸️ Über Ziel","")))</f>
+        <v>🛒 Nachkaufen</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.68</v>
+      </c>
+      <c r="F11" s="10">
+        <v>193</v>
+      </c>
+      <c r="G11" s="11">
+        <f t="shared" si="0"/>
+        <v>1.1940003031399733E-2</v>
+      </c>
+      <c r="H11" s="6">
+        <f>VLOOKUP($B11,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE)/'Parameter &amp; Regeln'!$B$4</f>
+        <v>4.9466537342386034E-2</v>
+      </c>
+      <c r="I11" s="10">
+        <f t="shared" si="1"/>
+        <v>799.58452958292924</v>
+      </c>
+      <c r="J11" s="10">
+        <f t="shared" si="2"/>
+        <v>606.58452958292924</v>
+      </c>
+      <c r="K11" s="11">
+        <f t="shared" si="3"/>
+        <v>-3.7526534310986299E-2</v>
+      </c>
+      <c r="L11" s="13" t="str">
+        <f>IF(C11="Aktie",IF(K11&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K11&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K11&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K11&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
+        <v>📈 Aufstocken</v>
+      </c>
+      <c r="M11" s="93" t="str">
+        <f>IF(C11="Aktie",IF(G11&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
+        <v/>
+      </c>
+      <c r="N11" s="85"/>
+      <c r="O11" s="85"/>
+      <c r="P11" s="65">
+        <f>IF(C11="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q11/SUMIFS($Q$5:$Q$24,$C$5:$C$24,"Aktie"),IFERROR(VLOOKUP(B11,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE),0))</f>
         <v>51</v>
       </c>
-      <c r="Q10" s="62">
-        <f>IF(OR(C10="ETF",C10="Gold"),H10,IF(C10&lt;&gt;"Aktie",0,IF(OR(LEFT(O10,1)="🔴",LEFT(N10,8)="DEFCON 1"),0,IF(LEFT(N10,8)="DEFCON 2",IFERROR(VLOOKUP(B10,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B10,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
+      <c r="Q11" s="58">
+        <f>IF(OR(C11="ETF",C11="Gold"),H11,IF(C11&lt;&gt;"Aktie",0,IF(OR(LEFT(O11,1)="🔴",LEFT(N11,8)="DEFCON 1"),0,IF(LEFT(N11,8)="DEFCON 2",IFERROR(VLOOKUP(B11,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B11,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
         <v>4.9466537342386034E-2</v>
       </c>
-      <c r="R10" s="94" t="str">
-        <f>IF(AND(C10="Aktie",OR(LEFT(O10,1)="🔴",LEFT(N10,8)="DEFCON 1")),IF(J10&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J10&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J10&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
+      <c r="R11" s="90" t="str">
+        <f>IF(AND(C11="Aktie",OR(LEFT(O11,1)="🔴",LEFT(N11,8)="DEFCON 1")),IF(J11&gt;'Parameter &amp; Regeln'!$B$65,"🚩 FLAG (gesperrt)",""),IF(J11&gt;'Parameter &amp; Regeln'!$B$65,"🛒 Nachkaufen",IF(J11&lt;-'Parameter &amp; Regeln'!$B$65,"⏸️ Über Ziel","")))</f>
         <v>🛒 Nachkaufen</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="63" t="s">
+    <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="64" t="s">
+      <c r="B12" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="64" t="s">
+      <c r="C12" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="64" t="s">
+      <c r="D12" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="65">
+      <c r="E12" s="61">
         <v>1</v>
       </c>
-      <c r="F11" s="66">
-        <v>381</v>
-      </c>
-      <c r="G11" s="67">
+      <c r="F12" s="62">
+        <v>367</v>
+      </c>
+      <c r="G12" s="63">
         <f t="shared" si="0"/>
-        <v>2.7875002926509494E-2</v>
-      </c>
-      <c r="H11" s="67">
+        <v>2.2704565349863742E-2</v>
+      </c>
+      <c r="H12" s="63">
         <f>'Parameter &amp; Regeln'!$B$35/'Parameter &amp; Regeln'!$B$4</f>
         <v>3.8797284190106696E-2</v>
       </c>
-      <c r="I11" s="66">
+      <c r="I12" s="62">
         <f t="shared" si="1"/>
-        <v>530.28748787584868</v>
-      </c>
-      <c r="J11" s="66">
+        <v>627.12512124151317</v>
+      </c>
+      <c r="J12" s="62">
         <f t="shared" si="2"/>
-        <v>149.28748787584868</v>
-      </c>
-      <c r="K11" s="67">
+        <v>260.12512124151317</v>
+      </c>
+      <c r="K12" s="63">
         <f t="shared" si="3"/>
-        <v>-1.0922281263597202E-2</v>
-      </c>
-      <c r="L11" s="64" t="str">
-        <f>IF(C11="Aktie",IF(K11&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K11&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K11&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K11&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
+        <v>-1.6092718840242954E-2</v>
+      </c>
+      <c r="L12" s="60" t="str">
+        <f>IF(C12="Aktie",IF(K12&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K12&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K12&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K12&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
         <v>⚖️ Halten</v>
       </c>
-      <c r="M11" s="78" t="str">
-        <f>IF(C11="Aktie",IF(G11&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
+      <c r="M12" s="74" t="str">
+        <f>IF(C12="Aktie",IF(G12&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
         <v>✅ OK</v>
       </c>
-      <c r="N11" s="84" t="s">
+      <c r="N12" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="O11" s="84" t="s">
+      <c r="O12" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="P11" s="69">
-        <f>IF(C11="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q11/SUMIFS($Q$5:$Q$23,$C$5:$C$23,"Aktie"),IFERROR(VLOOKUP(B11,'Parameter &amp; Regeln'!$A$56:$B$61,2,FALSE),0))</f>
+      <c r="P12" s="65">
+        <f>IF(C12="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q12/SUMIFS($Q$5:$Q$24,$C$5:$C$24,"Aktie"),IFERROR(VLOOKUP(B12,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE),0))</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="62">
-        <f>IF(OR(C11="ETF",C11="Gold"),H11,IF(C11&lt;&gt;"Aktie",0,IF(OR(LEFT(O11,1)="🔴",LEFT(N11,8)="DEFCON 1"),0,IF(LEFT(N11,8)="DEFCON 2",IFERROR(VLOOKUP(B11,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B11,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
+      <c r="Q12" s="58">
+        <f>IF(OR(C12="ETF",C12="Gold"),H12,IF(C12&lt;&gt;"Aktie",0,IF(OR(LEFT(O12,1)="🔴",LEFT(N12,8)="DEFCON 1"),0,IF(LEFT(N12,8)="DEFCON 2",IFERROR(VLOOKUP(B12,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B12,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
         <v>0</v>
       </c>
-      <c r="R11" s="95" t="str">
-        <f>IF(AND(C11="Aktie",OR(LEFT(O11,1)="🔴",LEFT(N11,8)="DEFCON 1")),IF(J11&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J11&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J11&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
+      <c r="R12" s="91" t="str">
+        <f>IF(AND(C12="Aktie",OR(LEFT(O12,1)="🔴",LEFT(N12,8)="DEFCON 1")),IF(J12&gt;'Parameter &amp; Regeln'!$B$65,"🚩 FLAG (gesperrt)",""),IF(J12&gt;'Parameter &amp; Regeln'!$B$65,"🛒 Nachkaufen",IF(J12&lt;-'Parameter &amp; Regeln'!$B$65,"⏸️ Über Ziel","")))</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="79" t="s">
+    <row r="13" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="80" t="s">
+      <c r="B13" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="80" t="s">
+      <c r="C13" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="80" t="s">
+      <c r="D13" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="81">
+      <c r="E13" s="77">
         <v>1</v>
       </c>
-      <c r="F12" s="68">
-        <v>343</v>
-      </c>
-      <c r="G12" s="82">
+      <c r="F13" s="64">
+        <v>369</v>
+      </c>
+      <c r="G13" s="78">
         <f t="shared" si="0"/>
-        <v>2.5094818907592537E-2</v>
-      </c>
-      <c r="H12" s="82">
+        <v>2.2828295951225399E-2</v>
+      </c>
+      <c r="H13" s="78">
         <f>'Parameter &amp; Regeln'!$B$37/'Parameter &amp; Regeln'!$B$4</f>
         <v>1.7458777885548012E-2</v>
       </c>
-      <c r="I12" s="68">
+      <c r="I13" s="64">
         <f t="shared" si="1"/>
-        <v>238.62936954413192</v>
-      </c>
-      <c r="J12" s="68">
+        <v>282.20630455868087</v>
+      </c>
+      <c r="J13" s="64">
         <f t="shared" si="2"/>
-        <v>-104.37063045586808</v>
-      </c>
-      <c r="K12" s="82">
+        <v>-86.79369544131913</v>
+      </c>
+      <c r="K13" s="78">
         <f t="shared" si="3"/>
-        <v>7.6360410220445256E-3</v>
-      </c>
-      <c r="L12" s="80" t="str">
-        <f>IF(C12="Aktie",IF(K12&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K12&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K12&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K12&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
+        <v>5.3695180656773873E-3</v>
+      </c>
+      <c r="L13" s="76" t="str">
+        <f>IF(C13="Aktie",IF(K13&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K13&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K13&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K13&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
         <v>⚖️ Halten</v>
       </c>
-      <c r="M12" s="83" t="str">
-        <f>IF(C12="Aktie",IF(G12&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
+      <c r="M13" s="79" t="str">
+        <f>IF(C13="Aktie",IF(G13&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
         <v>✅ OK</v>
       </c>
-      <c r="N12" s="85" t="s">
+      <c r="N13" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="O12" s="84" t="s">
+      <c r="O13" s="80" t="s">
         <v>43</v>
       </c>
-      <c r="P12" s="69">
-        <f>IF(C12="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q12/SUMIFS($Q$5:$Q$23,$C$5:$C$23,"Aktie"),IFERROR(VLOOKUP(B12,'Parameter &amp; Regeln'!$A$56:$B$61,2,FALSE),0))</f>
+      <c r="P13" s="65">
+        <f>IF(C13="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q13/SUMIFS($Q$5:$Q$24,$C$5:$C$24,"Aktie"),IFERROR(VLOOKUP(B13,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE),0))</f>
         <v>0</v>
       </c>
-      <c r="Q12" s="62">
-        <f>IF(OR(C12="ETF",C12="Gold"),H12,IF(C12&lt;&gt;"Aktie",0,IF(OR(LEFT(O12,1)="🔴",LEFT(N12,8)="DEFCON 1"),0,IF(LEFT(N12,8)="DEFCON 2",IFERROR(VLOOKUP(B12,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B12,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
+      <c r="Q13" s="58">
+        <f>IF(OR(C13="ETF",C13="Gold"),H13,IF(C13&lt;&gt;"Aktie",0,IF(OR(LEFT(O13,1)="🔴",LEFT(N13,8)="DEFCON 1"),0,IF(LEFT(N13,8)="DEFCON 2",IFERROR(VLOOKUP(B13,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B13,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
         <v>0</v>
       </c>
-      <c r="R12" s="96" t="str">
-        <f>IF(AND(C12="Aktie",OR(LEFT(O12,1)="🔴",LEFT(N12,8)="DEFCON 1")),IF(J12&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J12&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J12&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
+      <c r="R13" s="92" t="str">
+        <f>IF(AND(C13="Aktie",OR(LEFT(O13,1)="🔴",LEFT(N13,8)="DEFCON 1")),IF(J13&gt;'Parameter &amp; Regeln'!$B$65,"🚩 FLAG (gesperrt)",""),IF(J13&gt;'Parameter &amp; Regeln'!$B$65,"🛒 Nachkaufen",IF(J13&lt;-'Parameter &amp; Regeln'!$B$65,"⏸️ Über Ziel","")))</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="63" t="s">
+    <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="64" t="s">
+      <c r="B14" s="60" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="64" t="s">
+      <c r="C14" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="64" t="s">
+      <c r="D14" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="65">
+      <c r="E14" s="61">
         <v>0</v>
       </c>
-      <c r="F13" s="66">
-        <v>519</v>
-      </c>
-      <c r="G13" s="67">
+      <c r="F14" s="62">
+        <v>557</v>
+      </c>
+      <c r="G14" s="63">
         <f t="shared" si="0"/>
-        <v>3.7971460679418444E-2</v>
-      </c>
-      <c r="H13" s="67">
+        <v>3.4458972479220994E-2</v>
+      </c>
+      <c r="H14" s="63">
         <f>'Parameter &amp; Regeln'!$B$36/'Parameter &amp; Regeln'!$B$4</f>
         <v>3.1037827352085354E-2</v>
       </c>
-      <c r="I13" s="66">
+      <c r="I14" s="62">
         <f t="shared" si="1"/>
-        <v>424.22999030067894</v>
-      </c>
-      <c r="J13" s="66">
+        <v>501.70009699321048</v>
+      </c>
+      <c r="J14" s="62">
         <f t="shared" si="2"/>
-        <v>-94.770009699321065</v>
-      </c>
-      <c r="K13" s="67">
+        <v>-55.299903006789521</v>
+      </c>
+      <c r="K14" s="63">
         <f t="shared" si="3"/>
-        <v>6.9336333273330893E-3</v>
-      </c>
-      <c r="L13" s="64" t="str">
-        <f>IF(C13="Aktie",IF(K13&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K13&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K13&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K13&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
+        <v>3.4211451271356393E-3</v>
+      </c>
+      <c r="L14" s="60" t="str">
+        <f>IF(C14="Aktie",IF(K14&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K14&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K14&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K14&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
         <v>⚖️ Halten</v>
       </c>
-      <c r="M13" s="78" t="str">
-        <f>IF(C13="Aktie",IF(G13&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
+      <c r="M14" s="74" t="str">
+        <f>IF(C14="Aktie",IF(G14&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
         <v>✅ OK</v>
       </c>
-      <c r="N13" s="86" t="s">
+      <c r="N14" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="O13" s="87" t="s">
+      <c r="O14" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="P13" s="69">
-        <f>IF(C13="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q13/SUMIFS($Q$5:$Q$23,$C$5:$C$23,"Aktie"),IFERROR(VLOOKUP(B13,'Parameter &amp; Regeln'!$A$56:$B$61,2,FALSE),0))</f>
+      <c r="P14" s="65">
+        <f>IF(C14="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q14/SUMIFS($Q$5:$Q$24,$C$5:$C$24,"Aktie"),IFERROR(VLOOKUP(B14,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE),0))</f>
         <v>55.45798095238095</v>
       </c>
-      <c r="Q13" s="62">
-        <f>IF(OR(C13="ETF",C13="Gold"),H13,IF(C13&lt;&gt;"Aktie",0,IF(OR(LEFT(O13,1)="🔴",LEFT(N13,8)="DEFCON 1"),0,IF(LEFT(N13,8)="DEFCON 2",IFERROR(VLOOKUP(B13,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B13,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
+      <c r="Q14" s="58">
+        <f>IF(OR(C14="ETF",C14="Gold"),H14,IF(C14&lt;&gt;"Aktie",0,IF(OR(LEFT(O14,1)="🔴",LEFT(N14,8)="DEFCON 1"),0,IF(LEFT(N14,8)="DEFCON 2",IFERROR(VLOOKUP(B14,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B14,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
         <v>32</v>
       </c>
-      <c r="R13" s="95" t="str">
-        <f>IF(AND(C13="Aktie",OR(LEFT(O13,1)="🔴",LEFT(N13,8)="DEFCON 1")),IF(J13&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J13&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J13&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
+      <c r="R14" s="91" t="str">
+        <f>IF(AND(C14="Aktie",OR(LEFT(O14,1)="🔴",LEFT(N14,8)="DEFCON 1")),IF(J14&gt;'Parameter &amp; Regeln'!$B$65,"🚩 FLAG (gesperrt)",""),IF(J14&gt;'Parameter &amp; Regeln'!$B$65,"🛒 Nachkaufen",IF(J14&lt;-'Parameter &amp; Regeln'!$B$65,"⏸️ Über Ziel","")))</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="79" t="s">
+    <row r="15" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="80" t="s">
+      <c r="B15" s="76" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="80" t="s">
+      <c r="C15" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="80" t="s">
+      <c r="D15" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="81">
+      <c r="E15" s="77">
         <v>1</v>
       </c>
-      <c r="F14" s="68">
-        <v>448</v>
-      </c>
-      <c r="G14" s="82">
+      <c r="F15" s="64">
+        <v>446</v>
+      </c>
+      <c r="G15" s="78">
         <f t="shared" si="0"/>
-        <v>3.2776906328284131E-2</v>
-      </c>
-      <c r="H14" s="82">
+        <v>2.7591924103649124E-2</v>
+      </c>
+      <c r="H15" s="78">
         <f>'Parameter &amp; Regeln'!$B$37/'Parameter &amp; Regeln'!$B$4</f>
         <v>1.7458777885548012E-2</v>
       </c>
-      <c r="I14" s="68">
+      <c r="I15" s="64">
         <f t="shared" si="1"/>
-        <v>238.62936954413192</v>
-      </c>
-      <c r="J14" s="68">
+        <v>282.20630455868087</v>
+      </c>
+      <c r="J15" s="64">
         <f t="shared" si="2"/>
-        <v>-209.37063045586808</v>
-      </c>
-      <c r="K14" s="82">
+        <v>-163.79369544131913</v>
+      </c>
+      <c r="K15" s="78">
         <f t="shared" si="3"/>
-        <v>1.5318128442736119E-2</v>
-      </c>
-      <c r="L14" s="80" t="str">
-        <f>IF(C14="Aktie",IF(K14&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K14&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K14&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K14&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
+        <v>1.0133146218101113E-2</v>
+      </c>
+      <c r="L15" s="76" t="str">
+        <f>IF(C15="Aktie",IF(K15&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K15&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K15&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K15&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
         <v>⚖️ Halten</v>
       </c>
-      <c r="M14" s="83" t="str">
-        <f>IF(C14="Aktie",IF(G14&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
+      <c r="M15" s="79" t="str">
+        <f>IF(C15="Aktie",IF(G15&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
         <v>✅ OK</v>
       </c>
-      <c r="N14" s="86" t="s">
+      <c r="N15" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="O14" s="86" t="s">
+      <c r="O15" s="82" t="s">
         <v>51</v>
       </c>
-      <c r="P14" s="69">
-        <f>IF(C14="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q14/SUMIFS($Q$5:$Q$23,$C$5:$C$23,"Aktie"),IFERROR(VLOOKUP(B14,'Parameter &amp; Regeln'!$A$56:$B$61,2,FALSE),0))</f>
+      <c r="P15" s="65">
+        <f>IF(C15="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q15/SUMIFS($Q$5:$Q$24,$C$5:$C$24,"Aktie"),IFERROR(VLOOKUP(B15,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE),0))</f>
         <v>31.195114285714286</v>
       </c>
-      <c r="Q14" s="62">
-        <f>IF(OR(C14="ETF",C14="Gold"),H14,IF(C14&lt;&gt;"Aktie",0,IF(OR(LEFT(O14,1)="🔴",LEFT(N14,8)="DEFCON 1"),0,IF(LEFT(N14,8)="DEFCON 2",IFERROR(VLOOKUP(B14,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B14,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
+      <c r="Q15" s="58">
+        <f>IF(OR(C15="ETF",C15="Gold"),H15,IF(C15&lt;&gt;"Aktie",0,IF(OR(LEFT(O15,1)="🔴",LEFT(N15,8)="DEFCON 1"),0,IF(LEFT(N15,8)="DEFCON 2",IFERROR(VLOOKUP(B15,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B15,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
         <v>18</v>
       </c>
-      <c r="R14" s="96" t="str">
-        <f>IF(AND(C14="Aktie",OR(LEFT(O14,1)="🔴",LEFT(N14,8)="DEFCON 1")),IF(J14&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J14&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J14&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
+      <c r="R15" s="92" t="str">
+        <f>IF(AND(C15="Aktie",OR(LEFT(O15,1)="🔴",LEFT(N15,8)="DEFCON 1")),IF(J15&gt;'Parameter &amp; Regeln'!$B$65,"🚩 FLAG (gesperrt)",""),IF(J15&gt;'Parameter &amp; Regeln'!$B$65,"🛒 Nachkaufen",IF(J15&lt;-'Parameter &amp; Regeln'!$B$65,"⏸️ Über Ziel","")))</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="63" t="s">
+    <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="64" t="s">
+      <c r="B16" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="64" t="s">
+      <c r="C16" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="64" t="s">
+      <c r="D16" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="65">
+      <c r="E16" s="61">
         <v>1</v>
       </c>
-      <c r="F15" s="66">
-        <v>486</v>
-      </c>
-      <c r="G15" s="67">
+      <c r="F16" s="62">
+        <v>464</v>
+      </c>
+      <c r="G16" s="63">
         <f t="shared" si="0"/>
-        <v>3.5557090347201087E-2</v>
-      </c>
-      <c r="H15" s="67">
+        <v>2.8705499515904023E-2</v>
+      </c>
+      <c r="H16" s="63">
         <f>'Parameter &amp; Regeln'!$B$35/'Parameter &amp; Regeln'!$B$4</f>
         <v>3.8797284190106696E-2</v>
       </c>
-      <c r="I15" s="66">
+      <c r="I16" s="62">
         <f t="shared" si="1"/>
-        <v>530.28748787584868</v>
-      </c>
-      <c r="J15" s="66">
+        <v>627.12512124151317</v>
+      </c>
+      <c r="J16" s="62">
         <f t="shared" si="2"/>
-        <v>44.287487875848683</v>
-      </c>
-      <c r="K15" s="67">
+        <v>163.12512124151317</v>
+      </c>
+      <c r="K16" s="63">
         <f t="shared" si="3"/>
-        <v>-3.2401938429056087E-3</v>
-      </c>
-      <c r="L15" s="64" t="str">
-        <f>IF(C15="Aktie",IF(K15&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K15&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K15&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K15&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
+        <v>-1.0091784674202672E-2</v>
+      </c>
+      <c r="L16" s="60" t="str">
+        <f>IF(C16="Aktie",IF(K16&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K16&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K16&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K16&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
         <v>⚖️ Halten</v>
       </c>
-      <c r="M15" s="78" t="str">
-        <f>IF(C15="Aktie",IF(G15&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
+      <c r="M16" s="74" t="str">
+        <f>IF(C16="Aktie",IF(G16&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
         <v>✅ OK</v>
       </c>
-      <c r="N15" s="85" t="s">
+      <c r="N16" s="81" t="s">
         <v>54</v>
       </c>
-      <c r="O15" s="84" t="s">
+      <c r="O16" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="P15" s="69">
-        <f>IF(C15="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q15/SUMIFS($Q$5:$Q$23,$C$5:$C$23,"Aktie"),IFERROR(VLOOKUP(B15,'Parameter &amp; Regeln'!$A$56:$B$61,2,FALSE),0))</f>
+      <c r="P16" s="65">
+        <f>IF(C16="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q16/SUMIFS($Q$5:$Q$24,$C$5:$C$24,"Aktie"),IFERROR(VLOOKUP(B16,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE),0))</f>
         <v>0</v>
       </c>
-      <c r="Q15" s="62">
-        <f>IF(OR(C15="ETF",C15="Gold"),H15,IF(C15&lt;&gt;"Aktie",0,IF(OR(LEFT(O15,1)="🔴",LEFT(N15,8)="DEFCON 1"),0,IF(LEFT(N15,8)="DEFCON 2",IFERROR(VLOOKUP(B15,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B15,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
+      <c r="Q16" s="58">
+        <f>IF(OR(C16="ETF",C16="Gold"),H16,IF(C16&lt;&gt;"Aktie",0,IF(OR(LEFT(O16,1)="🔴",LEFT(N16,8)="DEFCON 1"),0,IF(LEFT(N16,8)="DEFCON 2",IFERROR(VLOOKUP(B16,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B16,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
         <v>0</v>
       </c>
-      <c r="R15" s="95" t="str">
-        <f>IF(AND(C15="Aktie",OR(LEFT(O15,1)="🔴",LEFT(N15,8)="DEFCON 1")),IF(J15&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J15&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J15&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
+      <c r="R16" s="91" t="str">
+        <f>IF(AND(C16="Aktie",OR(LEFT(O16,1)="🔴",LEFT(N16,8)="DEFCON 1")),IF(J16&gt;'Parameter &amp; Regeln'!$B$65,"🚩 FLAG (gesperrt)",""),IF(J16&gt;'Parameter &amp; Regeln'!$B$65,"🛒 Nachkaufen",IF(J16&lt;-'Parameter &amp; Regeln'!$B$65,"⏸️ Über Ziel","")))</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="79" t="s">
+    <row r="17" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="80" t="s">
+      <c r="B17" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="80" t="s">
+      <c r="C17" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="80" t="s">
+      <c r="D17" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="81">
+      <c r="E17" s="77">
         <v>0</v>
       </c>
-      <c r="F16" s="68">
-        <v>410</v>
-      </c>
-      <c r="G16" s="82">
+      <c r="F17" s="64">
+        <v>425</v>
+      </c>
+      <c r="G17" s="78">
         <f t="shared" si="0"/>
-        <v>2.9996722309367171E-2</v>
-      </c>
-      <c r="H16" s="82">
+        <v>2.6292752789351746E-2</v>
+      </c>
+      <c r="H17" s="78">
         <f>'Parameter &amp; Regeln'!$B$37/'Parameter &amp; Regeln'!$B$4</f>
         <v>1.7458777885548012E-2</v>
       </c>
-      <c r="I16" s="68">
+      <c r="I17" s="64">
         <f t="shared" si="1"/>
-        <v>238.62936954413192</v>
-      </c>
-      <c r="J16" s="68">
+        <v>282.20630455868087</v>
+      </c>
+      <c r="J17" s="64">
         <f t="shared" si="2"/>
-        <v>-171.37063045586808</v>
-      </c>
-      <c r="K16" s="82">
+        <v>-142.79369544131913</v>
+      </c>
+      <c r="K17" s="78">
         <f t="shared" si="3"/>
-        <v>1.2537944423819159E-2</v>
-      </c>
-      <c r="L16" s="80" t="str">
-        <f>IF(C16="Aktie",IF(K16&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K16&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K16&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K16&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
+        <v>8.8339749038037346E-3</v>
+      </c>
+      <c r="L17" s="76" t="str">
+        <f>IF(C17="Aktie",IF(K17&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K17&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K17&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K17&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
         <v>⚖️ Halten</v>
       </c>
-      <c r="M16" s="83" t="str">
-        <f>IF(C16="Aktie",IF(G16&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
+      <c r="M17" s="79" t="str">
+        <f>IF(C17="Aktie",IF(G17&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
         <v>✅ OK</v>
       </c>
-      <c r="N16" s="86" t="s">
+      <c r="N17" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="O16" s="86" t="s">
+      <c r="O17" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="69">
-        <f>IF(C16="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q16/SUMIFS($Q$5:$Q$23,$C$5:$C$23,"Aktie"),IFERROR(VLOOKUP(B16,'Parameter &amp; Regeln'!$A$56:$B$61,2,FALSE),0))</f>
+      <c r="P17" s="65">
+        <f>IF(C17="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q17/SUMIFS($Q$5:$Q$24,$C$5:$C$24,"Aktie"),IFERROR(VLOOKUP(B17,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE),0))</f>
         <v>31.195114285714286</v>
       </c>
-      <c r="Q16" s="62">
-        <f>IF(OR(C16="ETF",C16="Gold"),H16,IF(C16&lt;&gt;"Aktie",0,IF(OR(LEFT(O16,1)="🔴",LEFT(N16,8)="DEFCON 1"),0,IF(LEFT(N16,8)="DEFCON 2",IFERROR(VLOOKUP(B16,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B16,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
+      <c r="Q17" s="58">
+        <f>IF(OR(C17="ETF",C17="Gold"),H17,IF(C17&lt;&gt;"Aktie",0,IF(OR(LEFT(O17,1)="🔴",LEFT(N17,8)="DEFCON 1"),0,IF(LEFT(N17,8)="DEFCON 2",IFERROR(VLOOKUP(B17,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B17,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
         <v>18</v>
       </c>
-      <c r="R16" s="96" t="str">
-        <f>IF(AND(C16="Aktie",OR(LEFT(O16,1)="🔴",LEFT(N16,8)="DEFCON 1")),IF(J16&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J16&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J16&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
+      <c r="R17" s="92" t="str">
+        <f>IF(AND(C17="Aktie",OR(LEFT(O17,1)="🔴",LEFT(N17,8)="DEFCON 1")),IF(J17&gt;'Parameter &amp; Regeln'!$B$65,"🚩 FLAG (gesperrt)",""),IF(J17&gt;'Parameter &amp; Regeln'!$B$65,"🛒 Nachkaufen",IF(J17&lt;-'Parameter &amp; Regeln'!$B$65,"⏸️ Über Ziel","")))</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="63" t="s">
+    <row r="18" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="64" t="s">
+      <c r="B18" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="64" t="s">
+      <c r="C18" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="64" t="s">
+      <c r="D18" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="65">
+      <c r="E18" s="61">
         <v>0</v>
       </c>
-      <c r="F17" s="66">
+      <c r="F18" s="62">
         <v>0</v>
       </c>
-      <c r="G17" s="67">
+      <c r="G18" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H17" s="67">
+      <c r="H18" s="63">
         <f>'Parameter &amp; Regeln'!$B$36/'Parameter &amp; Regeln'!$B$4</f>
         <v>3.1037827352085354E-2</v>
       </c>
-      <c r="I17" s="66">
+      <c r="I18" s="62">
         <f t="shared" si="1"/>
-        <v>424.22999030067894</v>
-      </c>
-      <c r="J17" s="66">
+        <v>501.70009699321048</v>
+      </c>
+      <c r="J18" s="62">
         <f t="shared" si="2"/>
-        <v>424.22999030067894</v>
-      </c>
-      <c r="K17" s="67">
+        <v>501.70009699321048</v>
+      </c>
+      <c r="K18" s="63">
         <f t="shared" si="3"/>
         <v>-3.1037827352085354E-2</v>
       </c>
-      <c r="L17" s="64" t="str">
-        <f>IF(C17="Aktie",IF(K17&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K17&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K17&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K17&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
+      <c r="L18" s="60" t="str">
+        <f>IF(C18="Aktie",IF(K18&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K18&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K18&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K18&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
         <v>⚖️ Halten</v>
       </c>
-      <c r="M17" s="78" t="str">
-        <f>IF(C17="Aktie",IF(G17&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
+      <c r="M18" s="74" t="str">
+        <f>IF(C18="Aktie",IF(G18&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
         <v>✅ OK</v>
       </c>
-      <c r="N17" s="86" t="s">
+      <c r="N18" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="O17" s="86" t="s">
+      <c r="O18" s="82" t="s">
         <v>51</v>
       </c>
-      <c r="P17" s="69">
-        <f>IF(C17="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q17/SUMIFS($Q$5:$Q$23,$C$5:$C$23,"Aktie"),IFERROR(VLOOKUP(B17,'Parameter &amp; Regeln'!$A$56:$B$61,2,FALSE),0))</f>
+      <c r="P18" s="65">
+        <f>IF(C18="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q18/SUMIFS($Q$5:$Q$24,$C$5:$C$24,"Aktie"),IFERROR(VLOOKUP(B18,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE),0))</f>
         <v>55.45798095238095</v>
       </c>
-      <c r="Q17" s="62">
-        <f>IF(OR(C17="ETF",C17="Gold"),H17,IF(C17&lt;&gt;"Aktie",0,IF(OR(LEFT(O17,1)="🔴",LEFT(N17,8)="DEFCON 1"),0,IF(LEFT(N17,8)="DEFCON 2",IFERROR(VLOOKUP(B17,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B17,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
+      <c r="Q18" s="58">
+        <f>IF(OR(C18="ETF",C18="Gold"),H18,IF(C18&lt;&gt;"Aktie",0,IF(OR(LEFT(O18,1)="🔴",LEFT(N18,8)="DEFCON 1"),0,IF(LEFT(N18,8)="DEFCON 2",IFERROR(VLOOKUP(B18,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B18,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
         <v>32</v>
       </c>
-      <c r="R17" s="95" t="str">
-        <f>IF(AND(C17="Aktie",OR(LEFT(O17,1)="🔴",LEFT(N17,8)="DEFCON 1")),IF(J17&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J17&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J17&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
+      <c r="R18" s="91" t="str">
+        <f>IF(AND(C18="Aktie",OR(LEFT(O18,1)="🔴",LEFT(N18,8)="DEFCON 1")),IF(J18&gt;'Parameter &amp; Regeln'!$B$65,"🚩 FLAG (gesperrt)",""),IF(J18&gt;'Parameter &amp; Regeln'!$B$65,"🛒 Nachkaufen",IF(J18&lt;-'Parameter &amp; Regeln'!$B$65,"⏸️ Über Ziel","")))</f>
         <v>🛒 Nachkaufen</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="79" t="s">
+    <row r="19" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="75" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="80" t="s">
+      <c r="B19" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="80" t="s">
+      <c r="C19" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="80" t="s">
+      <c r="D19" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="81">
+      <c r="E19" s="77">
         <v>1</v>
       </c>
-      <c r="F18" s="68">
-        <v>425</v>
-      </c>
-      <c r="G18" s="82">
+      <c r="F19" s="64">
+        <v>400</v>
+      </c>
+      <c r="G19" s="78">
         <f t="shared" si="0"/>
-        <v>3.1094163369465969E-2</v>
-      </c>
-      <c r="H18" s="82">
+        <v>2.4746120272331053E-2</v>
+      </c>
+      <c r="H19" s="78">
         <f>'Parameter &amp; Regeln'!$B$35/'Parameter &amp; Regeln'!$B$4</f>
         <v>3.8797284190106696E-2</v>
       </c>
-      <c r="I18" s="68">
+      <c r="I19" s="64">
         <f t="shared" si="1"/>
-        <v>530.28748787584868</v>
-      </c>
-      <c r="J18" s="68">
+        <v>627.12512124151317</v>
+      </c>
+      <c r="J19" s="64">
         <f t="shared" si="2"/>
-        <v>105.28748787584868</v>
-      </c>
-      <c r="K18" s="82">
+        <v>227.12512124151317</v>
+      </c>
+      <c r="K19" s="78">
         <f t="shared" si="3"/>
-        <v>-7.7031208206407263E-3</v>
-      </c>
-      <c r="L18" s="80" t="str">
-        <f>IF(C18="Aktie",IF(K18&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K18&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K18&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K18&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
+        <v>-1.4051163917775642E-2</v>
+      </c>
+      <c r="L19" s="76" t="str">
+        <f>IF(C19="Aktie",IF(K19&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K19&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K19&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K19&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
         <v>⚖️ Halten</v>
       </c>
-      <c r="M18" s="83" t="str">
-        <f>IF(C18="Aktie",IF(G18&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
+      <c r="M19" s="79" t="str">
+        <f>IF(C19="Aktie",IF(G19&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
         <v>✅ OK</v>
       </c>
-      <c r="N18" s="85" t="s">
+      <c r="N19" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="O18" s="84" t="s">
+      <c r="O19" s="80" t="s">
         <v>66</v>
       </c>
-      <c r="P18" s="69">
-        <f>IF(C18="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q18/SUMIFS($Q$5:$Q$23,$C$5:$C$23,"Aktie"),IFERROR(VLOOKUP(B18,'Parameter &amp; Regeln'!$A$56:$B$61,2,FALSE),0))</f>
+      <c r="P19" s="65">
+        <f>IF(C19="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q19/SUMIFS($Q$5:$Q$24,$C$5:$C$24,"Aktie"),IFERROR(VLOOKUP(B19,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE),0))</f>
         <v>0</v>
       </c>
-      <c r="Q18" s="62">
-        <f>IF(OR(C18="ETF",C18="Gold"),H18,IF(C18&lt;&gt;"Aktie",0,IF(OR(LEFT(O18,1)="🔴",LEFT(N18,8)="DEFCON 1"),0,IF(LEFT(N18,8)="DEFCON 2",IFERROR(VLOOKUP(B18,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B18,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
+      <c r="Q19" s="58">
+        <f>IF(OR(C19="ETF",C19="Gold"),H19,IF(C19&lt;&gt;"Aktie",0,IF(OR(LEFT(O19,1)="🔴",LEFT(N19,8)="DEFCON 1"),0,IF(LEFT(N19,8)="DEFCON 2",IFERROR(VLOOKUP(B19,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B19,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
         <v>0</v>
       </c>
-      <c r="R18" s="96" t="str">
-        <f>IF(AND(C18="Aktie",OR(LEFT(O18,1)="🔴",LEFT(N18,8)="DEFCON 1")),IF(J18&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J18&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J18&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
+      <c r="R19" s="92" t="str">
+        <f>IF(AND(C19="Aktie",OR(LEFT(O19,1)="🔴",LEFT(N19,8)="DEFCON 1")),IF(J19&gt;'Parameter &amp; Regeln'!$B$65,"🚩 FLAG (gesperrt)",""),IF(J19&gt;'Parameter &amp; Regeln'!$B$65,"🛒 Nachkaufen",IF(J19&lt;-'Parameter &amp; Regeln'!$B$65,"⏸️ Über Ziel","")))</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="63" t="s">
+    <row r="20" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="64" t="s">
+      <c r="B20" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="64" t="s">
+      <c r="C20" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="64" t="s">
+      <c r="D20" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="65">
+      <c r="E20" s="61">
         <v>0</v>
       </c>
-      <c r="F19" s="66">
-        <v>418</v>
-      </c>
-      <c r="G19" s="67">
+      <c r="F20" s="62">
+        <v>410</v>
+      </c>
+      <c r="G20" s="63">
         <f t="shared" si="0"/>
-        <v>3.058202420808653E-2</v>
-      </c>
-      <c r="H19" s="67">
+        <v>2.536477327913933E-2</v>
+      </c>
+      <c r="H20" s="63">
         <f>'Parameter &amp; Regeln'!$B$37/'Parameter &amp; Regeln'!$B$4</f>
         <v>1.7458777885548012E-2</v>
       </c>
-      <c r="I19" s="66">
+      <c r="I20" s="62">
         <f t="shared" si="1"/>
-        <v>238.62936954413192</v>
-      </c>
-      <c r="J19" s="66">
+        <v>282.20630455868087</v>
+      </c>
+      <c r="J20" s="62">
         <f t="shared" si="2"/>
-        <v>-179.37063045586808</v>
-      </c>
-      <c r="K19" s="67">
+        <v>-127.79369544131913</v>
+      </c>
+      <c r="K20" s="63">
         <f t="shared" si="3"/>
-        <v>1.3123246322538518E-2</v>
-      </c>
-      <c r="L19" s="64" t="str">
-        <f>IF(C19="Aktie",IF(K19&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K19&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K19&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K19&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
+        <v>7.9059953935913183E-3</v>
+      </c>
+      <c r="L20" s="60" t="str">
+        <f>IF(C20="Aktie",IF(K20&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K20&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K20&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K20&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
         <v>⚖️ Halten</v>
       </c>
-      <c r="M19" s="78" t="str">
-        <f>IF(C19="Aktie",IF(G19&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
+      <c r="M20" s="74" t="str">
+        <f>IF(C20="Aktie",IF(G20&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
         <v>✅ OK</v>
       </c>
-      <c r="N19" s="86" t="s">
+      <c r="N20" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="O19" s="86" t="s">
+      <c r="O20" s="82" t="s">
         <v>51</v>
       </c>
-      <c r="P19" s="69">
-        <f>IF(C19="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q19/SUMIFS($Q$5:$Q$23,$C$5:$C$23,"Aktie"),IFERROR(VLOOKUP(B19,'Parameter &amp; Regeln'!$A$56:$B$61,2,FALSE),0))</f>
+      <c r="P20" s="65">
+        <f>IF(C20="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q20/SUMIFS($Q$5:$Q$24,$C$5:$C$24,"Aktie"),IFERROR(VLOOKUP(B20,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE),0))</f>
         <v>31.195114285714286</v>
       </c>
-      <c r="Q19" s="62">
-        <f>IF(OR(C19="ETF",C19="Gold"),H19,IF(C19&lt;&gt;"Aktie",0,IF(OR(LEFT(O19,1)="🔴",LEFT(N19,8)="DEFCON 1"),0,IF(LEFT(N19,8)="DEFCON 2",IFERROR(VLOOKUP(B19,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B19,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
+      <c r="Q20" s="58">
+        <f>IF(OR(C20="ETF",C20="Gold"),H20,IF(C20&lt;&gt;"Aktie",0,IF(OR(LEFT(O20,1)="🔴",LEFT(N20,8)="DEFCON 1"),0,IF(LEFT(N20,8)="DEFCON 2",IFERROR(VLOOKUP(B20,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B20,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
         <v>18</v>
       </c>
-      <c r="R19" s="95" t="str">
-        <f>IF(AND(C19="Aktie",OR(LEFT(O19,1)="🔴",LEFT(N19,8)="DEFCON 1")),IF(J19&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J19&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J19&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
+      <c r="R20" s="91" t="str">
+        <f>IF(AND(C20="Aktie",OR(LEFT(O20,1)="🔴",LEFT(N20,8)="DEFCON 1")),IF(J20&gt;'Parameter &amp; Regeln'!$B$65,"🚩 FLAG (gesperrt)",""),IF(J20&gt;'Parameter &amp; Regeln'!$B$65,"🛒 Nachkaufen",IF(J20&lt;-'Parameter &amp; Regeln'!$B$65,"⏸️ Über Ziel","")))</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="79" t="s">
+    <row r="21" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="80" t="s">
+      <c r="B21" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="80" t="s">
+      <c r="C21" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="80" t="s">
+      <c r="D21" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="81">
+      <c r="E21" s="77">
         <v>1</v>
       </c>
-      <c r="F20" s="68">
-        <v>451</v>
-      </c>
-      <c r="G20" s="82">
+      <c r="F21" s="64">
+        <v>924</v>
+      </c>
+      <c r="G21" s="78">
         <f t="shared" si="0"/>
-        <v>3.299639454030389E-2</v>
-      </c>
-      <c r="H20" s="82">
+        <v>5.7163537829084732E-2</v>
+      </c>
+      <c r="H21" s="78">
         <f>'Parameter &amp; Regeln'!$B$35/'Parameter &amp; Regeln'!$B$4</f>
         <v>3.8797284190106696E-2</v>
       </c>
-      <c r="I20" s="68">
+      <c r="I21" s="64">
         <f t="shared" si="1"/>
-        <v>530.28748787584868</v>
-      </c>
-      <c r="J20" s="68">
+        <v>627.12512124151317</v>
+      </c>
+      <c r="J21" s="64">
         <f t="shared" si="2"/>
-        <v>79.287487875848683</v>
-      </c>
-      <c r="K20" s="82">
+        <v>-296.87487875848683</v>
+      </c>
+      <c r="K21" s="78">
         <f t="shared" si="3"/>
-        <v>-5.8008896498028054E-3</v>
-      </c>
-      <c r="L20" s="80" t="str">
-        <f>IF(C20="Aktie",IF(K20&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K20&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K20&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K20&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
+        <v>1.8366253638978036E-2</v>
+      </c>
+      <c r="L21" s="76" t="str">
+        <f>IF(C21="Aktie",IF(K21&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K21&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K21&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K21&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
         <v>⚖️ Halten</v>
       </c>
-      <c r="M20" s="83" t="str">
-        <f>IF(C20="Aktie",IF(G20&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
+      <c r="M21" s="79" t="str">
+        <f>IF(C21="Aktie",IF(G21&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
         <v>✅ OK</v>
       </c>
-      <c r="N20" s="86" t="s">
+      <c r="N21" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="O20" s="86" t="s">
+      <c r="O21" s="82" t="s">
         <v>51</v>
       </c>
-      <c r="P20" s="69">
-        <f>IF(C20="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q20/SUMIFS($Q$5:$Q$23,$C$5:$C$23,"Aktie"),IFERROR(VLOOKUP(B20,'Parameter &amp; Regeln'!$A$56:$B$61,2,FALSE),0))</f>
+      <c r="P21" s="65">
+        <f>IF(C21="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q21/SUMIFS($Q$5:$Q$24,$C$5:$C$24,"Aktie"),IFERROR(VLOOKUP(B21,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE),0))</f>
         <v>69.322476190476181</v>
       </c>
-      <c r="Q20" s="62">
-        <f>IF(OR(C20="ETF",C20="Gold"),H20,IF(C20&lt;&gt;"Aktie",0,IF(OR(LEFT(O20,1)="🔴",LEFT(N20,8)="DEFCON 1"),0,IF(LEFT(N20,8)="DEFCON 2",IFERROR(VLOOKUP(B20,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B20,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
+      <c r="Q21" s="58">
+        <f>IF(OR(C21="ETF",C21="Gold"),H21,IF(C21&lt;&gt;"Aktie",0,IF(OR(LEFT(O21,1)="🔴",LEFT(N21,8)="DEFCON 1"),0,IF(LEFT(N21,8)="DEFCON 2",IFERROR(VLOOKUP(B21,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B21,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
         <v>40</v>
       </c>
-      <c r="R20" s="96" t="str">
-        <f>IF(AND(C20="Aktie",OR(LEFT(O20,1)="🔴",LEFT(N20,8)="DEFCON 1")),IF(J20&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J20&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J20&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
+      <c r="R21" s="92" t="str">
+        <f>IF(AND(C21="Aktie",OR(LEFT(O21,1)="🔴",LEFT(N21,8)="DEFCON 1")),IF(J21&gt;'Parameter &amp; Regeln'!$B$65,"🚩 FLAG (gesperrt)",""),IF(J21&gt;'Parameter &amp; Regeln'!$B$65,"🛒 Nachkaufen",IF(J21&lt;-'Parameter &amp; Regeln'!$B$65,"⏸️ Über Ziel","")))</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="63" t="s">
+    <row r="22" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="59" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="64" t="s">
+      <c r="B22" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="64" t="s">
+      <c r="C22" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="64" t="s">
+      <c r="D22" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="65">
+      <c r="E22" s="61">
         <v>1</v>
       </c>
-      <c r="F21" s="66">
+      <c r="F22" s="62">
         <v>396</v>
       </c>
-      <c r="G21" s="67">
+      <c r="G22" s="63">
         <f t="shared" si="0"/>
-        <v>2.8972443986608292E-2</v>
-      </c>
-      <c r="H21" s="67">
+        <v>2.4498659069607742E-2</v>
+      </c>
+      <c r="H22" s="63">
         <f>'Parameter &amp; Regeln'!$B$37/'Parameter &amp; Regeln'!$B$4</f>
         <v>1.7458777885548012E-2</v>
       </c>
-      <c r="I21" s="66">
+      <c r="I22" s="62">
         <f t="shared" si="1"/>
-        <v>238.62936954413192</v>
-      </c>
-      <c r="J21" s="66">
+        <v>282.20630455868087</v>
+      </c>
+      <c r="J22" s="62">
         <f t="shared" si="2"/>
-        <v>-157.37063045586808</v>
-      </c>
-      <c r="K21" s="67">
+        <v>-113.79369544131913</v>
+      </c>
+      <c r="K22" s="63">
         <f t="shared" si="3"/>
-        <v>1.151366610106028E-2</v>
-      </c>
-      <c r="L21" s="64" t="str">
-        <f>IF(C21="Aktie",IF(K21&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K21&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K21&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K21&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
+        <v>7.0398811840597306E-3</v>
+      </c>
+      <c r="L22" s="60" t="str">
+        <f>IF(C22="Aktie",IF(K22&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K22&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K22&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K22&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
         <v>⚖️ Halten</v>
       </c>
-      <c r="M21" s="78" t="str">
-        <f>IF(C21="Aktie",IF(G21&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
+      <c r="M22" s="74" t="str">
+        <f>IF(C22="Aktie",IF(G22&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
         <v>✅ OK</v>
       </c>
-      <c r="N21" s="86" t="s">
+      <c r="N22" s="82" t="s">
         <v>74</v>
       </c>
-      <c r="O21" s="87" t="s">
+      <c r="O22" s="83" t="s">
         <v>75</v>
       </c>
-      <c r="P21" s="69">
-        <f>IF(C21="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q21/SUMIFS($Q$5:$Q$23,$C$5:$C$23,"Aktie"),IFERROR(VLOOKUP(B21,'Parameter &amp; Regeln'!$A$56:$B$61,2,FALSE),0))</f>
+      <c r="P22" s="65">
+        <f>IF(C22="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q22/SUMIFS($Q$5:$Q$24,$C$5:$C$24,"Aktie"),IFERROR(VLOOKUP(B22,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE),0))</f>
         <v>31.195114285714286</v>
       </c>
-      <c r="Q21" s="62">
-        <f>IF(OR(C21="ETF",C21="Gold"),H21,IF(C21&lt;&gt;"Aktie",0,IF(OR(LEFT(O21,1)="🔴",LEFT(N21,8)="DEFCON 1"),0,IF(LEFT(N21,8)="DEFCON 2",IFERROR(VLOOKUP(B21,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B21,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
+      <c r="Q22" s="58">
+        <f>IF(OR(C22="ETF",C22="Gold"),H22,IF(C22&lt;&gt;"Aktie",0,IF(OR(LEFT(O22,1)="🔴",LEFT(N22,8)="DEFCON 1"),0,IF(LEFT(N22,8)="DEFCON 2",IFERROR(VLOOKUP(B22,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B22,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
         <v>18</v>
       </c>
-      <c r="R21" s="95" t="str">
-        <f>IF(AND(C21="Aktie",OR(LEFT(O21,1)="🔴",LEFT(N21,8)="DEFCON 1")),IF(J21&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J21&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J21&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
+      <c r="R22" s="91" t="str">
+        <f>IF(AND(C22="Aktie",OR(LEFT(O22,1)="🔴",LEFT(N22,8)="DEFCON 1")),IF(J22&gt;'Parameter &amp; Regeln'!$B$65,"🚩 FLAG (gesperrt)",""),IF(J22&gt;'Parameter &amp; Regeln'!$B$65,"🛒 Nachkaufen",IF(J22&lt;-'Parameter &amp; Regeln'!$B$65,"⏸️ Über Ziel","")))</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="79" t="s">
+    <row r="23" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="75" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="80" t="s">
+      <c r="B23" s="76" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="80" t="s">
+      <c r="C23" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="80" t="s">
+      <c r="D23" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="81">
+      <c r="E23" s="77">
         <v>1</v>
       </c>
-      <c r="F22" s="68">
-        <v>475</v>
-      </c>
-      <c r="G22" s="82">
+      <c r="F23" s="64">
+        <v>481</v>
+      </c>
+      <c r="G23" s="78">
         <f t="shared" si="0"/>
-        <v>3.4752300236461968E-2</v>
-      </c>
-      <c r="H22" s="82">
+        <v>2.9757209627478094E-2</v>
+      </c>
+      <c r="H23" s="78">
         <f>'Parameter &amp; Regeln'!$B$36/'Parameter &amp; Regeln'!$B$4</f>
         <v>3.1037827352085354E-2</v>
       </c>
-      <c r="I22" s="68">
+      <c r="I23" s="64">
         <f t="shared" si="1"/>
-        <v>424.22999030067894</v>
-      </c>
-      <c r="J22" s="68">
+        <v>501.70009699321048</v>
+      </c>
+      <c r="J23" s="64">
         <f t="shared" si="2"/>
-        <v>-50.770009699321065</v>
-      </c>
-      <c r="K22" s="82">
+        <v>20.700096993210479</v>
+      </c>
+      <c r="K23" s="78">
         <f t="shared" si="3"/>
-        <v>3.7144728843766135E-3</v>
-      </c>
-      <c r="L22" s="80" t="str">
-        <f>IF(C22="Aktie",IF(K22&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K22&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K22&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K22&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
+        <v>-1.2806177246072609E-3</v>
+      </c>
+      <c r="L23" s="76" t="str">
+        <f>IF(C23="Aktie",IF(K23&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K23&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K23&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K23&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
         <v>⚖️ Halten</v>
       </c>
-      <c r="M22" s="83" t="str">
-        <f>IF(C22="Aktie",IF(G22&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
+      <c r="M23" s="79" t="str">
+        <f>IF(C23="Aktie",IF(G23&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
         <v>✅ OK</v>
       </c>
-      <c r="N22" s="85" t="s">
+      <c r="N23" s="81" t="s">
         <v>78</v>
       </c>
-      <c r="O22" s="85" t="s">
+      <c r="O23" s="81" t="s">
         <v>79</v>
       </c>
-      <c r="P22" s="69">
-        <f>IF(C22="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q22/SUMIFS($Q$5:$Q$23,$C$5:$C$23,"Aktie"),IFERROR(VLOOKUP(B22,'Parameter &amp; Regeln'!$A$56:$B$61,2,FALSE),0))</f>
+      <c r="P23" s="65">
+        <f>IF(C23="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q23/SUMIFS($Q$5:$Q$24,$C$5:$C$24,"Aktie"),IFERROR(VLOOKUP(B23,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE),0))</f>
         <v>27.728990476190475</v>
       </c>
-      <c r="Q22" s="62">
-        <f>IF(OR(C22="ETF",C22="Gold"),H22,IF(C22&lt;&gt;"Aktie",0,IF(OR(LEFT(O22,1)="🔴",LEFT(N22,8)="DEFCON 1"),0,IF(LEFT(N22,8)="DEFCON 2",IFERROR(VLOOKUP(B22,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B22,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
+      <c r="Q23" s="58">
+        <f>IF(OR(C23="ETF",C23="Gold"),H23,IF(C23&lt;&gt;"Aktie",0,IF(OR(LEFT(O23,1)="🔴",LEFT(N23,8)="DEFCON 1"),0,IF(LEFT(N23,8)="DEFCON 2",IFERROR(VLOOKUP(B23,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B23,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
         <v>16</v>
       </c>
-      <c r="R22" s="96" t="str">
-        <f>IF(AND(C22="Aktie",OR(LEFT(O22,1)="🔴",LEFT(N22,8)="DEFCON 1")),IF(J22&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J22&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J22&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
+      <c r="R23" s="92" t="str">
+        <f>IF(AND(C23="Aktie",OR(LEFT(O23,1)="🔴",LEFT(N23,8)="DEFCON 1")),IF(J23&gt;'Parameter &amp; Regeln'!$B$65,"🚩 FLAG (gesperrt)",""),IF(J23&gt;'Parameter &amp; Regeln'!$B$65,"🛒 Nachkaufen",IF(J23&lt;-'Parameter &amp; Regeln'!$B$65,"⏸️ Über Ziel","")))</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="63" t="s">
+    <row r="24" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="59" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="64" t="s">
+      <c r="B24" s="60" t="s">
         <v>81</v>
       </c>
-      <c r="C23" s="64" t="s">
+      <c r="C24" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="64" t="s">
+      <c r="D24" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="E23" s="65">
+      <c r="E24" s="61">
         <v>1</v>
       </c>
-      <c r="F23" s="66">
-        <v>472</v>
-      </c>
-      <c r="G23" s="67">
+      <c r="F24" s="62">
+        <v>434</v>
+      </c>
+      <c r="G24" s="63">
         <f t="shared" si="0"/>
-        <v>3.4532812024442208E-2</v>
-      </c>
-      <c r="H23" s="67">
+        <v>2.6849540495479194E-2</v>
+      </c>
+      <c r="H24" s="63">
         <f>'Parameter &amp; Regeln'!$B$37/'Parameter &amp; Regeln'!$B$4</f>
         <v>1.7458777885548012E-2</v>
       </c>
-      <c r="I23" s="66">
+      <c r="I24" s="62">
         <f t="shared" si="1"/>
-        <v>238.62936954413192</v>
-      </c>
-      <c r="J23" s="66">
+        <v>282.20630455868087</v>
+      </c>
+      <c r="J24" s="62">
         <f t="shared" si="2"/>
-        <v>-233.37063045586808</v>
-      </c>
-      <c r="K23" s="67">
+        <v>-151.79369544131913</v>
+      </c>
+      <c r="K24" s="63">
         <f t="shared" si="3"/>
-        <v>1.7074034138894197E-2</v>
-      </c>
-      <c r="L23" s="64" t="str">
-        <f>IF(C23="Aktie",IF(K23&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K23&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K23&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K23&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
+        <v>9.3907626099311824E-3</v>
+      </c>
+      <c r="L24" s="60" t="str">
+        <f>IF(C24="Aktie",IF(K24&gt;'Parameter &amp; Regeln'!B$9,"📉 Reduzieren",IF(K24&lt;-'Parameter &amp; Regeln'!B$9,"📈 Aufstocken","⚖️ Halten")),IF(K24&gt;'Parameter &amp; Regeln'!B$8,"📉 Reduzieren",IF(K24&lt;-'Parameter &amp; Regeln'!B$8,"📈 Aufstocken","⚖️ Halten")))</f>
         <v>⚖️ Halten</v>
       </c>
-      <c r="M23" s="78" t="str">
-        <f>IF(C23="Aktie",IF(G23&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
+      <c r="M24" s="74" t="str">
+        <f>IF(C24="Aktie",IF(G24&gt;'Parameter &amp; Regeln'!B$10,"🚨 ÜBER CAP","✅ OK"),"")</f>
         <v>✅ OK</v>
       </c>
-      <c r="N23" s="86" t="s">
+      <c r="N24" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="O23" s="86" t="s">
+      <c r="O24" s="82" t="s">
         <v>51</v>
       </c>
-      <c r="P23" s="69">
-        <f>IF(C23="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q23/SUMIFS($Q$5:$Q$23,$C$5:$C$23,"Aktie"),IFERROR(VLOOKUP(B23,'Parameter &amp; Regeln'!$A$56:$B$61,2,FALSE),0))</f>
+      <c r="P24" s="65">
+        <f>IF(C24="Aktie",'Parameter &amp; Regeln'!$B$4*'Parameter &amp; Regeln'!$B$6*Q24/SUMIFS($Q$5:$Q$24,$C$5:$C$24,"Aktie"),IFERROR(VLOOKUP(B24,'Parameter &amp; Regeln'!$A$56:$B$62,2,FALSE),0))</f>
         <v>31.195114285714286</v>
       </c>
-      <c r="Q23" s="62">
-        <f>IF(OR(C23="ETF",C23="Gold"),H23,IF(C23&lt;&gt;"Aktie",0,IF(OR(LEFT(O23,1)="🔴",LEFT(N23,8)="DEFCON 1"),0,IF(LEFT(N23,8)="DEFCON 2",IFERROR(VLOOKUP(B23,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B23,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
+      <c r="Q24" s="58">
+        <f>IF(OR(C24="ETF",C24="Gold"),H24,IF(C24&lt;&gt;"Aktie",0,IF(OR(LEFT(O24,1)="🔴",LEFT(N24,8)="DEFCON 1"),0,IF(LEFT(N24,8)="DEFCON 2",IFERROR(VLOOKUP(B24,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)*'Parameter &amp; Regeln'!$B$27,IFERROR(VLOOKUP(B24,'Parameter &amp; Regeln'!$A$41:$C$53,3,FALSE),0)))))</f>
         <v>18</v>
       </c>
-      <c r="R23" s="95" t="str">
-        <f>IF(AND(C23="Aktie",OR(LEFT(O23,1)="🔴",LEFT(N23,8)="DEFCON 1")),IF(J23&gt;'Parameter &amp; Regeln'!$B$64,"🚩 FLAG (gesperrt)",""),IF(J23&gt;'Parameter &amp; Regeln'!$B$64,"🛒 Nachkaufen",IF(J23&lt;-'Parameter &amp; Regeln'!$B$64,"⏸️ Über Ziel","")))</f>
+      <c r="R24" s="91" t="str">
+        <f>IF(AND(C24="Aktie",OR(LEFT(O24,1)="🔴",LEFT(N24,8)="DEFCON 1")),IF(J24&gt;'Parameter &amp; Regeln'!$B$65,"🚩 FLAG (gesperrt)",""),IF(J24&gt;'Parameter &amp; Regeln'!$B$65,"🛒 Nachkaufen",IF(J24&lt;-'Parameter &amp; Regeln'!$B$65,"⏸️ Über Ziel","")))</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
+    <row r="25" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="20">
-        <f>SUM(F5:F23)</f>
-        <v>12637.16</v>
-      </c>
-      <c r="G24" s="21">
-        <f>SUM(G5:G23)</f>
-        <v>0.92456921780254253</v>
-      </c>
-      <c r="H24" s="21">
-        <f>SUM(H5:H23)</f>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="16">
+        <f>SUM(F5:F24)</f>
+        <v>15133.15</v>
+      </c>
+      <c r="G25" s="17">
+        <f>SUM(G5:G24)</f>
+        <v>0.93621687499806661</v>
+      </c>
+      <c r="H25" s="17">
+        <f>SUM(H5:H24)</f>
         <v>1.0000000000000002</v>
       </c>
-      <c r="I24" s="20">
-        <f>SUM(I5:I23)</f>
-        <v>13668.160000000003</v>
-      </c>
-      <c r="J24" s="20">
-        <f>ROUND(SUM(J5:J23),2)</f>
+      <c r="I25" s="16">
+        <f>SUM(I5:I24)</f>
+        <v>16164.15</v>
+      </c>
+      <c r="J25" s="16">
+        <f>ROUND(SUM(J5:J24),2)</f>
         <v>1031</v>
       </c>
-      <c r="K24" s="21">
-        <f t="array" ref="K24">SUMPRODUCT((C5:C23="Aktie")*ABS(K5:K23))/COUNTIF(C5:C23,"Aktie")</f>
-        <v>1.1273498430141091E-2</v>
-      </c>
-      <c r="L24" s="18" t="s">
+      <c r="K25" s="17">
+        <f t="array" ref="K25">SUMPRODUCT((C5:C24="Aktie")*ABS(K5:K24))/COUNTIF(C5:C24,"Aktie")</f>
+        <v>1.1001137665399386E-2</v>
+      </c>
+      <c r="L25" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="M24" s="22">
-        <f>COUNTIF(M5:M23,"🚨 ÜBER CAP")</f>
+      <c r="M25" s="18">
+        <f>COUNTIF(M5:M24,"🚨 ÜBER CAP")</f>
         <v>0</v>
       </c>
-      <c r="N24" s="23">
-        <f>COUNTIF(N5:N23,"DEFCON 1*")+COUNTIF(N5:N23,"DEFCON 2*")+COUNTIF(N5:N23,"DEFCON 3*")</f>
+      <c r="N25" s="19">
+        <f>COUNTIF(N5:N24,"DEFCON 1*")+COUNTIF(N5:N24,"DEFCON 2*")+COUNTIF(N5:N24,"DEFCON 3*")</f>
         <v>13</v>
       </c>
-      <c r="O24" s="23">
-        <f>COUNTIF(O5:O23,"🚩*")+COUNTIF(O5:O23,"🔴*")</f>
+      <c r="O25" s="19">
+        <f>COUNTIF(O5:O24,"🚩*")+COUNTIF(O5:O24,"🔴*")</f>
         <v>4</v>
       </c>
-      <c r="P24" s="20">
-        <f>SUMIF(C5:C23,"Aktie",P5:P23)+SUMIF(C5:C23,"&lt;&gt;Aktie",P5:P23)</f>
+      <c r="P25" s="16">
+        <f>SUMIF(C5:C24,"Aktie",P5:P24)+SUMIF(C5:C24,"&lt;&gt;Aktie",P5:P24)</f>
         <v>1030.943</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K25" s="24">
-        <f t="array" ref="K25">SUMPRODUCT((C5:C23&lt;&gt;"Aktie")*ABS(K5:K23))/COUNTIF(C5:C23,"&lt;&gt;Aktie")</f>
-        <v>3.0199988405231831E-2</v>
-      </c>
-      <c r="L25" s="25" t="s">
+    <row r="26" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K26" s="20">
+        <f t="array" ref="K26">SUMPRODUCT((C5:C24&lt;&gt;"Aktie")*ABS(K5:K24))/COUNTIF(C5:C24,"&lt;&gt;Aktie")</f>
+        <v>3.5091824931223356E-2</v>
+      </c>
+      <c r="L26" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="M25" s="26">
-        <f>COUNTIF(M5:M10,"🚨 ÜBER CAP")</f>
+      <c r="M26" s="22">
+        <f>COUNTIF(M5:M11,"🚨 ÜBER CAP")</f>
         <v>0</v>
       </c>
-      <c r="N25" s="27" t="s">
+      <c r="N26" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="O25" s="27" t="s">
+      <c r="O26" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="P25" s="28" t="s">
+      <c r="P26" s="24" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="29" t="s">
+    <row r="27" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="F26" s="30">
-        <v>567.88</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="31" t="s">
+      <c r="F27" s="26">
+        <v>74.3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="F27" s="32">
+      <c r="F28" s="28">
         <v>1031</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="29" t="s">
+    <row r="29" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="F28" s="33">
-        <f>F24 + F27</f>
-        <v>13668.16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A29" s="31" t="s">
+      <c r="F29" s="29">
+        <f>F25 + F28</f>
+        <v>16164.15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="F29" s="34">
-        <f>SUMIFS(P5:P23,D5:D23,"ING")</f>
-        <v>380</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" s="70" t="s">
+      <c r="F30" s="30">
+        <f>SUMIFS(P5:P24,D5:D24,"ING")</f>
+        <v>411</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="F30" s="71">
-        <f>IF((F27-F29)&lt;=0,0,F26/(F27-F29))</f>
-        <v>0.87231950844854067</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32" s="76" t="s">
+      <c r="F31" s="67">
+        <f>IF((F28-F30)&lt;=0,0,F27/(F28-F30))</f>
+        <v>0.11983870967741934</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="72" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="91" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="B33" s="92" t="s">
+      <c r="B34" s="88" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="91" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="87" t="s">
         <v>96</v>
       </c>
-      <c r="B34" s="92" t="s">
+      <c r="B35" s="88" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="91" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="87" t="s">
         <v>98</v>
       </c>
-      <c r="B35" s="92" t="s">
+      <c r="B36" s="88" t="s">
         <v>99</v>
       </c>
     </row>
@@ -3233,74 +3812,146 @@
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
-  <conditionalFormatting sqref="L5:L23">
-    <cfRule type="expression" dxfId="17" priority="23">
+  <conditionalFormatting sqref="L5:L24">
+    <cfRule type="expression" dxfId="20" priority="23">
       <formula>NOT(ISERROR(SEARCH("Reduzieren",L5)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="24">
+    <cfRule type="expression" dxfId="19" priority="24">
       <formula>NOT(ISERROR(SEARCH("Aufstocken",L5)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="25">
+    <cfRule type="expression" dxfId="18" priority="25">
       <formula>NOT(ISERROR(SEARCH("Halten",L5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M5:M23">
-    <cfRule type="expression" dxfId="14" priority="5">
+  <conditionalFormatting sqref="M5:M24">
+    <cfRule type="expression" dxfId="17" priority="5">
       <formula>NOT(ISERROR(SEARCH("ÜBER CAP",M5)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="6">
+    <cfRule type="expression" dxfId="16" priority="6">
       <formula>NOT(ISERROR(SEARCH("OK",M5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N11:N23">
-    <cfRule type="containsText" dxfId="12" priority="26" operator="containsText" text="DEFCON 1">
-      <formula>NOT(ISERROR(SEARCH("DEFCON 1",N11)))</formula>
+  <conditionalFormatting sqref="N12:N24">
+    <cfRule type="containsText" dxfId="15" priority="26" operator="containsText" text="DEFCON 1">
+      <formula>NOT(ISERROR(SEARCH("DEFCON 1",N12)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="27" operator="containsText" text="DEFCON 2">
-      <formula>NOT(ISERROR(SEARCH("DEFCON 2",N11)))</formula>
+    <cfRule type="containsText" dxfId="14" priority="27" operator="containsText" text="DEFCON 2">
+      <formula>NOT(ISERROR(SEARCH("DEFCON 2",N12)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="28" operator="containsText" text="DEFCON 3">
-      <formula>NOT(ISERROR(SEARCH("DEFCON 3",N11)))</formula>
+    <cfRule type="containsText" dxfId="13" priority="28" operator="containsText" text="DEFCON 3">
+      <formula>NOT(ISERROR(SEARCH("DEFCON 3",N12)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O11:O23">
-    <cfRule type="containsText" dxfId="9" priority="29" operator="containsText" text="🔴">
-      <formula>NOT(ISERROR(SEARCH("🔴",O11)))</formula>
+  <conditionalFormatting sqref="O12:O24">
+    <cfRule type="containsText" dxfId="12" priority="29" operator="containsText" text="🔴">
+      <formula>NOT(ISERROR(SEARCH("🔴",O12)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="30" operator="containsText" text="🟠">
-      <formula>NOT(ISERROR(SEARCH("🟠",O11)))</formula>
+    <cfRule type="containsText" dxfId="11" priority="30" operator="containsText" text="🟠">
+      <formula>NOT(ISERROR(SEARCH("🟠",O12)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="31" operator="containsText" text="🟡">
-      <formula>NOT(ISERROR(SEARCH("🟡",O11)))</formula>
+    <cfRule type="containsText" dxfId="10" priority="31" operator="containsText" text="🟡">
+      <formula>NOT(ISERROR(SEARCH("🟡",O12)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="32" operator="containsText" text="✅">
-      <formula>NOT(ISERROR(SEARCH("✅",O11)))</formula>
+    <cfRule type="containsText" dxfId="9" priority="32" operator="containsText" text="✅">
+      <formula>NOT(ISERROR(SEARCH("✅",O12)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P5:P23">
-    <cfRule type="expression" dxfId="5" priority="15">
+  <conditionalFormatting sqref="P5:P24">
+    <cfRule type="expression" dxfId="8" priority="15">
       <formula>P5=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R5:R23">
-    <cfRule type="containsText" dxfId="4" priority="33" operator="containsText" text="Nachkaufen">
+  <conditionalFormatting sqref="R5:R24">
+    <cfRule type="containsText" dxfId="7" priority="33" operator="containsText" text="Nachkaufen">
       <formula>NOT(ISERROR(SEARCH("Nachkaufen",R5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="34" operator="containsText" text="Über Ziel">
+    <cfRule type="containsText" dxfId="6" priority="34" operator="containsText" text="Über Ziel">
       <formula>NOT(ISERROR(SEARCH("Über Ziel",R5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="35" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="5" priority="35" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",R5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
+  <conditionalFormatting sqref="H25">
+    <cfRule type="expression" dxfId="1" priority="36">
+      <formula>ABS($H$25-1)&gt;0.0001</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5:K24">
+    <cfRule type="dataBar" priority="38">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{7A9732FD-B1B0-40D3-8F5A-E481BF5616DC}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Ungültiger Typ" error="Nur Gold, ETF oder Aktie erlaubt." sqref="C5:C24" xr:uid="{7BBAE249-DC07-473B-93ED-32DF2122CB22}">
+      <formula1>"Gold,ETF,Aktie"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Ungültiger Broker" error="Nur ING oder Scalable erlaubt." sqref="D5:D24" xr:uid="{E9FCDCE6-16FB-49C7-88E6-DF223F55E5A2}">
+      <formula1>"ING,Scalable"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Ungültiger US-Faktor" error="US-Faktor muss zwischen 0 und 1 liegen." sqref="E5:E24" xr:uid="{87105C34-BD03-4305-8A18-F6D5176B04FF}">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation type="custom" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="DEFCON-Format prüfen" error="Eintrag muss mit 'DEFCON 1'..'DEFCON 4' beginnen." sqref="N5:N24" xr:uid="{690ECAB1-1577-4948-A9D4-6370A8C8E719}">
+      <formula1>OR(N5="",LEFT(N5,8)="DEFCON 1",LEFT(N5,8)="DEFCON 2",LEFT(N5,8)="DEFCON 3",LEFT(N5,8)="DEFCON 4")</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.30555555555555558" bottom="0.30555555555555558" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="23" orientation="landscape" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="37" id="{E5E8FAB5-D9F8-40E5-83DD-80D526E99FBA}">
+            <xm:f>ABS($J$25-'Parameter &amp; Regeln'!$B$4)&gt;0.5</xm:f>
+            <x14:dxf>
+              <font>
+                <b/>
+                <i val="0"/>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor indexed="64"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>J25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{7A9732FD-B1B0-40D3-8F5A-E481BF5616DC}">
+            <x14:dataBar minLength="0" maxLength="100" direction="leftToRight" axisPosition="middle">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="max"/>
+              <x14:negativeFillColor rgb="FFFF555A"/>
+              <x14:axisColor rgb="FF808080"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>K5:K24</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" customWidth="1"/>
@@ -3311,501 +3962,523 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="31" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="32" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="37" t="str">
+      <c r="A4" s="33" t="str">
         <f>'Portfolio &amp; Rebalancing'!A5</f>
         <v>EUWAX Gold</v>
       </c>
-      <c r="B4" s="38" t="str">
+      <c r="B4" s="34" t="str">
         <f>'Portfolio &amp; Rebalancing'!B5</f>
         <v>EWG2</v>
       </c>
-      <c r="C4" s="39">
+      <c r="C4" s="35">
         <f>'Portfolio &amp; Rebalancing'!F5</f>
-        <v>659</v>
-      </c>
-      <c r="D4" s="40">
+        <v>630</v>
+      </c>
+      <c r="D4" s="36">
         <f>'Portfolio &amp; Rebalancing'!E5</f>
         <v>0</v>
       </c>
-      <c r="E4" s="39">
-        <f t="shared" ref="E4:E22" si="0">C4*D4</f>
+      <c r="E4" s="35">
+        <f t="shared" ref="E4:E23" si="0">C4*D4</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="str">
+      <c r="A5" s="33" t="str">
         <f>'Portfolio &amp; Rebalancing'!A6</f>
         <v>iShares Core MSCI World</v>
       </c>
-      <c r="B5" s="38" t="str">
+      <c r="B5" s="34" t="str">
         <f>'Portfolio &amp; Rebalancing'!B6</f>
         <v>IWDA</v>
       </c>
-      <c r="C5" s="39">
+      <c r="C5" s="35">
         <f>'Portfolio &amp; Rebalancing'!F6</f>
-        <v>3930.74</v>
-      </c>
-      <c r="D5" s="40">
+        <v>3943.46</v>
+      </c>
+      <c r="D5" s="36">
         <f>'Portfolio &amp; Rebalancing'!E6</f>
         <v>0.7</v>
       </c>
-      <c r="E5" s="39">
+      <c r="E5" s="35">
         <f t="shared" si="0"/>
-        <v>2751.5179999999996</v>
+        <v>2760.422</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="37" t="str">
+      <c r="A6" s="33" t="str">
         <f>'Portfolio &amp; Rebalancing'!A7</f>
         <v>iShares Core MSCI EM IMI</v>
       </c>
-      <c r="B6" s="38" t="str">
+      <c r="B6" s="34" t="str">
         <f>'Portfolio &amp; Rebalancing'!B7</f>
         <v>EIMI</v>
       </c>
-      <c r="C6" s="39">
+      <c r="C6" s="35">
         <f>'Portfolio &amp; Rebalancing'!F7</f>
-        <v>1292.42</v>
-      </c>
-      <c r="D6" s="40">
+        <v>1349.52</v>
+      </c>
+      <c r="D6" s="36">
         <f>'Portfolio &amp; Rebalancing'!E7</f>
         <v>0</v>
       </c>
-      <c r="E6" s="39">
+      <c r="E6" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="37" t="str">
+      <c r="A7" s="33" t="str">
         <f>'Portfolio &amp; Rebalancing'!A8</f>
+        <v>Xtrackers MSCI World ex USA</v>
+      </c>
+      <c r="B7" s="34" t="str">
+        <f>'Portfolio &amp; Rebalancing'!B8</f>
+        <v>EXUS</v>
+      </c>
+      <c r="C7" s="35">
+        <f>'Portfolio &amp; Rebalancing'!F8</f>
+        <v>1978.17</v>
+      </c>
+      <c r="D7" s="36">
+        <f>'Portfolio &amp; Rebalancing'!E8</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="35">
+        <f t="shared" ref="E7" si="1">C7*D7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="33" t="str">
+        <f>'Portfolio &amp; Rebalancing'!A9</f>
         <v>Avantis Global Small Cap Value</v>
       </c>
-      <c r="B7" s="38" t="str">
-        <f>'Portfolio &amp; Rebalancing'!B8</f>
+      <c r="B8" s="34" t="str">
+        <f>'Portfolio &amp; Rebalancing'!B9</f>
         <v>AVGC</v>
       </c>
-      <c r="C7" s="39">
-        <f>'Portfolio &amp; Rebalancing'!F8</f>
-        <v>1335</v>
-      </c>
-      <c r="D7" s="40">
-        <f>'Portfolio &amp; Rebalancing'!E8</f>
+      <c r="C8" s="35">
+        <f>'Portfolio &amp; Rebalancing'!F9</f>
+        <v>1366</v>
+      </c>
+      <c r="D8" s="36">
+        <f>'Portfolio &amp; Rebalancing'!E9</f>
         <v>0.67</v>
       </c>
-      <c r="E7" s="39">
+      <c r="E8" s="35">
         <f t="shared" si="0"/>
-        <v>894.45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="37" t="str">
-        <f>'Portfolio &amp; Rebalancing'!A9</f>
+        <v>915.22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="33" t="str">
+        <f>'Portfolio &amp; Rebalancing'!A10</f>
         <v>VanEck Space Innovators</v>
       </c>
-      <c r="B8" s="38" t="str">
-        <f>'Portfolio &amp; Rebalancing'!B9</f>
+      <c r="B9" s="34" t="str">
+        <f>'Portfolio &amp; Rebalancing'!B10</f>
         <v>JEDI</v>
       </c>
-      <c r="C8" s="39">
-        <f>'Portfolio &amp; Rebalancing'!F9</f>
+      <c r="C9" s="35">
+        <f>'Portfolio &amp; Rebalancing'!F10</f>
         <v>0</v>
       </c>
-      <c r="D8" s="40">
-        <f>'Portfolio &amp; Rebalancing'!E9</f>
+      <c r="D9" s="36">
+        <f>'Portfolio &amp; Rebalancing'!E10</f>
         <v>0.62</v>
       </c>
-      <c r="E8" s="39">
+      <c r="E9" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="str">
-        <f>'Portfolio &amp; Rebalancing'!A10</f>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="33" t="str">
+        <f>'Portfolio &amp; Rebalancing'!A11</f>
         <v>WisdomTree Quantum Computing</v>
       </c>
-      <c r="B9" s="38" t="str">
-        <f>'Portfolio &amp; Rebalancing'!B10</f>
+      <c r="B10" s="34" t="str">
+        <f>'Portfolio &amp; Rebalancing'!B11</f>
         <v>WQTM</v>
       </c>
-      <c r="C9" s="39">
-        <f>'Portfolio &amp; Rebalancing'!F10</f>
-        <v>196</v>
-      </c>
-      <c r="D9" s="40">
-        <f>'Portfolio &amp; Rebalancing'!E10</f>
+      <c r="C10" s="35">
+        <f>'Portfolio &amp; Rebalancing'!F11</f>
+        <v>193</v>
+      </c>
+      <c r="D10" s="36">
+        <f>'Portfolio &amp; Rebalancing'!E11</f>
         <v>0.68</v>
       </c>
-      <c r="E9" s="39">
+      <c r="E10" s="35">
         <f t="shared" si="0"/>
-        <v>133.28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="37" t="str">
-        <f>'Portfolio &amp; Rebalancing'!A11</f>
+        <v>131.24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="33" t="str">
+        <f>'Portfolio &amp; Rebalancing'!A12</f>
         <v>Amazon.com</v>
       </c>
-      <c r="B10" s="38" t="str">
-        <f>'Portfolio &amp; Rebalancing'!B11</f>
+      <c r="B11" s="34" t="str">
+        <f>'Portfolio &amp; Rebalancing'!B12</f>
         <v>AMZN</v>
       </c>
-      <c r="C10" s="39">
-        <f>'Portfolio &amp; Rebalancing'!F11</f>
-        <v>381</v>
-      </c>
-      <c r="D10" s="40">
-        <f>'Portfolio &amp; Rebalancing'!E11</f>
-        <v>1</v>
-      </c>
-      <c r="E10" s="39">
-        <f t="shared" si="0"/>
-        <v>381</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="37" t="str">
-        <f>'Portfolio &amp; Rebalancing'!A12</f>
-        <v>Amphenol</v>
-      </c>
-      <c r="B11" s="38" t="str">
-        <f>'Portfolio &amp; Rebalancing'!B12</f>
-        <v>APH</v>
-      </c>
-      <c r="C11" s="39">
+      <c r="C11" s="35">
         <f>'Portfolio &amp; Rebalancing'!F12</f>
-        <v>343</v>
-      </c>
-      <c r="D11" s="40">
+        <v>367</v>
+      </c>
+      <c r="D11" s="36">
         <f>'Portfolio &amp; Rebalancing'!E12</f>
         <v>1</v>
       </c>
-      <c r="E11" s="39">
+      <c r="E11" s="35">
         <f t="shared" si="0"/>
-        <v>343</v>
+        <v>367</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="37" t="str">
+      <c r="A12" s="33" t="str">
         <f>'Portfolio &amp; Rebalancing'!A13</f>
+        <v>Amphenol</v>
+      </c>
+      <c r="B12" s="34" t="str">
+        <f>'Portfolio &amp; Rebalancing'!B13</f>
+        <v>APH</v>
+      </c>
+      <c r="C12" s="35">
+        <f>'Portfolio &amp; Rebalancing'!F13</f>
+        <v>369</v>
+      </c>
+      <c r="D12" s="36">
+        <f>'Portfolio &amp; Rebalancing'!E13</f>
+        <v>1</v>
+      </c>
+      <c r="E12" s="35">
+        <f t="shared" si="0"/>
+        <v>369</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="33" t="str">
+        <f>'Portfolio &amp; Rebalancing'!A14</f>
         <v>ASML Holding</v>
       </c>
-      <c r="B12" s="38" t="str">
-        <f>'Portfolio &amp; Rebalancing'!B13</f>
+      <c r="B13" s="34" t="str">
+        <f>'Portfolio &amp; Rebalancing'!B14</f>
         <v>ASML</v>
       </c>
-      <c r="C12" s="39">
-        <f>'Portfolio &amp; Rebalancing'!F13</f>
-        <v>519</v>
-      </c>
-      <c r="D12" s="40">
-        <f>'Portfolio &amp; Rebalancing'!E13</f>
+      <c r="C13" s="35">
+        <f>'Portfolio &amp; Rebalancing'!F14</f>
+        <v>557</v>
+      </c>
+      <c r="D13" s="36">
+        <f>'Portfolio &amp; Rebalancing'!E14</f>
         <v>0</v>
       </c>
-      <c r="E12" s="39">
+      <c r="E13" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="37" t="str">
-        <f>'Portfolio &amp; Rebalancing'!A14</f>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="33" t="str">
+        <f>'Portfolio &amp; Rebalancing'!A15</f>
         <v>Berkshire Hathaway</v>
       </c>
-      <c r="B13" s="38" t="str">
-        <f>'Portfolio &amp; Rebalancing'!B14</f>
+      <c r="B14" s="34" t="str">
+        <f>'Portfolio &amp; Rebalancing'!B15</f>
         <v>BRK.B</v>
       </c>
-      <c r="C13" s="39">
-        <f>'Portfolio &amp; Rebalancing'!F14</f>
-        <v>448</v>
-      </c>
-      <c r="D13" s="40">
-        <f>'Portfolio &amp; Rebalancing'!E14</f>
-        <v>1</v>
-      </c>
-      <c r="E13" s="39">
-        <f t="shared" si="0"/>
-        <v>448</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="str">
-        <f>'Portfolio &amp; Rebalancing'!A15</f>
-        <v>Broadcom</v>
-      </c>
-      <c r="B14" s="38" t="str">
-        <f>'Portfolio &amp; Rebalancing'!B15</f>
-        <v>AVGO</v>
-      </c>
-      <c r="C14" s="39">
+      <c r="C14" s="35">
         <f>'Portfolio &amp; Rebalancing'!F15</f>
-        <v>486</v>
-      </c>
-      <c r="D14" s="40">
+        <v>446</v>
+      </c>
+      <c r="D14" s="36">
         <f>'Portfolio &amp; Rebalancing'!E15</f>
         <v>1</v>
       </c>
-      <c r="E14" s="39">
+      <c r="E14" s="35">
         <f t="shared" si="0"/>
-        <v>486</v>
+        <v>446</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="37" t="str">
+      <c r="A15" s="33" t="str">
         <f>'Portfolio &amp; Rebalancing'!A16</f>
+        <v>Broadcom</v>
+      </c>
+      <c r="B15" s="34" t="str">
+        <f>'Portfolio &amp; Rebalancing'!B16</f>
+        <v>AVGO</v>
+      </c>
+      <c r="C15" s="35">
+        <f>'Portfolio &amp; Rebalancing'!F16</f>
+        <v>464</v>
+      </c>
+      <c r="D15" s="36">
+        <f>'Portfolio &amp; Rebalancing'!E16</f>
+        <v>1</v>
+      </c>
+      <c r="E15" s="35">
+        <f t="shared" si="0"/>
+        <v>464</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="33" t="str">
+        <f>'Portfolio &amp; Rebalancing'!A17</f>
         <v>Hermès</v>
       </c>
-      <c r="B15" s="38" t="str">
-        <f>'Portfolio &amp; Rebalancing'!B16</f>
+      <c r="B16" s="34" t="str">
+        <f>'Portfolio &amp; Rebalancing'!B17</f>
         <v>RMS</v>
       </c>
-      <c r="C15" s="39">
-        <f>'Portfolio &amp; Rebalancing'!F16</f>
-        <v>410</v>
-      </c>
-      <c r="D15" s="40">
-        <f>'Portfolio &amp; Rebalancing'!E16</f>
+      <c r="C16" s="35">
+        <f>'Portfolio &amp; Rebalancing'!F17</f>
+        <v>425</v>
+      </c>
+      <c r="D16" s="36">
+        <f>'Portfolio &amp; Rebalancing'!E17</f>
         <v>0</v>
       </c>
-      <c r="E15" s="39">
+      <c r="E16" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="str">
-        <f>'Portfolio &amp; Rebalancing'!A17</f>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="33" t="str">
+        <f>'Portfolio &amp; Rebalancing'!A18</f>
         <v>Keyence</v>
       </c>
-      <c r="B16" s="38" t="str">
-        <f>'Portfolio &amp; Rebalancing'!B17</f>
+      <c r="B17" s="34" t="str">
+        <f>'Portfolio &amp; Rebalancing'!B18</f>
         <v>KYCCF</v>
       </c>
-      <c r="C16" s="39">
-        <f>'Portfolio &amp; Rebalancing'!F17</f>
+      <c r="C17" s="35">
+        <f>'Portfolio &amp; Rebalancing'!F18</f>
         <v>0</v>
       </c>
-      <c r="D16" s="40">
-        <f>'Portfolio &amp; Rebalancing'!E17</f>
+      <c r="D17" s="36">
+        <f>'Portfolio &amp; Rebalancing'!E18</f>
         <v>0</v>
       </c>
-      <c r="E16" s="39">
+      <c r="E17" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="37" t="str">
-        <f>'Portfolio &amp; Rebalancing'!A18</f>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="33" t="str">
+        <f>'Portfolio &amp; Rebalancing'!A19</f>
         <v>Microsoft</v>
       </c>
-      <c r="B17" s="38" t="str">
-        <f>'Portfolio &amp; Rebalancing'!B18</f>
+      <c r="B18" s="34" t="str">
+        <f>'Portfolio &amp; Rebalancing'!B19</f>
         <v>MSFT</v>
       </c>
-      <c r="C17" s="39">
-        <f>'Portfolio &amp; Rebalancing'!F18</f>
-        <v>425</v>
-      </c>
-      <c r="D17" s="40">
-        <f>'Portfolio &amp; Rebalancing'!E18</f>
+      <c r="C18" s="35">
+        <f>'Portfolio &amp; Rebalancing'!F19</f>
+        <v>400</v>
+      </c>
+      <c r="D18" s="36">
+        <f>'Portfolio &amp; Rebalancing'!E19</f>
         <v>1</v>
       </c>
-      <c r="E17" s="39">
+      <c r="E18" s="35">
         <f t="shared" si="0"/>
-        <v>425</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="37" t="str">
-        <f>'Portfolio &amp; Rebalancing'!A19</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="33" t="str">
+        <f>'Portfolio &amp; Rebalancing'!A20</f>
         <v>Schneider Electric</v>
       </c>
-      <c r="B18" s="38" t="str">
-        <f>'Portfolio &amp; Rebalancing'!B19</f>
+      <c r="B19" s="34" t="str">
+        <f>'Portfolio &amp; Rebalancing'!B20</f>
         <v>SU</v>
       </c>
-      <c r="C18" s="39">
-        <f>'Portfolio &amp; Rebalancing'!F19</f>
-        <v>418</v>
-      </c>
-      <c r="D18" s="40">
-        <f>'Portfolio &amp; Rebalancing'!E19</f>
+      <c r="C19" s="35">
+        <f>'Portfolio &amp; Rebalancing'!F20</f>
+        <v>410</v>
+      </c>
+      <c r="D19" s="36">
+        <f>'Portfolio &amp; Rebalancing'!E20</f>
         <v>0</v>
       </c>
-      <c r="E18" s="39">
+      <c r="E19" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="37" t="str">
-        <f>'Portfolio &amp; Rebalancing'!A20</f>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="33" t="str">
+        <f>'Portfolio &amp; Rebalancing'!A21</f>
         <v>ServiceNow</v>
       </c>
-      <c r="B19" s="38" t="str">
-        <f>'Portfolio &amp; Rebalancing'!B20</f>
+      <c r="B20" s="34" t="str">
+        <f>'Portfolio &amp; Rebalancing'!B21</f>
         <v>NOW</v>
       </c>
-      <c r="C19" s="39">
-        <f>'Portfolio &amp; Rebalancing'!F20</f>
-        <v>451</v>
-      </c>
-      <c r="D19" s="40">
-        <f>'Portfolio &amp; Rebalancing'!E20</f>
-        <v>1</v>
-      </c>
-      <c r="E19" s="39">
-        <f t="shared" si="0"/>
-        <v>451</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="37" t="str">
-        <f>'Portfolio &amp; Rebalancing'!A21</f>
-        <v>Thermo Fisher</v>
-      </c>
-      <c r="B20" s="38" t="str">
-        <f>'Portfolio &amp; Rebalancing'!B21</f>
-        <v>TMO</v>
-      </c>
-      <c r="C20" s="39">
+      <c r="C20" s="35">
         <f>'Portfolio &amp; Rebalancing'!F21</f>
-        <v>396</v>
-      </c>
-      <c r="D20" s="40">
+        <v>924</v>
+      </c>
+      <c r="D20" s="36">
         <f>'Portfolio &amp; Rebalancing'!E21</f>
         <v>1</v>
       </c>
-      <c r="E20" s="39">
+      <c r="E20" s="35">
+        <f t="shared" si="0"/>
+        <v>924</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="33" t="str">
+        <f>'Portfolio &amp; Rebalancing'!A22</f>
+        <v>Thermo Fisher</v>
+      </c>
+      <c r="B21" s="34" t="str">
+        <f>'Portfolio &amp; Rebalancing'!B22</f>
+        <v>TMO</v>
+      </c>
+      <c r="C21" s="35">
+        <f>'Portfolio &amp; Rebalancing'!F22</f>
+        <v>396</v>
+      </c>
+      <c r="D21" s="36">
+        <f>'Portfolio &amp; Rebalancing'!E22</f>
+        <v>1</v>
+      </c>
+      <c r="E21" s="35">
         <f t="shared" si="0"/>
         <v>396</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="37" t="str">
-        <f>'Portfolio &amp; Rebalancing'!A22</f>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="33" t="str">
+        <f>'Portfolio &amp; Rebalancing'!A23</f>
         <v>Visa</v>
       </c>
-      <c r="B21" s="38" t="str">
-        <f>'Portfolio &amp; Rebalancing'!B22</f>
+      <c r="B22" s="34" t="str">
+        <f>'Portfolio &amp; Rebalancing'!B23</f>
         <v>V</v>
       </c>
-      <c r="C21" s="39">
-        <f>'Portfolio &amp; Rebalancing'!F22</f>
-        <v>475</v>
-      </c>
-      <c r="D21" s="40">
-        <f>'Portfolio &amp; Rebalancing'!E22</f>
-        <v>1</v>
-      </c>
-      <c r="E21" s="39">
-        <f t="shared" si="0"/>
-        <v>475</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="37" t="str">
-        <f>'Portfolio &amp; Rebalancing'!A23</f>
-        <v>Zeta Global</v>
-      </c>
-      <c r="B22" s="38" t="str">
-        <f>'Portfolio &amp; Rebalancing'!B23</f>
-        <v>ZETA</v>
-      </c>
-      <c r="C22" s="39">
+      <c r="C22" s="35">
         <f>'Portfolio &amp; Rebalancing'!F23</f>
-        <v>472</v>
-      </c>
-      <c r="D22" s="40">
+        <v>481</v>
+      </c>
+      <c r="D22" s="36">
         <f>'Portfolio &amp; Rebalancing'!E23</f>
         <v>1</v>
       </c>
-      <c r="E22" s="39">
+      <c r="E22" s="35">
         <f t="shared" si="0"/>
-        <v>472</v>
+        <v>481</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="41" t="str">
+      <c r="A23" s="33" t="str">
+        <f>'Portfolio &amp; Rebalancing'!A24</f>
+        <v>Zeta Global</v>
+      </c>
+      <c r="B23" s="34" t="str">
+        <f>'Portfolio &amp; Rebalancing'!B24</f>
+        <v>ZETA</v>
+      </c>
+      <c r="C23" s="35">
+        <f>'Portfolio &amp; Rebalancing'!F24</f>
+        <v>434</v>
+      </c>
+      <c r="D23" s="36">
+        <f>'Portfolio &amp; Rebalancing'!E24</f>
+        <v>1</v>
+      </c>
+      <c r="E23" s="35">
+        <f t="shared" si="0"/>
+        <v>434</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="37" t="str">
         <f>"GESAMT"</f>
         <v>GESAMT</v>
       </c>
-      <c r="C23" s="42">
-        <f>'Portfolio &amp; Rebalancing'!F24</f>
-        <v>12637.16</v>
-      </c>
-      <c r="E23" s="42">
-        <f>SUM(E4:E22)</f>
-        <v>7656.2479999999996</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="41" t="s">
+      <c r="C24" s="38">
+        <f>'Portfolio &amp; Rebalancing'!F25</f>
+        <v>15133.15</v>
+      </c>
+      <c r="E24" s="38">
+        <f>SUM(E4:E23)</f>
+        <v>8087.8819999999996</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="B25" s="43">
-        <f>IF('Portfolio &amp; Rebalancing'!F24=0,0,E23/'Portfolio &amp; Rebalancing'!F24)</f>
-        <v>0.60585194774775342</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="41" t="s">
+      <c r="B26" s="39">
+        <f>IF('Portfolio &amp; Rebalancing'!F25=0,0,E24/'Portfolio &amp; Rebalancing'!F25)</f>
+        <v>0.53444801644072781</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="43">
-        <f>SUMPRODUCT('Portfolio &amp; Rebalancing'!$E$5:$E$23,'Portfolio &amp; Rebalancing'!$I$5:$I$23)/SUM('Portfolio &amp; Rebalancing'!$I$5:$I$23)</f>
-        <v>0.58043646944713845</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="41" t="s">
+      <c r="B27" s="39">
+        <f>SUMPRODUCT('Portfolio &amp; Rebalancing'!$E$5:$E$24,'Portfolio &amp; Rebalancing'!$I$5:$I$24)/SUM('Portfolio &amp; Rebalancing'!$I$5:$I$24)</f>
+        <v>0.52614936954413194</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="B27" s="44">
+      <c r="B28" s="40">
         <f>'Parameter &amp; Regeln'!B11</f>
         <v>0.63</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="41" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="B28" s="41" t="str">
-        <f>IF(B25&gt;B27,"⛔ ÜBER CAP","✅ OK")</f>
+      <c r="B29" s="37" t="str">
+        <f>IF(B26&gt;B28,"⛔ ÜBER CAP","✅ OK")</f>
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="41" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="B29" s="41" t="str">
-        <f>IF(B26&gt;B27,"⛔ ZIEL ÜBER CAP","✅ Ziel OK")</f>
+      <c r="B30" s="37" t="str">
+        <f>IF(B27&gt;B28,"⛔ ZIEL ÜBER CAP","✅ Ziel OK")</f>
         <v>✅ Ziel OK</v>
       </c>
     </row>
@@ -3816,7 +4489,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
@@ -3825,350 +4498,350 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="31" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="32" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="B4" s="45">
+      <c r="B4" s="41">
         <v>1031</v>
       </c>
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="42" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="B5" s="47">
+      <c r="B5" s="43">
         <v>0.59699999999999998</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="42" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="B6" s="47">
+      <c r="B6" s="43">
         <v>0.35299999999999998</v>
       </c>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="42" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="B7" s="47">
+      <c r="B7" s="43">
         <v>0.05</v>
       </c>
-      <c r="C7" s="46" t="s">
+      <c r="C7" s="42" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="B8" s="48">
+      <c r="B8" s="44">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="C8" s="42" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="B9" s="48">
+      <c r="B9" s="44">
         <v>0.04</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="C9" s="42" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="B10" s="47">
+      <c r="B10" s="43">
         <v>0.1</v>
       </c>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="42" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="B11" s="47">
+      <c r="B11" s="43">
         <v>0.63</v>
       </c>
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="42" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="46">
+      <c r="B12" s="42">
         <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="B13" s="46">
-        <f>COUNTIF('Portfolio &amp; Rebalancing'!C5:C23,"Aktie")</f>
+      <c r="B13" s="42">
+        <f>COUNTIF('Portfolio &amp; Rebalancing'!C5:C24,"Aktie")</f>
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="B14" s="49">
-        <f>COUNTIFS('Portfolio &amp; Rebalancing'!A5:A23,"&lt;&gt;",'Portfolio &amp; Rebalancing'!F5:F23,"&gt;0")</f>
-        <v>17</v>
+      <c r="B14" s="45">
+        <f>COUNTIFS('Portfolio &amp; Rebalancing'!A5:A24,"&lt;&gt;",'Portfolio &amp; Rebalancing'!F5:F24,"&gt;0")</f>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="37" t="s">
+      <c r="A15" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="B15" s="49">
+      <c r="B15" s="45">
         <v>3</v>
       </c>
-      <c r="C15" s="46" t="s">
+      <c r="C15" s="42" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="s">
+      <c r="A16" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="B16" s="47">
+      <c r="B16" s="43">
         <f>B5+B6+B7</f>
         <v>1</v>
       </c>
-      <c r="C16" s="46" t="s">
+      <c r="C16" s="42" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="50" t="s">
+      <c r="A17" s="46" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="51" t="s">
+      <c r="A19" s="47" t="s">
         <v>129</v>
       </c>
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="C19" s="51" t="s">
+      <c r="C19" s="47" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="37" t="s">
+      <c r="A20" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="C20" s="46" t="s">
+      <c r="C20" s="42" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="37" t="s">
+      <c r="A21" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="46" t="s">
+      <c r="B21" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="C21" s="46" t="s">
+      <c r="C21" s="42" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="42" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="37" t="s">
+      <c r="A23" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="B23" s="46" t="s">
+      <c r="B23" s="42" t="s">
         <v>141</v>
       </c>
-      <c r="C23" s="46" t="s">
+      <c r="C23" s="42" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="52" t="s">
+      <c r="A25" s="48" t="s">
         <v>143</v>
       </c>
-      <c r="B25" s="58">
+      <c r="B25" s="54">
         <f>B4*B6</f>
         <v>363.94299999999998</v>
       </c>
-      <c r="C25" s="53" t="s">
+      <c r="C25" s="49" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="52" t="s">
+      <c r="A26" s="48" t="s">
         <v>144</v>
       </c>
-      <c r="B26" s="60">
-        <f>COUNTIFS('Portfolio &amp; Rebalancing'!C5:C23,"Aktie",'Portfolio &amp; Rebalancing'!N5:N23,"DEFCON 4*",'Portfolio &amp; Rebalancing'!O5:O23,"&lt;&gt;🔴*")+COUNTIFS('Portfolio &amp; Rebalancing'!C5:C23,"Aktie",'Portfolio &amp; Rebalancing'!N5:N23,"DEFCON 3*",'Portfolio &amp; Rebalancing'!O5:O23,"&lt;&gt;🔴*")</f>
+      <c r="B26" s="56">
+        <f>COUNTIFS('Portfolio &amp; Rebalancing'!C5:C24,"Aktie",'Portfolio &amp; Rebalancing'!N5:N24,"DEFCON 4*",'Portfolio &amp; Rebalancing'!O5:O24,"&lt;&gt;🔴*")+COUNTIFS('Portfolio &amp; Rebalancing'!C5:C24,"Aktie",'Portfolio &amp; Rebalancing'!N5:N24,"DEFCON 3*",'Portfolio &amp; Rebalancing'!O5:O24,"&lt;&gt;🔴*")</f>
         <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="54" t="s">
+      <c r="A27" s="50" t="s">
         <v>145</v>
       </c>
-      <c r="B27" s="59">
+      <c r="B27" s="55">
         <v>0.5</v>
       </c>
-      <c r="C27" s="57" t="s">
+      <c r="C27" s="53" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="55" t="s">
+      <c r="A28" s="51" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="54" t="s">
+      <c r="A29" s="50" t="s">
         <v>147</v>
       </c>
-      <c r="B29" s="56" t="s">
+      <c r="B29" s="52" t="s">
         <v>148</v>
       </c>
-      <c r="C29" s="54" t="s">
+      <c r="C29" s="50" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="54" t="s">
+      <c r="A30" s="50" t="s">
         <v>150</v>
       </c>
-      <c r="B30" s="56" t="s">
+      <c r="B30" s="52" t="s">
         <v>151</v>
       </c>
-      <c r="C30" s="54" t="s">
+      <c r="C30" s="50" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="54" t="s">
+      <c r="A31" s="50" t="s">
         <v>153</v>
       </c>
-      <c r="B31" s="56" t="s">
+      <c r="B31" s="52" t="s">
         <v>154</v>
       </c>
-      <c r="C31" s="54" t="s">
+      <c r="C31" s="50" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="54" t="s">
+      <c r="A32" s="50" t="s">
         <v>156</v>
       </c>
-      <c r="B32" s="56" t="s">
+      <c r="B32" s="52" t="s">
         <v>154</v>
       </c>
-      <c r="C32" s="54" t="s">
+      <c r="C32" s="50" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="72" t="s">
+      <c r="A34" s="68" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="54" t="s">
+      <c r="A35" s="50" t="s">
         <v>159</v>
       </c>
-      <c r="B35" s="73">
+      <c r="B35" s="69">
         <v>40</v>
       </c>
-      <c r="C35" s="54" t="s">
+      <c r="C35" s="50" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="54" t="s">
+      <c r="A36" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="B36" s="73">
+      <c r="B36" s="69">
         <v>32</v>
       </c>
-      <c r="C36" s="54" t="s">
+      <c r="C36" s="50" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="54" t="s">
+      <c r="A37" s="50" t="s">
         <v>163</v>
       </c>
-      <c r="B37" s="73">
+      <c r="B37" s="69">
         <v>18</v>
       </c>
-      <c r="C37" s="54" t="s">
+      <c r="C37" s="50" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="72" t="s">
+      <c r="A39" s="68" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="74" t="s">
+      <c r="A40" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="B40" s="75" t="s">
+      <c r="B40" s="71" t="s">
         <v>166</v>
       </c>
-      <c r="C40" s="74" t="s">
+      <c r="C40" s="70" t="s">
         <v>167</v>
       </c>
     </row>
@@ -4329,7 +5002,7 @@
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="76" t="s">
+      <c r="A55" s="72" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4337,7 +5010,7 @@
       <c r="A56" t="s">
         <v>20</v>
       </c>
-      <c r="B56" s="77">
+      <c r="B56" s="73">
         <v>51</v>
       </c>
     </row>
@@ -4345,62 +5018,67 @@
       <c r="A57" t="s">
         <v>24</v>
       </c>
-      <c r="B57" s="77">
-        <v>257</v>
+      <c r="B57" s="73">
+        <v>206</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>28</v>
       </c>
-      <c r="B58" s="77">
+      <c r="B58" s="73">
         <v>123</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>30</v>
-      </c>
-      <c r="B59" s="77">
-        <v>103</v>
+        <v>171</v>
+      </c>
+      <c r="B59" s="73">
+        <v>82</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>32</v>
-      </c>
-      <c r="B60" s="77">
+        <v>30</v>
+      </c>
+      <c r="B60" s="73">
         <v>82</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>32</v>
+      </c>
+      <c r="B61" s="73">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>34</v>
       </c>
-      <c r="B61" s="77">
+      <c r="B62" s="73">
         <v>51</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="76" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="72" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>170</v>
       </c>
-      <c r="B64" s="77">
+      <c r="B65" s="73">
         <v>300</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B16">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>B16=1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>B16&lt;&gt;1</formula>
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>ABS($B$16-1)&gt;0.0001</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
